--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samanthahowley\Desktop\SpringMetabolism_FlowReversals\04_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8023056E-2C93-4EE8-80E9-2D5BA108008A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CFA93A-FAFC-4CBC-A0BF-06B2963C9E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="ID" sheetId="3" r:id="rId3"/>
     <sheet name="LF" sheetId="4" r:id="rId4"/>
     <sheet name="OS" sheetId="5" r:id="rId5"/>
+    <sheet name="velocity" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -9312,4 +9313,1178 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96202A1F-4F02-47EE-B239-F409335667E4}">
+  <dimension ref="A1:C111"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.66360277136277601</v>
+      </c>
+      <c r="B2">
+        <v>0.41148000000000001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>0.66360277136277601</v>
+      </c>
+      <c r="B3">
+        <v>0.41148000000000001</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>0.84496568832957797</v>
+      </c>
+      <c r="B4">
+        <v>0.41148000000000001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>0.84496568832957797</v>
+      </c>
+      <c r="B5">
+        <v>0.41148000000000001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1.79712100240526</v>
+      </c>
+      <c r="B6">
+        <v>9.6864407E-2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1.79712100240526</v>
+      </c>
+      <c r="B7">
+        <v>9.6864407E-2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1.91936208989603</v>
+      </c>
+      <c r="B8">
+        <v>2.5907667999999998E-2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1.91936208989603</v>
+      </c>
+      <c r="B9">
+        <v>2.5907667999999998E-2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1.5364118092654899</v>
+      </c>
+      <c r="B10">
+        <v>0.111489093</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1.5364118092654899</v>
+      </c>
+      <c r="B11">
+        <v>0.111489093</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1.14254792657094</v>
+      </c>
+      <c r="B12">
+        <v>8.1843182E-2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1.14254792657094</v>
+      </c>
+      <c r="B13">
+        <v>8.1843182E-2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>0.76948902444658396</v>
+      </c>
+      <c r="B14">
+        <v>0.24384</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>0.74683198736593104</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>0.634197514012805</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>0.81193724612891904</v>
+      </c>
+      <c r="B17">
+        <v>0.26351463400000003</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>0.81193724612891904</v>
+      </c>
+      <c r="B18">
+        <v>0.26351463400000003</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>0.64229622161300404</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.64229622161300404</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>0.66551573852542301</v>
+      </c>
+      <c r="B21">
+        <v>0.24384</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>0.66551573852542301</v>
+      </c>
+      <c r="B22">
+        <v>0.24384</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>0.66831711482098599</v>
+      </c>
+      <c r="B23">
+        <v>0.392848743</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>0.66831711482098599</v>
+      </c>
+      <c r="B24">
+        <v>0.392848743</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>0.65580679181917101</v>
+      </c>
+      <c r="B25">
+        <v>0.392848743</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>0.65580679181917101</v>
+      </c>
+      <c r="B26">
+        <v>0.392848743</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>0.500234239386116</v>
+      </c>
+      <c r="B27">
+        <v>0.13716</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>0.500234239386116</v>
+      </c>
+      <c r="B28">
+        <v>0.13716</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>0.49838619196324002</v>
+      </c>
+      <c r="B29">
+        <v>0.195072</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>0.49838619196324002</v>
+      </c>
+      <c r="B30">
+        <v>0.195072</v>
+      </c>
+      <c r="C30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>0.496481994488156</v>
+      </c>
+      <c r="B31">
+        <v>0.18592800000000001</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>0.496481994488156</v>
+      </c>
+      <c r="B32">
+        <v>0.18592800000000001</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>0.49364073113116103</v>
+      </c>
+      <c r="B33">
+        <v>0.176784</v>
+      </c>
+      <c r="C33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>0.49364073113116103</v>
+      </c>
+      <c r="B34">
+        <v>0.176784</v>
+      </c>
+      <c r="C34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="B35">
+        <v>0.20116800000000001</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="B36">
+        <v>0.20116800000000001</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>0.48738009477924898</v>
+      </c>
+      <c r="B37">
+        <v>0.20319999999999999</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>0.46633139234925403</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>0.44959398748926399</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>0.42847041975631001</v>
+      </c>
+      <c r="B40">
+        <v>0.17526</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>0.40867897602588799</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>0.41829191635495</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>0.57001899623787999</v>
+      </c>
+      <c r="B43">
+        <v>9.0498811999999998E-2</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="B44">
+        <v>0.132051846</v>
+      </c>
+      <c r="C44" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>0.52913409322569804</v>
+      </c>
+      <c r="B45">
+        <v>0.16555581</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>0.51433262189204798</v>
+      </c>
+      <c r="B46">
+        <v>0.15135790499999999</v>
+      </c>
+      <c r="C46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>0.84629581545158405</v>
+      </c>
+      <c r="B47">
+        <v>0.38927203100000002</v>
+      </c>
+      <c r="C47" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>0.84629581545158405</v>
+      </c>
+      <c r="B48">
+        <v>0.38927203100000002</v>
+      </c>
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>0.89039772710795695</v>
+      </c>
+      <c r="B49">
+        <v>0.24384</v>
+      </c>
+      <c r="C49" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>0.89039772710795695</v>
+      </c>
+      <c r="B50">
+        <v>0.24384</v>
+      </c>
+      <c r="C50" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1.2795322417230099</v>
+      </c>
+      <c r="B51">
+        <v>0.27730699199999997</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1.2795322417230099</v>
+      </c>
+      <c r="B52">
+        <v>0.27730699199999997</v>
+      </c>
+      <c r="C52" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1.93587245637372</v>
+      </c>
+      <c r="B53">
+        <v>0.152032679</v>
+      </c>
+      <c r="C53" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1.93587245637372</v>
+      </c>
+      <c r="B54">
+        <v>0.152032679</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2.4780665467373599</v>
+      </c>
+      <c r="B55">
+        <v>9.9617103999999998E-2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2.4780665467373599</v>
+      </c>
+      <c r="B56">
+        <v>9.9617103999999998E-2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>1.77503019033284</v>
+      </c>
+      <c r="B57">
+        <v>0.20904352600000001</v>
+      </c>
+      <c r="C57" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>1.7075802077995601</v>
+      </c>
+      <c r="B58">
+        <v>0.14364185700000001</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>1.4922591097125699</v>
+      </c>
+      <c r="B59">
+        <v>0.217546613</v>
+      </c>
+      <c r="C59" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1.11609574558469</v>
+      </c>
+      <c r="B60">
+        <v>0.29169342100000001</v>
+      </c>
+      <c r="C60" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1.00713808149247</v>
+      </c>
+      <c r="C61" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>0.99935539120017003</v>
+      </c>
+      <c r="B62">
+        <v>0.245749827</v>
+      </c>
+      <c r="C62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>0.99935539120017003</v>
+      </c>
+      <c r="B63">
+        <v>0.245749827</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>0.94487655915406399</v>
+      </c>
+      <c r="B64">
+        <v>0.31575888699999999</v>
+      </c>
+      <c r="C64" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>0.94487655915406399</v>
+      </c>
+      <c r="B65">
+        <v>0.31575888699999999</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>0.87483234652335495</v>
+      </c>
+      <c r="B66">
+        <v>0.27092143800000001</v>
+      </c>
+      <c r="C66" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>0.87483234652335495</v>
+      </c>
+      <c r="B67">
+        <v>0.27092143800000001</v>
+      </c>
+      <c r="C67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>0.27582680972963097</v>
+      </c>
+      <c r="B68">
+        <v>9.9059999999999995E-2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>0.27582680972963097</v>
+      </c>
+      <c r="B69">
+        <v>9.9059999999999995E-2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>0.14842325926962999</v>
+      </c>
+      <c r="B70">
+        <v>0.103632</v>
+      </c>
+      <c r="C70" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>0.14842325926962999</v>
+      </c>
+      <c r="B71">
+        <v>0.103632</v>
+      </c>
+      <c r="C71" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>0.13941805406320101</v>
+      </c>
+      <c r="B72">
+        <v>0.100003886</v>
+      </c>
+      <c r="C72" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>0.13941805406320101</v>
+      </c>
+      <c r="B73">
+        <v>0.100003886</v>
+      </c>
+      <c r="C73" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>0.35708644464821998</v>
+      </c>
+      <c r="B74">
+        <v>6.8341643999999993E-2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>0.35708644464821998</v>
+      </c>
+      <c r="B75">
+        <v>6.8341643999999993E-2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>0.97908907233996301</v>
+      </c>
+      <c r="B76">
+        <v>7.7164556999999995E-2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>0.97908907233996301</v>
+      </c>
+      <c r="B77">
+        <v>7.7164556999999995E-2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>0.73912910715284497</v>
+      </c>
+      <c r="B78">
+        <v>5.9129280999999999E-2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>0.73912910715284497</v>
+      </c>
+      <c r="B79">
+        <v>5.9129280999999999E-2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>0.50655758454314603</v>
+      </c>
+      <c r="B80">
+        <v>0.12576395200000001</v>
+      </c>
+      <c r="C80" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>0.50655758454314603</v>
+      </c>
+      <c r="B81">
+        <v>0.12576395200000001</v>
+      </c>
+      <c r="C81" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>0.26422745354100802</v>
+      </c>
+      <c r="B82">
+        <v>9.0472021999999999E-2</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>0.26422745354100802</v>
+      </c>
+      <c r="B83">
+        <v>9.0472021999999999E-2</v>
+      </c>
+      <c r="C83" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>0.20547930573848</v>
+      </c>
+      <c r="B84">
+        <v>0.10404495</v>
+      </c>
+      <c r="C84" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>0.20547930573848</v>
+      </c>
+      <c r="B85">
+        <v>0.10404495</v>
+      </c>
+      <c r="C85" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>0.168078940883987</v>
+      </c>
+      <c r="C86" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>0.168078940883987</v>
+      </c>
+      <c r="C87" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>0.25776243935158599</v>
+      </c>
+      <c r="B88">
+        <v>0.142205108</v>
+      </c>
+      <c r="C88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>0.30718976746298698</v>
+      </c>
+      <c r="C89" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>0.24912069961521999</v>
+      </c>
+      <c r="B90">
+        <v>0.11911748799999999</v>
+      </c>
+      <c r="C90" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>0.24912069961521999</v>
+      </c>
+      <c r="B91">
+        <v>0.11911748799999999</v>
+      </c>
+      <c r="C91" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>0.23799883780685399</v>
+      </c>
+      <c r="C92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>0.23799883780685399</v>
+      </c>
+      <c r="C93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>0.26752308407063402</v>
+      </c>
+      <c r="C94" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>0.26752308407063402</v>
+      </c>
+      <c r="C95" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>0.16056832408994501</v>
+      </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>0.16056832408994501</v>
+      </c>
+      <c r="C97" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>0.74411257103448103</v>
+      </c>
+      <c r="B98">
+        <v>0.116835492</v>
+      </c>
+      <c r="C98" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>0.74411257103448103</v>
+      </c>
+      <c r="B99">
+        <v>0.116835492</v>
+      </c>
+      <c r="C99" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>0.87528110109794</v>
+      </c>
+      <c r="B100">
+        <v>8.9573877999999996E-2</v>
+      </c>
+      <c r="C100" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>0.87528110109794</v>
+      </c>
+      <c r="B101">
+        <v>8.9573877999999996E-2</v>
+      </c>
+      <c r="C101" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>1.62598028208757</v>
+      </c>
+      <c r="B102">
+        <v>4.0360477999999998E-2</v>
+      </c>
+      <c r="C102" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>1.62598028208757</v>
+      </c>
+      <c r="B103">
+        <v>4.0360477999999998E-2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>1.32277923770115</v>
+      </c>
+      <c r="B104">
+        <v>3.2272940999999999E-2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>1.32277923770115</v>
+      </c>
+      <c r="B105">
+        <v>3.2272940999999999E-2</v>
+      </c>
+      <c r="C105" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>1.0535668624027901</v>
+      </c>
+      <c r="B106">
+        <v>5.4257143000000001E-2</v>
+      </c>
+      <c r="C106" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>0.78894922945176305</v>
+      </c>
+      <c r="C107" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>0.73759563320647703</v>
+      </c>
+      <c r="B108">
+        <v>0.137964795</v>
+      </c>
+      <c r="C108" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>0.73062868871751996</v>
+      </c>
+      <c r="B109">
+        <v>0.14825882000000001</v>
+      </c>
+      <c r="C109" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>0.74233596483651698</v>
+      </c>
+      <c r="B110">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>0.74233596483651698</v>
+      </c>
+      <c r="B111">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36CFA93A-FAFC-4CBC-A0BF-06B2963C9E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36744AEB-1C57-404E-BF73-00A3EA00B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,9 @@
     <sheet name="ID" sheetId="3" r:id="rId3"/>
     <sheet name="LF" sheetId="4" r:id="rId4"/>
     <sheet name="OS" sheetId="5" r:id="rId5"/>
-    <sheet name="velocity" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="42">
   <si>
     <t>Date</t>
   </si>
@@ -304,26 +304,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>AM!$B$2:$B$26</c:f>
+              <c:f>AM!$B$2:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.66360277136277601</c:v>
                 </c:pt>
@@ -337,66 +323,81 @@
                   <c:v>0.84496568832957797</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.79712100240526</c:v>
+                  <c:v>0.84496568832957797</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1.79712100240526</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.91936208989603</c:v>
+                  <c:v>1.79712100240526</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1.91936208989603</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.5364118092654899</c:v>
+                  <c:v>1.91936208989603</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.5364118092654899</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>1.5364118092654899</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.5364118092654899</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>1.14254792657094</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>1.14254792657094</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
+                  <c:v>1.14254792657094</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.76948902444658396</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="16">
                   <c:v>0.74683198736593104</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="17">
+                  <c:v>0.74683198736593104</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>0.634197514012805</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>0.81193724612891904</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>0.81193724612891904</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="21">
                   <c:v>0.64229622161300404</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="22">
                   <c:v>0.64229622161300404</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>0.66551573852542301</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>0.66551573852542301</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
+                  <c:v>0.66551573852542301</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0.66831711482098599</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="27">
                   <c:v>0.66831711482098599</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="28">
                   <c:v>0.65580679181917101</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="29">
                   <c:v>0.65580679181917101</c:v>
                 </c:pt>
               </c:numCache>
@@ -404,10 +405,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>AM!$C$2:$C$26</c:f>
+              <c:f>AM!$C$2:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
                   <c:v>0.41148000000000001</c:v>
                 </c:pt>
@@ -421,54 +422,66 @@
                   <c:v>0.41148000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.6864407E-2</c:v>
+                  <c:v>0.41148000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>9.6864407E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.5907667999999998E-2</c:v>
+                  <c:v>9.6864407E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>2.5907667999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.111489093</c:v>
+                  <c:v>2.5907667999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0.111489093</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>0.111489093</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.111489093</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>8.1843182E-2</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
                   <c:v>8.1843182E-2</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="14">
+                  <c:v>8.1843182E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0.24384</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="19">
                   <c:v>0.26351463400000003</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="20">
                   <c:v>0.26351463400000003</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="23">
                   <c:v>0.24384</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="24">
                   <c:v>0.24384</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="25">
+                  <c:v>0.24384</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0.392848743</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="27">
                   <c:v>0.392848743</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="28">
                   <c:v>0.392848743</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="29">
                   <c:v>0.392848743</c:v>
                 </c:pt>
               </c:numCache>
@@ -477,7 +490,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B42E-4FE4-A5B9-479E57418EA2}"/>
+              <c16:uniqueId val="{00000000-46A5-4B22-86F8-C2458802697F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -489,11 +502,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="481018623"/>
-        <c:axId val="481011903"/>
+        <c:axId val="1128867872"/>
+        <c:axId val="1128877952"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="481018623"/>
+        <c:axId val="1128867872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -550,12 +563,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481011903"/>
+        <c:crossAx val="1128877952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="481011903"/>
+        <c:axId val="1128877952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -612,7 +625,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="481018623"/>
+        <c:crossAx val="1128867872"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -626,6 +639,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -633,7 +647,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -723,11 +736,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>AM!$F$1</c:f>
+              <c:f>GB!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>k600_1d</c:v>
+                  <c:v>u</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -770,150 +783,174 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>AM!$E$2:$E$26</c:f>
+              <c:f>GB!$B$2:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>0.62006974316123398</c:v>
+                  <c:v>0.500234239386116</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.62006974316123398</c:v>
+                  <c:v>0.500234239386116</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.48697835389441602</c:v>
+                  <c:v>0.500234239386116</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.48697835389441602</c:v>
+                  <c:v>0.49838619196324002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.38997690585983E-2</c:v>
+                  <c:v>0.49838619196324002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.38997690585983E-2</c:v>
+                  <c:v>0.496481994488156</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.34980617447766E-2</c:v>
+                  <c:v>0.496481994488156</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.34980617447766E-2</c:v>
+                  <c:v>0.49364073113116103</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.25645899931604E-2</c:v>
+                  <c:v>0.49364073113116103</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.25645899931604E-2</c:v>
+                  <c:v>0.49364073113116103</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.1632165353124999E-2</c:v>
+                  <c:v>0.48014251849385198</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.1632165353124999E-2</c:v>
+                  <c:v>0.48014251849385198</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.31688561142944099</c:v>
+                  <c:v>0.48014251849385198</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.48738009477924898</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.48738009477924898</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.32455049359585503</c:v>
+                  <c:v>0.46633139234925403</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.32455049359585503</c:v>
+                  <c:v>0.44959398748926399</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.42847041975631001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.42847041975631001</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.36639253722274701</c:v>
+                  <c:v>0.40867897602588799</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.36639253722274701</c:v>
+                  <c:v>0.40867897602588799</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.587817870121772</c:v>
+                  <c:v>0.41829191635495</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.587817870121772</c:v>
+                  <c:v>0.57001899623787999</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.59903122062865499</c:v>
+                  <c:v>0.55068895347565805</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.59903122062865499</c:v>
+                  <c:v>0.55068895347565805</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.52913409322569804</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.51433262189204798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>AM!$F$2:$F$26</c:f>
+              <c:f>GB!$F$2:$F$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="25"/>
+                <c:ptCount val="27"/>
+                <c:pt idx="0">
+                  <c:v>8.0617713895940106</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>14.0537866274825</c:v>
+                  <c:v>8.0092423263314494</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.2509884099436</c:v>
+                  <c:v>20.759702379649699</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17.9748429691486</c:v>
+                  <c:v>11.7604829329048</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.3659747293628499</c:v>
+                  <c:v>11.63069034185</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.43477614979118</c:v>
+                  <c:v>16.082464877533099</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.762817767337299</c:v>
+                  <c:v>19.278549967453198</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.954970513126703</c:v>
+                  <c:v>18.3266040851639</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.2531836035536301</c:v>
+                  <c:v>18.238219059268399</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.4433323290317999</c:v>
+                  <c:v>15.8324828082942</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.0432970693483599</c:v>
+                  <c:v>12.5427239203201</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.7839849332143101</c:v>
+                  <c:v>10.123963721124101</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.6754733355837299</c:v>
+                  <c:v>9.9882836327260591</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>22.624195858075399</c:v>
+                  <c:v>15.491084387970799</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>16.1504080056141</c:v>
+                  <c:v>15.422189134531401</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.76777594040046</c:v>
+                  <c:v>28.8790872259084</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>11.6535292051355</c:v>
+                  <c:v>31.877696149374302</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>32.6657378105105</c:v>
+                  <c:v>32.379700829916601</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>51.880320990253502</c:v>
+                  <c:v>32.274144438345303</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8.0612152297113795</c:v>
+                  <c:v>19.545410722183501</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>19.3542063534147</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>23.531152831216499</c:v>
+                  <c:v>21.2301041068087</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>18.703245444769301</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>15.9745813671168</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>17.496680423021001</c:v>
+                  <c:v>-2.7729314633187902E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>17.612268500013801</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>10.116682809798901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -921,7 +958,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E24B-4400-B4B2-F00507D02776}"/>
+              <c16:uniqueId val="{00000000-7845-4E05-9612-5DF4AEBCDB3E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -933,11 +970,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="650986447"/>
-        <c:axId val="554169119"/>
+        <c:axId val="1729563344"/>
+        <c:axId val="1886997552"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="650986447"/>
+        <c:axId val="1729563344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -994,12 +1031,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="554169119"/>
+        <c:crossAx val="1886997552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="554169119"/>
+        <c:axId val="1886997552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1056,7 +1093,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="650986447"/>
+        <c:crossAx val="1729563344"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1070,6 +1107,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1077,7 +1115,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1167,7 +1204,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GB!$C$1</c:f>
+              <c:f>ID!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1198,178 +1235,101 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="4.3667760279965002E-2"/>
-                  <c:y val="-0.4613137941090697"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>GB!$B$2:$B$21</c:f>
+              <c:f>ID!$B$2:$B$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0.500234239386116</c:v>
+                  <c:v>0.84629581545158405</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.500234239386116</c:v>
+                  <c:v>0.89039772710795695</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.49838619196324002</c:v>
+                  <c:v>1.2795322417230099</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.49838619196324002</c:v>
+                  <c:v>1.93587245637372</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.496481994488156</c:v>
+                  <c:v>2.4780665467373599</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.496481994488156</c:v>
+                  <c:v>1.77503019033284</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.49364073113116103</c:v>
+                  <c:v>1.7075802077995601</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.49364073113116103</c:v>
+                  <c:v>1.4922591097125699</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.48014251849385198</c:v>
+                  <c:v>1.4922591097125699</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.48014251849385198</c:v>
+                  <c:v>1.11609574558469</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.48738009477924898</c:v>
+                  <c:v>1.00713808149247</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.46633139234925403</c:v>
+                  <c:v>0.99935539120017003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.44959398748926399</c:v>
+                  <c:v>0.94487655915406399</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.42847041975631001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.40867897602588799</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.41829191635495</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.57001899623787999</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.55068895347565805</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.52913409322569804</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.51433262189204798</c:v>
+                  <c:v>0.87483234652335495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$C$2:$C$21</c:f>
+              <c:f>ID!$C$2:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
-                  <c:v>0.13716</c:v>
+                  <c:v>0.38927203100000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.13716</c:v>
+                  <c:v>0.24384</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.195072</c:v>
+                  <c:v>0.27730699199999997</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.195072</c:v>
+                  <c:v>0.152032679</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.18592800000000001</c:v>
+                  <c:v>9.9617103999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.18592800000000001</c:v>
+                  <c:v>0.20904352600000001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.176784</c:v>
+                  <c:v>0.14364185700000001</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.176784</c:v>
+                  <c:v>0.217546613</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.20116800000000001</c:v>
+                  <c:v>0.217546613</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.20116800000000001</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20319999999999999</c:v>
+                  <c:v>0.29169342100000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.245749827</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.31575888699999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.17526</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>9.0498811999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.132051846</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.16555581</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.15135790499999999</c:v>
+                  <c:v>0.27092143800000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1377,7 +1337,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AF59-4D97-8BDB-D486BAD63497}"/>
+              <c16:uniqueId val="{00000000-20BD-4835-9365-47E4A348CA11}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1389,11 +1349,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="650985967"/>
-        <c:axId val="650988367"/>
+        <c:axId val="1871026208"/>
+        <c:axId val="1871025728"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="650985967"/>
+        <c:axId val="1871026208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1450,12 +1410,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="650988367"/>
+        <c:crossAx val="1871025728"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="650988367"/>
+        <c:axId val="1871025728"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1512,7 +1472,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="650985967"/>
+        <c:crossAx val="1871026208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1526,6 +1486,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1533,7 +1494,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1623,11 +1583,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GB!$F$1</c:f>
+              <c:f>LF!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>k600_1d</c:v>
+                  <c:v>u</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1665,164 +1625,119 @@
               <a:effectLst/>
             </c:spPr>
             <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:layout>
-                <c:manualLayout>
-                  <c:x val="4.9454943132108485E-2"/>
-                  <c:y val="-0.66493985126859145"/>
-                </c:manualLayout>
-              </c:layout>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>GB!$E$2:$E$21</c:f>
+              <c:f>LF!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0.27419154708066701</c:v>
+                  <c:v>0.27582680972963097</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.27419154708066701</c:v>
+                  <c:v>0.27582680972963097</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.39140731253322603</c:v>
+                  <c:v>0.14842325926962999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.39140731253322603</c:v>
+                  <c:v>0.13941805406320101</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.37449092225727298</c:v>
+                  <c:v>0.35708644464821998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.37449092225727298</c:v>
+                  <c:v>0.35708644464821998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35812279832522198</c:v>
+                  <c:v>0.97908907233996301</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35812279832522198</c:v>
+                  <c:v>0.73912910715284497</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.418975600475957</c:v>
+                  <c:v>0.50655758454314603</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.418975600475957</c:v>
+                  <c:v>0.26422745354100802</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.41692305897727699</c:v>
+                  <c:v>0.20547930573848</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.21787081390374799</c:v>
+                  <c:v>0.168078940883987</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.31185470424768102</c:v>
+                  <c:v>0.25776243935158599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.40903640465934199</c:v>
+                  <c:v>0.30718976746298698</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.24912069961521999</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.23799883780685399</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.15876455451009799</c:v>
+                  <c:v>0.26752308407063402</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.239793889393565</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.31288063294266599</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.29428019642854403</c:v>
+                  <c:v>0.16056832408994501</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$F$2:$F$21</c:f>
+              <c:f>LF!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>9.9059999999999995E-2</c:v>
+                </c:pt>
                 <c:pt idx="1">
-                  <c:v>20.759702379649699</c:v>
+                  <c:v>9.9059999999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.7604829329048</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11.63069034185</c:v>
+                  <c:v>0.103632</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16.082464877533099</c:v>
+                  <c:v>6.8341643999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>19.278549967453198</c:v>
+                  <c:v>6.8341643999999993E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>18.3266040851639</c:v>
+                  <c:v>7.7164556999999995E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>15.8324828082942</c:v>
+                  <c:v>5.9129280999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.5427239203201</c:v>
+                  <c:v>0.12576395200000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10.123963721124101</c:v>
+                  <c:v>9.0472021999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>15.491084387970799</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>28.8790872259084</c:v>
+                  <c:v>0.10404495</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>31.877696149374302</c:v>
+                  <c:v>0.142205108</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>19.545410722183501</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>21.2301041068087</c:v>
+                  <c:v>0.11911748799999999</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.23330000000000001</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>44.743071696612503</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>17.612268500013801</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>10.116682809798901</c:v>
+                  <c:v>0.23330000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1830,7 +1745,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-137A-4BF5-8D48-6C2CA5C13296}"/>
+              <c16:uniqueId val="{00000000-2349-4E14-91C4-B8E9F08548FA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1842,11 +1757,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="559563103"/>
-        <c:axId val="559567903"/>
+        <c:axId val="1624481104"/>
+        <c:axId val="1132239360"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="559563103"/>
+        <c:axId val="1624481104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1903,12 +1818,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559567903"/>
+        <c:crossAx val="1132239360"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="559567903"/>
+        <c:axId val="1132239360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1965,7 +1880,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="559563103"/>
+        <c:crossAx val="1624481104"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1979,6 +1894,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1986,7 +1902,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2076,7 +1991,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>LF!$C$1</c:f>
+              <c:f>OS!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2107,217 +2022,116 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="1"/>
-            <c:dispEq val="1"/>
-            <c:trendlineLbl>
-              <c:numFmt formatCode="General" sourceLinked="0"/>
-              <c:spPr>
-                <a:noFill/>
-                <a:ln>
-                  <a:noFill/>
-                </a:ln>
-                <a:effectLst/>
-              </c:spPr>
-              <c:txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="+mn-lt"/>
-                      <a:ea typeface="+mn-ea"/>
-                      <a:cs typeface="+mn-cs"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:endParaRPr lang="en-US"/>
-                </a:p>
-              </c:txPr>
-            </c:trendlineLbl>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>LF!$B$2:$B$31</c:f>
+              <c:f>OS!$B$2:$B$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>0.27582680972963097</c:v>
+                  <c:v>0.74411257103448103</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.27582680972963097</c:v>
+                  <c:v>0.74411257103448103</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.14842325926962999</c:v>
+                  <c:v>0.74411257103448103</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.14842325926962999</c:v>
+                  <c:v>0.87528110109794</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.13941805406320101</c:v>
+                  <c:v>0.87528110109794</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.13941805406320101</c:v>
+                  <c:v>0.87528110109794</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.35708644464821998</c:v>
+                  <c:v>1.62598028208757</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35708644464821998</c:v>
+                  <c:v>1.62598028208757</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.97908907233996301</c:v>
+                  <c:v>1.32277923770115</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.97908907233996301</c:v>
+                  <c:v>1.32277923770115</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.73912910715284497</c:v>
+                  <c:v>1.0535668624027901</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.73912910715284497</c:v>
+                  <c:v>0.78894922945176305</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.50655758454314603</c:v>
+                  <c:v>0.73759563320647703</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.50655758454314603</c:v>
+                  <c:v>0.73062868871751996</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.26422745354100802</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.26422745354100802</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.20547930573848</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.20547930573848</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.168078940883987</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.168078940883987</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.25776243935158599</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.30718976746298698</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.24912069961521999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.24912069961521999</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.23799883780685399</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.23799883780685399</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.26752308407063402</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.26752308407063402</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>0.16056832408994501</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>0.16056832408994501</c:v>
+                  <c:v>0.73062868871751996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>LF!$C$2:$C$31</c:f>
+              <c:f>OS!$C$2:$C$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>9.9059999999999995E-2</c:v>
+                  <c:v>0.116835492</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.9059999999999995E-2</c:v>
+                  <c:v>0.116835492</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.103632</c:v>
+                  <c:v>0.116835492</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.103632</c:v>
+                  <c:v>8.9573877999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.100003886</c:v>
+                  <c:v>8.9573877999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.100003886</c:v>
+                  <c:v>8.9573877999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.8341643999999993E-2</c:v>
+                  <c:v>4.0360477999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.8341643999999993E-2</c:v>
+                  <c:v>4.0360477999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.7164556999999995E-2</c:v>
+                  <c:v>3.2272940999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.7164556999999995E-2</c:v>
+                  <c:v>3.2272940999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>5.9129280999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>5.9129280999999999E-2</c:v>
+                  <c:v>5.4257143000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.12576395200000001</c:v>
+                  <c:v>0.137964795</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.12576395200000001</c:v>
+                  <c:v>0.14825882000000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>9.0472021999999999E-2</c:v>
+                  <c:v>0.14825882000000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>9.0472021999999999E-2</c:v>
+                  <c:v>1.2192E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.10404495</c:v>
+                  <c:v>1.2192E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.10404495</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.142205108</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.11911748799999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.11911748799999999</c:v>
+                  <c:v>1.2192E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2325,7 +2139,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B288-4377-9DF3-9AB298D3888C}"/>
+              <c16:uniqueId val="{00000000-BA74-41FB-86E9-C0420B0B15F4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2337,11 +2151,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="192776815"/>
-        <c:axId val="192777775"/>
+        <c:axId val="1860211616"/>
+        <c:axId val="1860209216"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="192776815"/>
+        <c:axId val="1860211616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2398,12 +2212,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="192777775"/>
+        <c:crossAx val="1860209216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="192777775"/>
+        <c:axId val="1860209216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2460,7 +2274,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="192776815"/>
+        <c:crossAx val="1860211616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2474,6 +2288,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2481,490 +2296,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>LF!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>k600_1d</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
-          <c:xVal>
-            <c:numRef>
-              <c:f>LF!$E$2:$E$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>0.359138403178066</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.359138403178066</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.69821940651323</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.69821940651323</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.71729509260447999</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.71729509260447999</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.19138683370444401</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.19138683370444401</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>7.8812601610986702E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>7.8812601610986702E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.9998582693852197E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.9998582693852197E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.24827177765667799</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.24827177765667799</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.34240205091314901</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.34240205091314901</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.50635245055977096</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.50635245055977096</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.32164483971442398</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.32164483971442398</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.55169057352857198</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>0.47815170792303902</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.47815170792303902</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.97021100240578795</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.97021100240578795</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.87207427654505298</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.87207427654505298</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.45296403460818</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.45296403460818</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>LF!$F$2:$F$31</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
-                <c:pt idx="0">
-                  <c:v>24.690084932127998</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>24.690084932127998</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>118.259222088889</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>118.259222088889</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>50.954752325421801</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50.954752325421801</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>9.73092604234097</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>9.73092604234097</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>12.1601192837523</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>12.1601192837523</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>7.9516472320781002</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>7.9516472320781002</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>30.7702058957052</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30.7702058957052</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>34.983383524448797</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>34.983383524448797</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>53.152789367811998</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>53.152789367811998</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>33.341043343649702</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>33.341043343649702</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>31.9180285667398</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>15.8650769934215</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>26.1959995510725</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>26.1959995510725</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>94.218748150536896</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>94.218748150536896</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>115.910838296351</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>115.910838296351</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2BBC-429F-A4D5-5C4DCC543DBB}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1488350767"/>
-        <c:axId val="1488347407"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1488350767"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1488347407"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1488347407"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1488350767"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3199,46 +2530,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -5819,543 +5110,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>195262</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>195262</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>14287</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5723568D-6F30-465C-6B76-C1E870311CD4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE14FCCF-C532-FAD8-B774-C29805A0D67D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6373,42 +5148,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>271462</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>271462</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{305B2FCC-A530-0982-BA29-B1624C664FDF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6416,23 +5155,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>100012</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3210AEA8-1DCC-E3EB-36BE-C186F27E7654}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE4B8E65-7449-6AA2-303D-7FEFFFCE5381}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6450,42 +5189,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>366712</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>23812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>366712</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{266D8F5C-4B2B-634B-4FB5-6E8C52644873}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -6493,15 +5196,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6509,7 +5212,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{187AEFAC-F13A-7EED-5423-4F81C144B062}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDEC00EF-2730-19B8-DB6A-50F0EE1D5199}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6527,25 +5230,30 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>357187</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>176212</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>357187</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
+        <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB4813E-DDD7-9266-8F7B-CB99233116D3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49BF9AF9-F0B6-3241-B273-5C2893680841}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6557,7 +5265,48 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF99EFC-A32B-0EFF-C138-8FEB3F4F3926}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -6845,7 +5594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6890,6 +5639,9 @@
       <c r="E2">
         <v>0.62006974316123398</v>
       </c>
+      <c r="F2">
+        <v>8.7000179355782503</v>
+      </c>
       <c r="G2">
         <v>1.5</v>
       </c>
@@ -6966,7 +5718,7 @@
         <v>0.48697835389441602</v>
       </c>
       <c r="F5">
-        <v>17.9748429691486</v>
+        <v>14.019548098025901</v>
       </c>
       <c r="G5">
         <v>1.097</v>
@@ -6977,25 +5729,28 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>1.79712100240526</v>
+        <v>0.84496568832957797</v>
       </c>
       <c r="C6">
-        <v>9.6864407E-2</v>
+        <v>0.41148000000000001</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6">
-        <v>5.38997690585983E-2</v>
+        <v>0.48697835389441602</v>
       </c>
       <c r="F6">
-        <v>1.3659747293628499</v>
+        <v>17.9748429691486</v>
+      </c>
+      <c r="G6">
+        <v>1.097</v>
       </c>
       <c r="H6">
-        <v>71.140784310000001</v>
+        <v>71.486959999999996</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -7015,7 +5770,7 @@
         <v>5.38997690585983E-2</v>
       </c>
       <c r="F7">
-        <v>1.43477614979118</v>
+        <v>1.3659747293628499</v>
       </c>
       <c r="H7">
         <v>71.140784310000001</v>
@@ -7023,28 +5778,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>1.91936208989603</v>
+        <v>1.79712100240526</v>
       </c>
       <c r="C8">
-        <v>2.5907667999999998E-2</v>
+        <v>9.6864407E-2</v>
       </c>
       <c r="D8" t="s">
         <v>9</v>
       </c>
       <c r="E8">
-        <v>1.34980617447766E-2</v>
+        <v>5.38997690585983E-2</v>
       </c>
       <c r="F8">
-        <v>0.762817767337299</v>
-      </c>
-      <c r="G8">
-        <v>1.288</v>
+        <v>1.43477614979118</v>
       </c>
       <c r="H8">
-        <v>71.42</v>
+        <v>71.140784310000001</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -7064,7 +5816,7 @@
         <v>1.34980617447766E-2</v>
       </c>
       <c r="F9">
-        <v>0.954970513126703</v>
+        <v>0.762817767337299</v>
       </c>
       <c r="G9">
         <v>1.288</v>
@@ -7075,25 +5827,28 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>1.5364118092654899</v>
+        <v>1.91936208989603</v>
       </c>
       <c r="C10">
-        <v>0.111489093</v>
+        <v>2.5907667999999998E-2</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>7.25645899931604E-2</v>
+        <v>1.34980617447766E-2</v>
       </c>
       <c r="F10">
-        <v>3.2531836035536301</v>
+        <v>0.954970513126703</v>
       </c>
       <c r="G10">
-        <v>1.26</v>
+        <v>1.288</v>
+      </c>
+      <c r="H10">
+        <v>71.42</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -7113,7 +5868,7 @@
         <v>7.25645899931604E-2</v>
       </c>
       <c r="F11">
-        <v>2.4433323290317999</v>
+        <v>3.2531836035536301</v>
       </c>
       <c r="G11">
         <v>1.26</v>
@@ -7121,295 +5876,398 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>1.14254792657094</v>
+        <v>1.5364118092654899</v>
       </c>
       <c r="C12">
-        <v>8.1843182E-2</v>
+        <v>0.111489093</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
-        <v>7.1632165353124999E-2</v>
+        <v>7.25645899931604E-2</v>
       </c>
       <c r="F12">
-        <v>7.0432970693483599</v>
-      </c>
-      <c r="H12">
-        <v>72.604545450000003</v>
+        <v>2.4433323290317999</v>
+      </c>
+      <c r="G12">
+        <v>1.26</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13">
-        <v>1.14254792657094</v>
+        <v>1.5364118092654899</v>
       </c>
       <c r="C13">
-        <v>8.1843182E-2</v>
+        <v>0.111489093</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>7.1632165353124999E-2</v>
+        <v>7.25645899931604E-2</v>
       </c>
       <c r="F13">
-        <v>2.7839849332143101</v>
-      </c>
-      <c r="H13">
-        <v>72.604545450000003</v>
+        <v>2.43040464475121</v>
+      </c>
+      <c r="G13">
+        <v>1.26</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
-        <v>0.76948902444658396</v>
+        <v>1.14254792657094</v>
       </c>
       <c r="C14">
-        <v>0.24384</v>
+        <v>8.1843182E-2</v>
       </c>
       <c r="D14" t="s">
         <v>9</v>
       </c>
       <c r="E14">
-        <v>0.31688561142944099</v>
+        <v>7.1632165353124999E-2</v>
       </c>
       <c r="F14">
-        <v>7.6754733355837299</v>
+        <v>7.0432970693483599</v>
       </c>
       <c r="H14">
-        <v>73.478181820000003</v>
+        <v>72.604545450000003</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
       <c r="B15">
-        <v>0.74683198736593104</v>
+        <v>1.14254792657094</v>
+      </c>
+      <c r="C15">
+        <v>8.1843182E-2</v>
       </c>
       <c r="D15" t="s">
         <v>9</v>
       </c>
+      <c r="E15">
+        <v>7.1632165353124999E-2</v>
+      </c>
       <c r="F15">
-        <v>22.624195858075399</v>
+        <v>2.7839849332143101</v>
+      </c>
+      <c r="H15">
+        <v>72.604545450000003</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
       <c r="B16">
-        <v>0.634197514012805</v>
+        <v>1.14254792657094</v>
+      </c>
+      <c r="C16">
+        <v>8.1843182E-2</v>
       </c>
       <c r="D16" t="s">
         <v>9</v>
       </c>
+      <c r="E16">
+        <v>7.1632165353124999E-2</v>
+      </c>
       <c r="F16">
-        <v>16.1504080056141</v>
+        <v>2.7892918049894102</v>
+      </c>
+      <c r="H16">
+        <v>72.604545450000003</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>0.81193724612891904</v>
+        <v>0.76948902444658396</v>
       </c>
       <c r="C17">
-        <v>0.26351463400000003</v>
+        <v>0.24384</v>
       </c>
       <c r="D17" t="s">
         <v>9</v>
       </c>
       <c r="E17">
-        <v>0.32455049359585503</v>
+        <v>0.31688561142944099</v>
       </c>
       <c r="F17">
-        <v>7.76777594040046</v>
+        <v>7.6754733355837299</v>
+      </c>
+      <c r="H17">
+        <v>73.478181820000003</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
       <c r="B18">
-        <v>0.81193724612891904</v>
-      </c>
-      <c r="C18">
-        <v>0.26351463400000003</v>
+        <v>0.74683198736593104</v>
       </c>
       <c r="D18" t="s">
         <v>9</v>
       </c>
-      <c r="E18">
-        <v>0.32455049359585503</v>
-      </c>
       <c r="F18">
-        <v>11.6535292051355</v>
+        <v>22.624195858075399</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19">
-        <v>0.64229622161300404</v>
+        <v>0.74683198736593104</v>
       </c>
       <c r="D19" t="s">
         <v>9</v>
       </c>
       <c r="F19">
-        <v>32.6657378105105</v>
+        <v>22.5657731444328</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B20">
-        <v>0.64229622161300404</v>
+        <v>0.634197514012805</v>
       </c>
       <c r="D20" t="s">
         <v>9</v>
       </c>
       <c r="F20">
-        <v>51.880320990253502</v>
+        <v>16.1504080056141</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21">
-        <v>0.66551573852542301</v>
+        <v>0.81193724612891904</v>
       </c>
       <c r="C21">
-        <v>0.24384</v>
+        <v>0.26351463400000003</v>
       </c>
       <c r="D21" t="s">
         <v>9</v>
       </c>
       <c r="E21">
-        <v>0.36639253722274701</v>
+        <v>0.32455049359585503</v>
       </c>
       <c r="F21">
-        <v>8.0612152297113795</v>
+        <v>7.76777594040046</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22">
-        <v>0.66551573852542301</v>
+        <v>0.81193724612891904</v>
       </c>
       <c r="C22">
-        <v>0.24384</v>
+        <v>0.26351463400000003</v>
       </c>
       <c r="D22" t="s">
         <v>9</v>
       </c>
       <c r="E22">
-        <v>0.36639253722274701</v>
+        <v>0.32455049359585503</v>
+      </c>
+      <c r="F22">
+        <v>11.6535292051355</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>18</v>
-      </c>
       <c r="B23">
-        <v>0.66831711482098599</v>
-      </c>
-      <c r="C23">
-        <v>0.392848743</v>
+        <v>0.64229622161300404</v>
       </c>
       <c r="D23" t="s">
         <v>9</v>
       </c>
-      <c r="E23">
-        <v>0.587817870121772</v>
-      </c>
       <c r="F23">
-        <v>23.531152831216499</v>
-      </c>
-      <c r="G23">
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="H23">
-        <v>71.94</v>
+        <v>32.6657378105105</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
       <c r="B24">
-        <v>0.66831711482098599</v>
-      </c>
-      <c r="C24">
-        <v>0.392848743</v>
+        <v>0.64229622161300404</v>
       </c>
       <c r="D24" t="s">
         <v>9</v>
       </c>
-      <c r="E24">
-        <v>0.587817870121772</v>
-      </c>
       <c r="F24">
-        <v>18.703245444769301</v>
-      </c>
-      <c r="G24">
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="H24">
-        <v>71.94</v>
+        <v>51.880320990253502</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B25">
-        <v>0.65580679181917101</v>
+        <v>0.66551573852542301</v>
       </c>
       <c r="C25">
-        <v>0.392848743</v>
+        <v>0.24384</v>
       </c>
       <c r="D25" t="s">
         <v>9</v>
       </c>
       <c r="E25">
-        <v>0.59903122062865499</v>
+        <v>0.36639253722274701</v>
       </c>
       <c r="F25">
-        <v>15.9745813671168</v>
-      </c>
-      <c r="G25">
-        <v>1.42</v>
-      </c>
-      <c r="H25">
-        <v>71.942899999999995</v>
+        <v>8.0612152297113795</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B26">
-        <v>0.65580679181917101</v>
+        <v>0.66551573852542301</v>
       </c>
       <c r="C26">
-        <v>0.392848743</v>
+        <v>0.24384</v>
       </c>
       <c r="D26" t="s">
         <v>9</v>
       </c>
       <c r="E26">
+        <v>0.36639253722274701</v>
+      </c>
+      <c r="F26">
+        <v>7.8631523559558696</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27">
+        <v>0.66551573852542301</v>
+      </c>
+      <c r="C27">
+        <v>0.24384</v>
+      </c>
+      <c r="D27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27">
+        <v>0.36639253722274701</v>
+      </c>
+      <c r="F27">
+        <v>30.1775506886923</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>0.66831711482098599</v>
+      </c>
+      <c r="C28">
+        <v>0.392848743</v>
+      </c>
+      <c r="D28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28">
+        <v>0.587817870121772</v>
+      </c>
+      <c r="F28">
+        <v>23.531152831216499</v>
+      </c>
+      <c r="G28">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="H28">
+        <v>71.94</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B29">
+        <v>0.66831711482098599</v>
+      </c>
+      <c r="C29">
+        <v>0.392848743</v>
+      </c>
+      <c r="D29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>0.587817870121772</v>
+      </c>
+      <c r="F29">
+        <v>18.703245444769301</v>
+      </c>
+      <c r="G29">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="H29">
+        <v>71.94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>19</v>
+      </c>
+      <c r="B30">
+        <v>0.65580679181917101</v>
+      </c>
+      <c r="C30">
+        <v>0.392848743</v>
+      </c>
+      <c r="D30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30">
         <v>0.59903122062865499</v>
       </c>
-      <c r="F26">
+      <c r="F30">
+        <v>15.9745813671168</v>
+      </c>
+      <c r="G30">
+        <v>1.42</v>
+      </c>
+      <c r="H30">
+        <v>71.942899999999995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31">
+        <v>0.65580679181917101</v>
+      </c>
+      <c r="C31">
+        <v>0.392848743</v>
+      </c>
+      <c r="D31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E31">
+        <v>0.59903122062865499</v>
+      </c>
+      <c r="F31">
         <v>17.496680423021001</v>
       </c>
-      <c r="G26">
+      <c r="G31">
         <v>1.42</v>
       </c>
-      <c r="H26">
+      <c r="H31">
         <v>71.942899999999995</v>
       </c>
     </row>
@@ -7422,7 +6280,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7467,6 +6325,9 @@
       <c r="E2">
         <v>0.27419154708066701</v>
       </c>
+      <c r="F2">
+        <v>8.0617713895940106</v>
+      </c>
       <c r="G2">
         <v>6.25</v>
       </c>
@@ -7491,7 +6352,7 @@
         <v>0.27419154708066701</v>
       </c>
       <c r="F3">
-        <v>20.759702379649699</v>
+        <v>8.0092423263314494</v>
       </c>
       <c r="G3">
         <v>6.25</v>
@@ -7502,28 +6363,28 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>0.49838619196324002</v>
+        <v>0.500234239386116</v>
       </c>
       <c r="C4">
-        <v>0.195072</v>
+        <v>0.13716</v>
       </c>
       <c r="D4" t="s">
         <v>20</v>
       </c>
       <c r="E4">
-        <v>0.39140731253322603</v>
+        <v>0.27419154708066701</v>
       </c>
       <c r="F4">
-        <v>11.7604829329048</v>
+        <v>20.759702379649699</v>
       </c>
       <c r="G4">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="H4">
-        <v>73.188749999999999</v>
+        <v>72.545299999999997</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -7543,7 +6404,7 @@
         <v>0.39140731253322603</v>
       </c>
       <c r="F5">
-        <v>11.63069034185</v>
+        <v>11.7604829329048</v>
       </c>
       <c r="G5">
         <v>4.8</v>
@@ -7554,22 +6415,28 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>0.496481994488156</v>
+        <v>0.49838619196324002</v>
       </c>
       <c r="C6">
-        <v>0.18592800000000001</v>
+        <v>0.195072</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
       <c r="E6">
-        <v>0.37449092225727298</v>
+        <v>0.39140731253322603</v>
       </c>
       <c r="F6">
-        <v>16.082464877533099</v>
+        <v>11.63069034185</v>
+      </c>
+      <c r="G6">
+        <v>4.8</v>
+      </c>
+      <c r="H6">
+        <v>73.188749999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -7589,27 +6456,27 @@
         <v>0.37449092225727298</v>
       </c>
       <c r="F7">
-        <v>19.278549967453198</v>
+        <v>16.082464877533099</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>0.49364073113116103</v>
+        <v>0.496481994488156</v>
       </c>
       <c r="C8">
-        <v>0.176784</v>
+        <v>0.18592800000000001</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
       <c r="E8">
-        <v>0.35812279832522198</v>
+        <v>0.37449092225727298</v>
       </c>
       <c r="F8">
-        <v>18.3266040851639</v>
+        <v>19.278549967453198</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -7629,243 +6496,389 @@
         <v>0.35812279832522198</v>
       </c>
       <c r="F9">
-        <v>15.8324828082942</v>
+        <v>18.3266040851639</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B10">
-        <v>0.48014251849385198</v>
+        <v>0.49364073113116103</v>
       </c>
       <c r="C10">
-        <v>0.20116800000000001</v>
+        <v>0.176784</v>
       </c>
       <c r="D10" t="s">
         <v>20</v>
       </c>
       <c r="E10">
-        <v>0.418975600475957</v>
+        <v>0.35812279832522198</v>
       </c>
       <c r="F10">
-        <v>12.5427239203201</v>
-      </c>
-      <c r="G10">
-        <v>5.58</v>
-      </c>
-      <c r="H10">
-        <v>73.188749999999999</v>
+        <v>18.238219059268399</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>0.48014251849385198</v>
+        <v>0.49364073113116103</v>
       </c>
       <c r="C11">
-        <v>0.20116800000000001</v>
+        <v>0.176784</v>
       </c>
       <c r="D11" t="s">
         <v>20</v>
       </c>
       <c r="E11">
-        <v>0.418975600475957</v>
+        <v>0.35812279832522198</v>
       </c>
       <c r="F11">
-        <v>10.123963721124101</v>
-      </c>
-      <c r="G11">
-        <v>5.58</v>
-      </c>
-      <c r="H11">
-        <v>73.188749999999999</v>
+        <v>15.8324828082942</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12">
-        <v>0.48738009477924898</v>
+        <v>0.48014251849385198</v>
       </c>
       <c r="C12">
-        <v>0.20319999999999999</v>
+        <v>0.20116800000000001</v>
       </c>
       <c r="D12" t="s">
         <v>20</v>
       </c>
       <c r="E12">
-        <v>0.41692305897727699</v>
+        <v>0.418975600475957</v>
       </c>
       <c r="F12">
-        <v>15.491084387970799</v>
+        <v>12.5427239203201</v>
       </c>
       <c r="G12">
-        <v>4.6849999999999996</v>
+        <v>5.58</v>
       </c>
       <c r="H12">
-        <v>72.484999999999999</v>
+        <v>73.188749999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B13">
-        <v>0.46633139234925403</v>
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="C13">
+        <v>0.20116800000000001</v>
       </c>
       <c r="D13" t="s">
         <v>20</v>
       </c>
       <c r="E13">
-        <v>0.21787081390374799</v>
+        <v>0.418975600475957</v>
       </c>
       <c r="F13">
-        <v>28.8790872259084</v>
+        <v>10.123963721124101</v>
+      </c>
+      <c r="G13">
+        <v>5.58</v>
+      </c>
+      <c r="H13">
+        <v>73.188749999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B14">
-        <v>0.44959398748926399</v>
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="C14">
+        <v>0.20116800000000001</v>
       </c>
       <c r="D14" t="s">
         <v>20</v>
       </c>
       <c r="E14">
-        <v>0.31185470424768102</v>
+        <v>0.418975600475957</v>
       </c>
       <c r="F14">
-        <v>31.877696149374302</v>
+        <v>9.9882836327260591</v>
+      </c>
+      <c r="G14">
+        <v>5.58</v>
+      </c>
+      <c r="H14">
+        <v>73.188749999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>0.42847041975631001</v>
+        <v>0.48738009477924898</v>
       </c>
       <c r="C15">
-        <v>0.17526</v>
+        <v>0.20319999999999999</v>
       </c>
       <c r="D15" t="s">
         <v>20</v>
       </c>
       <c r="E15">
-        <v>0.40903640465934199</v>
+        <v>0.41692305897727699</v>
+      </c>
+      <c r="F15">
+        <v>15.491084387970799</v>
       </c>
       <c r="G15">
         <v>4.6849999999999996</v>
       </c>
+      <c r="H15">
+        <v>72.484999999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
       <c r="B16">
-        <v>0.40867897602588799</v>
+        <v>0.48738009477924898</v>
+      </c>
+      <c r="C16">
+        <v>0.20319999999999999</v>
       </c>
       <c r="D16" t="s">
         <v>20</v>
       </c>
+      <c r="E16">
+        <v>0.41692305897727699</v>
+      </c>
       <c r="F16">
-        <v>19.545410722183501</v>
+        <v>15.422189134531401</v>
+      </c>
+      <c r="G16">
+        <v>4.6849999999999996</v>
+      </c>
+      <c r="H16">
+        <v>72.484999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
       <c r="B17">
-        <v>0.41829191635495</v>
+        <v>0.46633139234925403</v>
       </c>
       <c r="D17" t="s">
         <v>20</v>
       </c>
+      <c r="E17">
+        <v>0.21787081390374799</v>
+      </c>
       <c r="F17">
-        <v>21.2301041068087</v>
+        <v>28.8790872259084</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B18">
-        <v>0.57001899623787999</v>
-      </c>
-      <c r="C18">
-        <v>9.0498811999999998E-2</v>
+        <v>0.44959398748926399</v>
       </c>
       <c r="D18" t="s">
         <v>20</v>
       </c>
       <c r="E18">
-        <v>0.15876455451009799</v>
-      </c>
-      <c r="G18">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="H18">
-        <v>72.918940000000006</v>
+        <v>0.31185470424768102</v>
+      </c>
+      <c r="F18">
+        <v>31.877696149374302</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19">
-        <v>0.55068895347565805</v>
+        <v>0.42847041975631001</v>
       </c>
       <c r="C19">
-        <v>0.132051846</v>
+        <v>0.17526</v>
       </c>
       <c r="D19" t="s">
         <v>20</v>
       </c>
       <c r="E19">
-        <v>0.239793889393565</v>
+        <v>0.40903640465934199</v>
       </c>
       <c r="F19">
-        <v>44.743071696612503</v>
+        <v>32.379700829916601</v>
+      </c>
+      <c r="G19">
+        <v>4.6849999999999996</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20">
-        <v>0.52913409322569804</v>
+        <v>0.42847041975631001</v>
       </c>
       <c r="C20">
-        <v>0.16555581</v>
+        <v>0.17526</v>
       </c>
       <c r="D20" t="s">
         <v>20</v>
       </c>
       <c r="E20">
-        <v>0.31288063294266599</v>
+        <v>0.40903640465934199</v>
       </c>
       <c r="F20">
-        <v>17.612268500013801</v>
+        <v>32.274144438345303</v>
+      </c>
+      <c r="G20">
+        <v>4.6849999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>24</v>
-      </c>
       <c r="B21">
-        <v>0.51433262189204798</v>
-      </c>
-      <c r="C21">
-        <v>0.15135790499999999</v>
+        <v>0.40867897602588799</v>
       </c>
       <c r="D21" t="s">
         <v>20</v>
       </c>
-      <c r="E21">
+      <c r="F21">
+        <v>19.545410722183501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>0.40867897602588799</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22">
+        <v>19.3542063534147</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>0.41829191635495</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23">
+        <v>21.2301041068087</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>0.57001899623787999</v>
+      </c>
+      <c r="C24">
+        <v>9.0498811999999998E-2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24">
+        <v>0.15876455451009799</v>
+      </c>
+      <c r="F24">
+        <v>-2.7729314633187902E-3</v>
+      </c>
+      <c r="G24">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="H24">
+        <v>72.918940000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="C25">
+        <v>0.132051846</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25">
+        <v>0.239793889393565</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="C26">
+        <v>0.132051846</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26">
+        <v>0.239793889393565</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27">
+        <v>0.52913409322569804</v>
+      </c>
+      <c r="C27">
+        <v>0.16555581</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27">
+        <v>0.31288063294266599</v>
+      </c>
+      <c r="F27">
+        <v>17.612268500013801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28">
+        <v>0.51433262189204798</v>
+      </c>
+      <c r="C28">
+        <v>0.15135790499999999</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28">
         <v>0.29428019642854403</v>
       </c>
-      <c r="F21">
+      <c r="F28">
         <v>10.116682809798901</v>
       </c>
     </row>
@@ -7878,7 +6891,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7929,404 +6942,265 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>0.84629581545158405</v>
+        <v>0.89039772710795695</v>
       </c>
       <c r="C3">
-        <v>0.38927203100000002</v>
+        <v>0.24384</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>0.45997158900317198</v>
+        <v>0.27385514649953202</v>
       </c>
       <c r="F3">
-        <v>7.8958984290259</v>
+        <v>6.2631698085533101</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>0.89039772710795695</v>
+        <v>1.2795322417230099</v>
       </c>
       <c r="C4">
-        <v>0.24384</v>
+        <v>0.27730699199999997</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>0.27385514649953202</v>
+        <v>0.21672528675524499</v>
       </c>
       <c r="F4">
-        <v>6.2631698085533101</v>
+        <v>4.17908012369488</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>0.89039772710795695</v>
+        <v>1.93587245637372</v>
       </c>
       <c r="C5">
-        <v>0.24384</v>
+        <v>0.152032679</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0.27385514649953202</v>
+        <v>7.8534450190374402E-2</v>
       </c>
       <c r="F5">
-        <v>6.2631698085533101</v>
+        <v>9.2886180882038705</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>1.2795322417230099</v>
+        <v>2.4780665467373599</v>
       </c>
       <c r="C6">
-        <v>0.27730699199999997</v>
+        <v>9.9617103999999998E-2</v>
       </c>
       <c r="D6" t="s">
         <v>3</v>
       </c>
       <c r="E6">
-        <v>0.21672528675524499</v>
+        <v>4.0199527382005301E-2</v>
       </c>
       <c r="F6">
-        <v>4.17908012369488</v>
+        <v>1.91650182628218</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>1.2795322417230099</v>
+        <v>1.77503019033284</v>
       </c>
       <c r="C7">
-        <v>0.27730699199999997</v>
+        <v>0.20904352600000001</v>
       </c>
       <c r="D7" t="s">
         <v>3</v>
       </c>
       <c r="E7">
-        <v>0.21672528675524499</v>
+        <v>0.117768997473109</v>
       </c>
       <c r="F7">
-        <v>4.17908012369488</v>
+        <v>4.44794425583971</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8">
-        <v>1.93587245637372</v>
+        <v>1.7075802077995601</v>
       </c>
       <c r="C8">
-        <v>0.152032679</v>
+        <v>0.14364185700000001</v>
       </c>
       <c r="D8" t="s">
         <v>3</v>
       </c>
       <c r="E8">
-        <v>7.8534450190374402E-2</v>
+        <v>8.4120122934137995E-2</v>
       </c>
       <c r="F8">
-        <v>9.2886180882038705</v>
+        <v>8.1938063501887299</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9">
-        <v>1.93587245637372</v>
+        <v>1.4922591097125699</v>
       </c>
       <c r="C9">
-        <v>0.152032679</v>
+        <v>0.217546613</v>
       </c>
       <c r="D9" t="s">
         <v>3</v>
       </c>
       <c r="E9">
-        <v>7.8534450190374402E-2</v>
+        <v>0.14578340422522401</v>
       </c>
       <c r="F9">
-        <v>9.2886180882038705</v>
+        <v>11.981817018407201</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10">
-        <v>2.4780665467373599</v>
+        <v>1.4922591097125699</v>
       </c>
       <c r="C10">
-        <v>9.9617103999999998E-2</v>
+        <v>0.217546613</v>
       </c>
       <c r="D10" t="s">
         <v>3</v>
       </c>
       <c r="E10">
-        <v>4.0199527382005301E-2</v>
+        <v>0.14578340422522401</v>
       </c>
       <c r="F10">
-        <v>1.91650182628218</v>
+        <v>11.9908106789727</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B11">
-        <v>2.4780665467373599</v>
+        <v>1.11609574558469</v>
       </c>
       <c r="C11">
-        <v>9.9617103999999998E-2</v>
+        <v>0.29169342100000001</v>
       </c>
       <c r="D11" t="s">
         <v>3</v>
       </c>
       <c r="E11">
-        <v>4.0199527382005301E-2</v>
+        <v>0.26135161087563402</v>
       </c>
       <c r="F11">
-        <v>1.91650182628218</v>
+        <v>8.5316662064735205</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
       <c r="B12">
-        <v>1.77503019033284</v>
-      </c>
-      <c r="C12">
-        <v>0.20904352600000001</v>
+        <v>1.00713808149247</v>
       </c>
       <c r="D12" t="s">
         <v>3</v>
       </c>
-      <c r="E12">
-        <v>0.117768997473109</v>
-      </c>
       <c r="F12">
-        <v>4.44794425583971</v>
+        <v>9.3052048733349402</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13">
-        <v>1.7075802077995601</v>
+        <v>0.99935539120017003</v>
       </c>
       <c r="C13">
-        <v>0.14364185700000001</v>
+        <v>0.245749827</v>
       </c>
       <c r="D13" t="s">
         <v>3</v>
       </c>
       <c r="E13">
-        <v>8.4120122934137995E-2</v>
+        <v>0.24590834168099901</v>
       </c>
       <c r="F13">
-        <v>8.1938063501887299</v>
+        <v>16.0453723843845</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B14">
-        <v>1.4922591097125699</v>
+        <v>0.94487655915406399</v>
       </c>
       <c r="C14">
-        <v>0.217546613</v>
+        <v>0.31575888699999999</v>
       </c>
       <c r="D14" t="s">
         <v>3</v>
       </c>
       <c r="E14">
-        <v>0.14578340422522401</v>
+        <v>0.33418004070573498</v>
       </c>
       <c r="F14">
-        <v>11.981817018407201</v>
+        <v>7.0638592430665703</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B15">
-        <v>1.11609574558469</v>
+        <v>0.87483234652335495</v>
       </c>
       <c r="C15">
-        <v>0.29169342100000001</v>
+        <v>0.27092143800000001</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
       </c>
       <c r="E15">
-        <v>0.26135161087563402</v>
+        <v>0.30968383722511</v>
       </c>
       <c r="F15">
-        <v>8.5316662064735205</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B16">
-        <v>1.00713808149247</v>
-      </c>
-      <c r="D16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16">
-        <v>9.3052048733349402</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17">
-        <v>0.99935539120017003</v>
-      </c>
-      <c r="C17">
-        <v>0.245749827</v>
-      </c>
-      <c r="D17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17">
-        <v>0.24590834168099901</v>
-      </c>
-      <c r="F17">
-        <v>16.0453723843845</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>0.99935539120017003</v>
-      </c>
-      <c r="C18">
-        <v>0.245749827</v>
-      </c>
-      <c r="D18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18">
-        <v>0.24590834168099901</v>
-      </c>
-      <c r="F18">
-        <v>16.0453723843845</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>0.94487655915406399</v>
-      </c>
-      <c r="C19">
-        <v>0.31575888699999999</v>
-      </c>
-      <c r="D19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19">
-        <v>0.33418004070573498</v>
-      </c>
-      <c r="F19">
-        <v>7.0638592430665703</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20">
-        <v>0.94487655915406399</v>
-      </c>
-      <c r="C20">
-        <v>0.31575888699999999</v>
-      </c>
-      <c r="D20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20">
-        <v>0.33418004070573498</v>
-      </c>
-      <c r="F20">
-        <v>7.0638592430665703</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21">
-        <v>0.87483234652335495</v>
-      </c>
-      <c r="C21">
-        <v>0.27092143800000001</v>
-      </c>
-      <c r="D21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21">
-        <v>0.30968383722511</v>
-      </c>
-      <c r="F21">
-        <v>8.2264856374067996</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22">
-        <v>0.87483234652335495</v>
-      </c>
-      <c r="C22">
-        <v>0.27092143800000001</v>
-      </c>
-      <c r="D22" t="s">
-        <v>3</v>
-      </c>
-      <c r="E22">
-        <v>0.30968383722511</v>
-      </c>
-      <c r="F22">
         <v>8.2264856374067996</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -8398,7 +7272,7 @@
         <v>0.359138403178066</v>
       </c>
       <c r="F3">
-        <v>24.690084932127998</v>
+        <v>23.148382126467901</v>
       </c>
       <c r="G3">
         <v>1.76</v>
@@ -8435,569 +7309,317 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5">
-        <v>0.14842325926962999</v>
-      </c>
-      <c r="C5">
-        <v>0.103632</v>
+        <v>0.13941805406320101</v>
       </c>
       <c r="D5" t="s">
         <v>26</v>
       </c>
       <c r="E5">
-        <v>0.69821940651323</v>
+        <v>0.71729509260447999</v>
       </c>
       <c r="F5">
-        <v>118.259222088889</v>
-      </c>
-      <c r="G5">
-        <v>1.83</v>
-      </c>
-      <c r="H5">
-        <v>73.290000000000006</v>
+        <v>50.954752325421801</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>0.13941805406320101</v>
+        <v>0.35708644464821998</v>
       </c>
       <c r="C6">
-        <v>0.100003886</v>
+        <v>6.8341643999999993E-2</v>
       </c>
       <c r="D6" t="s">
         <v>26</v>
       </c>
       <c r="E6">
-        <v>0.71729509260447999</v>
+        <v>0.19138683370444401</v>
       </c>
       <c r="F6">
-        <v>50.954752325421801</v>
+        <v>9.73092604234097</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>0.13941805406320101</v>
+        <v>0.35708644464821998</v>
       </c>
       <c r="C7">
-        <v>0.100003886</v>
+        <v>6.8341643999999993E-2</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7">
-        <v>0.71729509260447999</v>
+        <v>0.19138683370444401</v>
       </c>
       <c r="F7">
-        <v>50.954752325421801</v>
+        <v>9.5554623120508193</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8">
-        <v>0.35708644464821998</v>
+        <v>0.97908907233996301</v>
       </c>
       <c r="C8">
-        <v>6.8341643999999993E-2</v>
+        <v>7.7164556999999995E-2</v>
       </c>
       <c r="D8" t="s">
         <v>26</v>
       </c>
       <c r="E8">
-        <v>0.19138683370444401</v>
+        <v>7.8812601610986702E-2</v>
       </c>
       <c r="F8">
-        <v>9.73092604234097</v>
+        <v>12.1601192837523</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9">
-        <v>0.35708644464821998</v>
+        <v>0.73912910715284497</v>
       </c>
       <c r="C9">
-        <v>6.8341643999999993E-2</v>
+        <v>5.9129280999999999E-2</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9">
-        <v>0.19138683370444401</v>
+        <v>7.9998582693852197E-2</v>
       </c>
       <c r="F9">
-        <v>9.73092604234097</v>
+        <v>7.9516472320781002</v>
+      </c>
+      <c r="G9">
+        <v>1.93</v>
+      </c>
+      <c r="H9">
+        <v>74.42</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10">
-        <v>0.97908907233996301</v>
+        <v>0.50655758454314603</v>
       </c>
       <c r="C10">
-        <v>7.7164556999999995E-2</v>
+        <v>0.12576395200000001</v>
       </c>
       <c r="D10" t="s">
         <v>26</v>
       </c>
       <c r="E10">
-        <v>7.8812601610986702E-2</v>
+        <v>0.24827177765667799</v>
       </c>
       <c r="F10">
-        <v>12.1601192837523</v>
+        <v>30.7702058957052</v>
+      </c>
+      <c r="G10">
+        <v>1.53</v>
+      </c>
+      <c r="H10">
+        <v>71.739999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B11">
-        <v>0.97908907233996301</v>
+        <v>0.26422745354100802</v>
       </c>
       <c r="C11">
-        <v>7.7164556999999995E-2</v>
+        <v>9.0472021999999999E-2</v>
       </c>
       <c r="D11" t="s">
         <v>26</v>
       </c>
       <c r="E11">
-        <v>7.8812601610986702E-2</v>
+        <v>0.34240205091314901</v>
       </c>
       <c r="F11">
-        <v>12.1601192837523</v>
+        <v>34.983383524448797</v>
+      </c>
+      <c r="G11">
+        <v>1.704</v>
+      </c>
+      <c r="H11">
+        <v>73.278000000000006</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12">
-        <v>0.73912910715284497</v>
+        <v>0.20547930573848</v>
       </c>
       <c r="C12">
-        <v>5.9129280999999999E-2</v>
+        <v>0.10404495</v>
       </c>
       <c r="D12" t="s">
         <v>26</v>
       </c>
       <c r="E12">
-        <v>7.9998582693852197E-2</v>
+        <v>0.50635245055977096</v>
       </c>
       <c r="F12">
-        <v>7.9516472320781002</v>
-      </c>
-      <c r="G12">
-        <v>1.93</v>
+        <v>53.152789367811998</v>
       </c>
       <c r="H12">
-        <v>74.42</v>
+        <v>72.669256200000007</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B13">
-        <v>0.73912910715284497</v>
-      </c>
-      <c r="C13">
-        <v>5.9129280999999999E-2</v>
+        <v>0.168078940883987</v>
       </c>
       <c r="D13" t="s">
         <v>26</v>
       </c>
       <c r="E13">
-        <v>7.9998582693852197E-2</v>
+        <v>0.32164483971442398</v>
       </c>
       <c r="F13">
-        <v>7.9516472320781002</v>
-      </c>
-      <c r="G13">
-        <v>1.93</v>
-      </c>
-      <c r="H13">
-        <v>74.42</v>
+        <v>33.341043343649702</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B14">
-        <v>0.50655758454314603</v>
+        <v>0.25776243935158599</v>
       </c>
       <c r="C14">
-        <v>0.12576395200000001</v>
+        <v>0.142205108</v>
       </c>
       <c r="D14" t="s">
         <v>26</v>
       </c>
       <c r="E14">
-        <v>0.24827177765667799</v>
+        <v>0.55169057352857198</v>
       </c>
       <c r="F14">
-        <v>30.7702058957052</v>
+        <v>31.9180285667398</v>
       </c>
       <c r="G14">
-        <v>1.53</v>
+        <v>1.628292683</v>
       </c>
       <c r="H14">
-        <v>71.739999999999995</v>
+        <v>73.679374999999993</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>32</v>
-      </c>
       <c r="B15">
-        <v>0.50655758454314603</v>
-      </c>
-      <c r="C15">
-        <v>0.12576395200000001</v>
+        <v>0.30718976746298698</v>
       </c>
       <c r="D15" t="s">
         <v>26</v>
       </c>
-      <c r="E15">
-        <v>0.24827177765667799</v>
-      </c>
       <c r="F15">
-        <v>30.7702058957052</v>
-      </c>
-      <c r="G15">
-        <v>1.53</v>
-      </c>
-      <c r="H15">
-        <v>71.739999999999995</v>
+        <v>15.8650769934215</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B16">
-        <v>0.26422745354100802</v>
+        <v>0.24912069961521999</v>
       </c>
       <c r="C16">
-        <v>9.0472021999999999E-2</v>
+        <v>0.11911748799999999</v>
       </c>
       <c r="D16" t="s">
         <v>26</v>
       </c>
       <c r="E16">
-        <v>0.34240205091314901</v>
+        <v>0.47815170792303902</v>
       </c>
       <c r="F16">
-        <v>34.983383524448797</v>
+        <v>26.1959995510725</v>
       </c>
       <c r="G16">
-        <v>1.704</v>
+        <v>1.78</v>
       </c>
       <c r="H16">
-        <v>73.278000000000006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>73.430000000000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B17">
-        <v>0.26422745354100802</v>
-      </c>
-      <c r="C17">
-        <v>9.0472021999999999E-2</v>
+        <v>0.23799883780685399</v>
       </c>
       <c r="D17" t="s">
         <v>26</v>
       </c>
       <c r="E17">
-        <v>0.34240205091314901</v>
+        <v>0.97021100240578795</v>
       </c>
       <c r="F17">
-        <v>34.983383524448797</v>
-      </c>
-      <c r="G17">
-        <v>1.704</v>
-      </c>
-      <c r="H17">
-        <v>73.278000000000006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>94.218748150536896</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B18">
-        <v>0.20547930573848</v>
+        <v>0.26752308407063402</v>
       </c>
       <c r="C18">
-        <v>0.10404495</v>
+        <v>0.23330000000000001</v>
       </c>
       <c r="D18" t="s">
         <v>26</v>
       </c>
       <c r="E18">
-        <v>0.50635245055977096</v>
+        <v>0.87207427654505298</v>
       </c>
       <c r="F18">
-        <v>53.152789367811998</v>
-      </c>
-      <c r="H18">
-        <v>72.669256200000007</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>115.910838296351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B19">
-        <v>0.20547930573848</v>
+        <v>0.16056832408994501</v>
       </c>
       <c r="C19">
-        <v>0.10404495</v>
+        <v>0.23330000000000001</v>
       </c>
       <c r="D19" t="s">
         <v>26</v>
       </c>
       <c r="E19">
-        <v>0.50635245055977096</v>
+        <v>1.45296403460818</v>
       </c>
       <c r="F19">
-        <v>53.152789367811998</v>
-      </c>
-      <c r="H19">
-        <v>72.669256200000007</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20">
-        <v>0.168078940883987</v>
-      </c>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20">
-        <v>0.32164483971442398</v>
-      </c>
-      <c r="F20">
-        <v>33.341043343649702</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21">
-        <v>0.168078940883987</v>
-      </c>
-      <c r="D21" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21">
-        <v>0.32164483971442398</v>
-      </c>
-      <c r="F21">
-        <v>33.341043343649702</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
-      </c>
-      <c r="B22">
-        <v>0.25776243935158599</v>
-      </c>
-      <c r="C22">
-        <v>0.142205108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22">
-        <v>0.55169057352857198</v>
-      </c>
-      <c r="F22">
-        <v>31.9180285667398</v>
-      </c>
-      <c r="G22">
-        <v>1.628292683</v>
-      </c>
-      <c r="H22">
-        <v>73.679374999999993</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>0.30718976746298698</v>
-      </c>
-      <c r="D23" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23">
-        <v>15.8650769934215</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24">
-        <v>0.24912069961521999</v>
-      </c>
-      <c r="C24">
-        <v>0.11911748799999999</v>
-      </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24">
-        <v>0.47815170792303902</v>
-      </c>
-      <c r="F24">
-        <v>26.1959995510725</v>
-      </c>
-      <c r="G24">
-        <v>1.78</v>
-      </c>
-      <c r="H24">
-        <v>73.430000000000007</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25">
-        <v>0.24912069961521999</v>
-      </c>
-      <c r="C25">
-        <v>0.11911748799999999</v>
-      </c>
-      <c r="D25" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25">
-        <v>0.47815170792303902</v>
-      </c>
-      <c r="F25">
-        <v>26.1959995510725</v>
-      </c>
-      <c r="G25">
-        <v>1.78</v>
-      </c>
-      <c r="H25">
-        <v>73.430000000000007</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B26">
-        <v>0.23799883780685399</v>
-      </c>
-      <c r="D26" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26">
-        <v>0.97021100240578795</v>
-      </c>
-      <c r="F26">
-        <v>94.218748150536896</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27">
-        <v>0.23799883780685399</v>
-      </c>
-      <c r="D27" t="s">
-        <v>26</v>
-      </c>
-      <c r="E27">
-        <v>0.97021100240578795</v>
-      </c>
-      <c r="F27">
-        <v>94.218748150536896</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B28">
-        <v>0.26752308407063402</v>
-      </c>
-      <c r="D28" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28">
-        <v>0.87207427654505298</v>
-      </c>
-      <c r="F28">
-        <v>115.910838296351</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29">
-        <v>0.26752308407063402</v>
-      </c>
-      <c r="D29" t="s">
-        <v>26</v>
-      </c>
-      <c r="E29">
-        <v>0.87207427654505298</v>
-      </c>
-      <c r="F29">
-        <v>115.910838296351</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30">
-        <v>0.16056832408994501</v>
-      </c>
-      <c r="D30" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30">
-        <v>1.45296403460818</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31">
-        <v>0.16056832408994501</v>
-      </c>
-      <c r="D31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31">
-        <v>1.45296403460818</v>
+        <v>42.614245239660903</v>
       </c>
     </row>
   </sheetData>
@@ -9009,7 +7631,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9075,27 +7697,27 @@
         <v>0.157013194707318</v>
       </c>
       <c r="F3">
-        <v>4.8225004830932496</v>
+        <v>11.673900030623701</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4">
-        <v>0.87528110109794</v>
+        <v>0.74411257103448103</v>
       </c>
       <c r="C4">
-        <v>8.9573877999999996E-2</v>
+        <v>0.116835492</v>
       </c>
       <c r="D4" t="s">
         <v>41</v>
       </c>
       <c r="E4">
-        <v>0.10233726957847</v>
+        <v>0.157013194707318</v>
       </c>
       <c r="F4">
-        <v>2.0901187683293201</v>
+        <v>4.8225004830932496</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -9115,1376 +7737,274 @@
         <v>0.10233726957847</v>
       </c>
       <c r="F5">
-        <v>3.4348545944842801</v>
+        <v>2.0901187683293201</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6">
-        <v>1.62598028208757</v>
+        <v>0.87528110109794</v>
       </c>
       <c r="C6">
-        <v>4.0360477999999998E-2</v>
+        <v>8.9573877999999996E-2</v>
       </c>
       <c r="D6" t="s">
         <v>41</v>
       </c>
       <c r="E6">
-        <v>2.48222431997649E-2</v>
+        <v>0.10233726957847</v>
       </c>
       <c r="F6">
-        <v>11.4435970636991</v>
+        <v>2.0802072636448998</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7">
-        <v>1.62598028208757</v>
+        <v>0.87528110109794</v>
       </c>
       <c r="C7">
-        <v>4.0360477999999998E-2</v>
+        <v>8.9573877999999996E-2</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
       </c>
       <c r="E7">
-        <v>2.48222431997649E-2</v>
+        <v>0.10233726957847</v>
       </c>
       <c r="F7">
-        <v>5.2429283117314203</v>
+        <v>3.4348545944842801</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8">
-        <v>1.32277923770115</v>
+        <v>1.62598028208757</v>
       </c>
       <c r="C8">
-        <v>3.2272940999999999E-2</v>
+        <v>4.0360477999999998E-2</v>
       </c>
       <c r="D8" t="s">
         <v>41</v>
       </c>
       <c r="E8">
-        <v>2.4397828511496002E-2</v>
+        <v>2.48222431997649E-2</v>
       </c>
       <c r="F8">
-        <v>8.1503583923791698</v>
+        <v>11.4435970636991</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9">
-        <v>1.32277923770115</v>
+        <v>1.62598028208757</v>
       </c>
       <c r="C9">
-        <v>3.2272940999999999E-2</v>
+        <v>4.0360477999999998E-2</v>
       </c>
       <c r="D9" t="s">
         <v>41</v>
       </c>
       <c r="E9">
-        <v>2.4397828511496002E-2</v>
+        <v>2.48222431997649E-2</v>
       </c>
       <c r="F9">
-        <v>22.095712310493202</v>
+        <v>5.2429283117314203</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10">
-        <v>1.0535668624027901</v>
+        <v>1.32277923770115</v>
       </c>
       <c r="C10">
-        <v>5.4257143000000001E-2</v>
+        <v>3.2272940999999999E-2</v>
       </c>
       <c r="D10" t="s">
         <v>41</v>
       </c>
       <c r="E10">
-        <v>5.1498528414475699E-2</v>
+        <v>2.4397828511496002E-2</v>
       </c>
       <c r="F10">
-        <v>5.8251150947610704</v>
+        <v>8.1503583923791698</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
       <c r="B11">
-        <v>0.78894922945176305</v>
+        <v>1.32277923770115</v>
+      </c>
+      <c r="C11">
+        <v>3.2272940999999999E-2</v>
       </c>
       <c r="D11" t="s">
         <v>41</v>
       </c>
+      <c r="E11">
+        <v>2.4397828511496002E-2</v>
+      </c>
       <c r="F11">
-        <v>6.4381260228580199</v>
+        <v>22.095712310493202</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12">
-        <v>0.73759563320647703</v>
+        <v>1.0535668624027901</v>
       </c>
       <c r="C12">
-        <v>0.137964795</v>
+        <v>5.4257143000000001E-2</v>
       </c>
       <c r="D12" t="s">
         <v>41</v>
       </c>
       <c r="E12">
-        <v>0.18704665373388801</v>
+        <v>5.1498528414475699E-2</v>
       </c>
       <c r="F12">
-        <v>5.5662125718823496</v>
+        <v>5.8251150947610704</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>35</v>
-      </c>
       <c r="B13">
-        <v>0.73062868871751996</v>
-      </c>
-      <c r="C13">
-        <v>0.14825882000000001</v>
+        <v>0.78894922945176305</v>
       </c>
       <c r="D13" t="s">
         <v>41</v>
       </c>
-      <c r="E13">
-        <v>0.202919516150181</v>
-      </c>
       <c r="F13">
-        <v>5.1949848895037301</v>
+        <v>6.4381260228580199</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B14">
-        <v>0.74233596483651698</v>
+        <v>0.73759563320647703</v>
       </c>
       <c r="C14">
-        <v>1.2192E-2</v>
+        <v>0.137964795</v>
       </c>
       <c r="D14" t="s">
         <v>41</v>
       </c>
       <c r="E14">
-        <v>1.6423830418461599E-2</v>
+        <v>0.18704665373388801</v>
       </c>
       <c r="F14">
-        <v>-163.072100172185</v>
+        <v>5.5662125718823496</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15">
-        <v>0.74233596483651698</v>
+        <v>0.73062868871751996</v>
       </c>
       <c r="C15">
-        <v>1.2192E-2</v>
+        <v>0.14825882000000001</v>
       </c>
       <c r="D15" t="s">
         <v>41</v>
       </c>
       <c r="E15">
+        <v>0.202919516150181</v>
+      </c>
+      <c r="F15">
+        <v>5.1949848895037301</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16">
+        <v>0.73062868871751996</v>
+      </c>
+      <c r="C16">
+        <v>0.14825882000000001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16">
+        <v>0.202919516150181</v>
+      </c>
+      <c r="F16">
+        <v>5.1262681581610803</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17">
         <v>1.6423830418461599E-2</v>
       </c>
-      <c r="F15">
+      <c r="F17">
+        <v>-163.072100172185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>1.6423830418461599E-2</v>
+      </c>
+      <c r="F18">
+        <v>-157.05714565763799</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19">
+        <v>1.6423830418461599E-2</v>
+      </c>
+      <c r="F19">
         <v>53.487681099100698</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96202A1F-4F02-47EE-B239-F409335667E4}">
-  <dimension ref="A1:C111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>0.66360277136277601</v>
-      </c>
-      <c r="B2">
-        <v>0.41148000000000001</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>0.66360277136277601</v>
-      </c>
-      <c r="B3">
-        <v>0.41148000000000001</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0.84496568832957797</v>
-      </c>
-      <c r="B4">
-        <v>0.41148000000000001</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>0.84496568832957797</v>
-      </c>
-      <c r="B5">
-        <v>0.41148000000000001</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1.79712100240526</v>
-      </c>
-      <c r="B6">
-        <v>9.6864407E-2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>1.79712100240526</v>
-      </c>
-      <c r="B7">
-        <v>9.6864407E-2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1.91936208989603</v>
-      </c>
-      <c r="B8">
-        <v>2.5907667999999998E-2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1.91936208989603</v>
-      </c>
-      <c r="B9">
-        <v>2.5907667999999998E-2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1.5364118092654899</v>
-      </c>
-      <c r="B10">
-        <v>0.111489093</v>
-      </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>1.5364118092654899</v>
-      </c>
-      <c r="B11">
-        <v>0.111489093</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>1.14254792657094</v>
-      </c>
-      <c r="B12">
-        <v>8.1843182E-2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>1.14254792657094</v>
-      </c>
-      <c r="B13">
-        <v>8.1843182E-2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>0.76948902444658396</v>
-      </c>
-      <c r="B14">
-        <v>0.24384</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>0.74683198736593104</v>
-      </c>
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>0.634197514012805</v>
-      </c>
-      <c r="C16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>0.81193724612891904</v>
-      </c>
-      <c r="B17">
-        <v>0.26351463400000003</v>
-      </c>
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>0.81193724612891904</v>
-      </c>
-      <c r="B18">
-        <v>0.26351463400000003</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>0.64229622161300404</v>
-      </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>0.64229622161300404</v>
-      </c>
-      <c r="C20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>0.66551573852542301</v>
-      </c>
-      <c r="B21">
-        <v>0.24384</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>0.66551573852542301</v>
-      </c>
-      <c r="B22">
-        <v>0.24384</v>
-      </c>
-      <c r="C22" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>0.66831711482098599</v>
-      </c>
-      <c r="B23">
-        <v>0.392848743</v>
-      </c>
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>0.66831711482098599</v>
-      </c>
-      <c r="B24">
-        <v>0.392848743</v>
-      </c>
-      <c r="C24" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>0.65580679181917101</v>
-      </c>
-      <c r="B25">
-        <v>0.392848743</v>
-      </c>
-      <c r="C25" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>0.65580679181917101</v>
-      </c>
-      <c r="B26">
-        <v>0.392848743</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>0.500234239386116</v>
-      </c>
-      <c r="B27">
-        <v>0.13716</v>
-      </c>
-      <c r="C27" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>0.500234239386116</v>
-      </c>
-      <c r="B28">
-        <v>0.13716</v>
-      </c>
-      <c r="C28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>0.49838619196324002</v>
-      </c>
-      <c r="B29">
-        <v>0.195072</v>
-      </c>
-      <c r="C29" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>0.49838619196324002</v>
-      </c>
-      <c r="B30">
-        <v>0.195072</v>
-      </c>
-      <c r="C30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>0.496481994488156</v>
-      </c>
-      <c r="B31">
-        <v>0.18592800000000001</v>
-      </c>
-      <c r="C31" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>0.496481994488156</v>
-      </c>
-      <c r="B32">
-        <v>0.18592800000000001</v>
-      </c>
-      <c r="C32" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>0.49364073113116103</v>
-      </c>
-      <c r="B33">
-        <v>0.176784</v>
-      </c>
-      <c r="C33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>0.49364073113116103</v>
-      </c>
-      <c r="B34">
-        <v>0.176784</v>
-      </c>
-      <c r="C34" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>0.48014251849385198</v>
-      </c>
-      <c r="B35">
-        <v>0.20116800000000001</v>
-      </c>
-      <c r="C35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>0.48014251849385198</v>
-      </c>
-      <c r="B36">
-        <v>0.20116800000000001</v>
-      </c>
-      <c r="C36" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>0.48738009477924898</v>
-      </c>
-      <c r="B37">
-        <v>0.20319999999999999</v>
-      </c>
-      <c r="C37" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>0.46633139234925403</v>
-      </c>
-      <c r="C38" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>0.44959398748926399</v>
-      </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>0.42847041975631001</v>
-      </c>
-      <c r="B40">
-        <v>0.17526</v>
-      </c>
-      <c r="C40" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>0.40867897602588799</v>
-      </c>
-      <c r="C41" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>0.41829191635495</v>
-      </c>
-      <c r="C42" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>0.57001899623787999</v>
-      </c>
-      <c r="B43">
-        <v>9.0498811999999998E-2</v>
-      </c>
-      <c r="C43" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>0.55068895347565805</v>
-      </c>
-      <c r="B44">
-        <v>0.132051846</v>
-      </c>
-      <c r="C44" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>0.52913409322569804</v>
-      </c>
-      <c r="B45">
-        <v>0.16555581</v>
-      </c>
-      <c r="C45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>0.51433262189204798</v>
-      </c>
-      <c r="B46">
-        <v>0.15135790499999999</v>
-      </c>
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>0.84629581545158405</v>
-      </c>
-      <c r="B47">
-        <v>0.38927203100000002</v>
-      </c>
-      <c r="C47" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>0.84629581545158405</v>
-      </c>
-      <c r="B48">
-        <v>0.38927203100000002</v>
-      </c>
-      <c r="C48" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>0.89039772710795695</v>
-      </c>
-      <c r="B49">
-        <v>0.24384</v>
-      </c>
-      <c r="C49" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>0.89039772710795695</v>
-      </c>
-      <c r="B50">
-        <v>0.24384</v>
-      </c>
-      <c r="C50" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>1.2795322417230099</v>
-      </c>
-      <c r="B51">
-        <v>0.27730699199999997</v>
-      </c>
-      <c r="C51" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>1.2795322417230099</v>
-      </c>
-      <c r="B52">
-        <v>0.27730699199999997</v>
-      </c>
-      <c r="C52" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>1.93587245637372</v>
-      </c>
-      <c r="B53">
-        <v>0.152032679</v>
-      </c>
-      <c r="C53" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>1.93587245637372</v>
-      </c>
-      <c r="B54">
-        <v>0.152032679</v>
-      </c>
-      <c r="C54" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>2.4780665467373599</v>
-      </c>
-      <c r="B55">
-        <v>9.9617103999999998E-2</v>
-      </c>
-      <c r="C55" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>2.4780665467373599</v>
-      </c>
-      <c r="B56">
-        <v>9.9617103999999998E-2</v>
-      </c>
-      <c r="C56" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>1.77503019033284</v>
-      </c>
-      <c r="B57">
-        <v>0.20904352600000001</v>
-      </c>
-      <c r="C57" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>1.7075802077995601</v>
-      </c>
-      <c r="B58">
-        <v>0.14364185700000001</v>
-      </c>
-      <c r="C58" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>1.4922591097125699</v>
-      </c>
-      <c r="B59">
-        <v>0.217546613</v>
-      </c>
-      <c r="C59" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>1.11609574558469</v>
-      </c>
-      <c r="B60">
-        <v>0.29169342100000001</v>
-      </c>
-      <c r="C60" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>1.00713808149247</v>
-      </c>
-      <c r="C61" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>0.99935539120017003</v>
-      </c>
-      <c r="B62">
-        <v>0.245749827</v>
-      </c>
-      <c r="C62" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>0.99935539120017003</v>
-      </c>
-      <c r="B63">
-        <v>0.245749827</v>
-      </c>
-      <c r="C63" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>0.94487655915406399</v>
-      </c>
-      <c r="B64">
-        <v>0.31575888699999999</v>
-      </c>
-      <c r="C64" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>0.94487655915406399</v>
-      </c>
-      <c r="B65">
-        <v>0.31575888699999999</v>
-      </c>
-      <c r="C65" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>0.87483234652335495</v>
-      </c>
-      <c r="B66">
-        <v>0.27092143800000001</v>
-      </c>
-      <c r="C66" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>0.87483234652335495</v>
-      </c>
-      <c r="B67">
-        <v>0.27092143800000001</v>
-      </c>
-      <c r="C67" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>0.27582680972963097</v>
-      </c>
-      <c r="B68">
-        <v>9.9059999999999995E-2</v>
-      </c>
-      <c r="C68" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>0.27582680972963097</v>
-      </c>
-      <c r="B69">
-        <v>9.9059999999999995E-2</v>
-      </c>
-      <c r="C69" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>0.14842325926962999</v>
-      </c>
-      <c r="B70">
-        <v>0.103632</v>
-      </c>
-      <c r="C70" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>0.14842325926962999</v>
-      </c>
-      <c r="B71">
-        <v>0.103632</v>
-      </c>
-      <c r="C71" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>0.13941805406320101</v>
-      </c>
-      <c r="B72">
-        <v>0.100003886</v>
-      </c>
-      <c r="C72" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>0.13941805406320101</v>
-      </c>
-      <c r="B73">
-        <v>0.100003886</v>
-      </c>
-      <c r="C73" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>0.35708644464821998</v>
-      </c>
-      <c r="B74">
-        <v>6.8341643999999993E-2</v>
-      </c>
-      <c r="C74" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>0.35708644464821998</v>
-      </c>
-      <c r="B75">
-        <v>6.8341643999999993E-2</v>
-      </c>
-      <c r="C75" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>0.97908907233996301</v>
-      </c>
-      <c r="B76">
-        <v>7.7164556999999995E-2</v>
-      </c>
-      <c r="C76" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>0.97908907233996301</v>
-      </c>
-      <c r="B77">
-        <v>7.7164556999999995E-2</v>
-      </c>
-      <c r="C77" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>0.73912910715284497</v>
-      </c>
-      <c r="B78">
-        <v>5.9129280999999999E-2</v>
-      </c>
-      <c r="C78" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>0.73912910715284497</v>
-      </c>
-      <c r="B79">
-        <v>5.9129280999999999E-2</v>
-      </c>
-      <c r="C79" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>0.50655758454314603</v>
-      </c>
-      <c r="B80">
-        <v>0.12576395200000001</v>
-      </c>
-      <c r="C80" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>0.50655758454314603</v>
-      </c>
-      <c r="B81">
-        <v>0.12576395200000001</v>
-      </c>
-      <c r="C81" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>0.26422745354100802</v>
-      </c>
-      <c r="B82">
-        <v>9.0472021999999999E-2</v>
-      </c>
-      <c r="C82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>0.26422745354100802</v>
-      </c>
-      <c r="B83">
-        <v>9.0472021999999999E-2</v>
-      </c>
-      <c r="C83" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>0.20547930573848</v>
-      </c>
-      <c r="B84">
-        <v>0.10404495</v>
-      </c>
-      <c r="C84" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>0.20547930573848</v>
-      </c>
-      <c r="B85">
-        <v>0.10404495</v>
-      </c>
-      <c r="C85" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>0.168078940883987</v>
-      </c>
-      <c r="C86" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>0.168078940883987</v>
-      </c>
-      <c r="C87" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>0.25776243935158599</v>
-      </c>
-      <c r="B88">
-        <v>0.142205108</v>
-      </c>
-      <c r="C88" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>0.30718976746298698</v>
-      </c>
-      <c r="C89" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>0.24912069961521999</v>
-      </c>
-      <c r="B90">
-        <v>0.11911748799999999</v>
-      </c>
-      <c r="C90" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>0.24912069961521999</v>
-      </c>
-      <c r="B91">
-        <v>0.11911748799999999</v>
-      </c>
-      <c r="C91" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>0.23799883780685399</v>
-      </c>
-      <c r="C92" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>0.23799883780685399</v>
-      </c>
-      <c r="C93" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>0.26752308407063402</v>
-      </c>
-      <c r="C94" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>0.26752308407063402</v>
-      </c>
-      <c r="C95" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>0.16056832408994501</v>
-      </c>
-      <c r="C96" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>0.16056832408994501</v>
-      </c>
-      <c r="C97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>0.74411257103448103</v>
-      </c>
-      <c r="B98">
-        <v>0.116835492</v>
-      </c>
-      <c r="C98" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>0.74411257103448103</v>
-      </c>
-      <c r="B99">
-        <v>0.116835492</v>
-      </c>
-      <c r="C99" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>0.87528110109794</v>
-      </c>
-      <c r="B100">
-        <v>8.9573877999999996E-2</v>
-      </c>
-      <c r="C100" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>0.87528110109794</v>
-      </c>
-      <c r="B101">
-        <v>8.9573877999999996E-2</v>
-      </c>
-      <c r="C101" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>1.62598028208757</v>
-      </c>
-      <c r="B102">
-        <v>4.0360477999999998E-2</v>
-      </c>
-      <c r="C102" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103">
-        <v>1.62598028208757</v>
-      </c>
-      <c r="B103">
-        <v>4.0360477999999998E-2</v>
-      </c>
-      <c r="C103" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104">
-        <v>1.32277923770115</v>
-      </c>
-      <c r="B104">
-        <v>3.2272940999999999E-2</v>
-      </c>
-      <c r="C104" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105">
-        <v>1.32277923770115</v>
-      </c>
-      <c r="B105">
-        <v>3.2272940999999999E-2</v>
-      </c>
-      <c r="C105" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106">
-        <v>1.0535668624027901</v>
-      </c>
-      <c r="B106">
-        <v>5.4257143000000001E-2</v>
-      </c>
-      <c r="C106" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107">
-        <v>0.78894922945176305</v>
-      </c>
-      <c r="C107" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108">
-        <v>0.73759563320647703</v>
-      </c>
-      <c r="B108">
-        <v>0.137964795</v>
-      </c>
-      <c r="C108" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109">
-        <v>0.73062868871751996</v>
-      </c>
-      <c r="B109">
-        <v>0.14825882000000001</v>
-      </c>
-      <c r="C109" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110">
-        <v>0.74233596483651698</v>
-      </c>
-      <c r="B110">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="C110" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111">
-        <v>0.74233596483651698</v>
-      </c>
-      <c r="B111">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="C111" t="s">
-        <v>41</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36744AEB-1C57-404E-BF73-00A3EA00B8B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AC1A98-805B-4CA3-825B-5FD4C8DAED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25080" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -19,26 +19,12 @@
     <sheet name="LF" sheetId="4" r:id="rId4"/>
     <sheet name="OS" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -49,13 +35,16 @@
     <t>u</t>
   </si>
   <si>
+    <t>velocity</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
     <t>uh</t>
   </si>
   <si>
-    <t>k600_1d</t>
+    <t>k600_1.day</t>
   </si>
   <si>
     <t>VentDO</t>
@@ -89,6 +78,9 @@
   </si>
   <si>
     <t>5/29/2023</t>
+  </si>
+  <si>
+    <t>11/7/2022</t>
   </si>
   <si>
     <t>11/21/2022</t>
@@ -164,6 +156,9 @@
   </si>
   <si>
     <t>OS</t>
+  </si>
+  <si>
+    <t>3/20/2023</t>
   </si>
 </sst>
 </file>
@@ -273,11 +268,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>AM!$C$1</c:f>
+              <c:f>AM!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>u</c:v>
+                  <c:v>k600_1.day</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -306,10 +301,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>AM!$B$2:$B$31</c:f>
+              <c:f>AM!$B$2:$B$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>0.66360277136277601</c:v>
                 </c:pt>
@@ -379,9 +374,6 @@
                 <c:pt idx="22">
                   <c:v>0.64229622161300404</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.66551573852542301</c:v>
-                </c:pt>
                 <c:pt idx="24">
                   <c:v>0.66551573852542301</c:v>
                 </c:pt>
@@ -389,15 +381,18 @@
                   <c:v>0.66551573852542301</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.66831711482098599</c:v>
+                  <c:v>0.66551573852542301</c:v>
                 </c:pt>
                 <c:pt idx="27">
                   <c:v>0.66831711482098599</c:v>
                 </c:pt>
                 <c:pt idx="28">
+                  <c:v>0.66831711482098599</c:v>
+                </c:pt>
+                <c:pt idx="29">
                   <c:v>0.65580679181917101</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>0.65580679181917101</c:v>
                 </c:pt>
               </c:numCache>
@@ -405,84 +400,99 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>AM!$C$2:$C$31</c:f>
+              <c:f>AM!$G$2:$G$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>0.41148000000000001</c:v>
+                  <c:v>8.7000179355782503</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.41148000000000001</c:v>
+                  <c:v>14.0537866274825</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.41148000000000001</c:v>
+                  <c:v>14.2509884099436</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.41148000000000001</c:v>
+                  <c:v>14.019548098025901</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.41148000000000001</c:v>
+                  <c:v>17.9748429691486</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.6864407E-2</c:v>
+                  <c:v>1.3659747293628499</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.6864407E-2</c:v>
+                  <c:v>1.43477614979118</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.5907667999999998E-2</c:v>
+                  <c:v>0.762817767337299</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.5907667999999998E-2</c:v>
+                  <c:v>0.954970513126703</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.111489093</c:v>
+                  <c:v>3.2531836035536301</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.111489093</c:v>
+                  <c:v>2.4433323290317999</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.111489093</c:v>
+                  <c:v>2.43040464475121</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8.1843182E-2</c:v>
+                  <c:v>7.0432970693483599</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8.1843182E-2</c:v>
+                  <c:v>2.7839849332143101</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>8.1843182E-2</c:v>
+                  <c:v>2.7892918049894102</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.24384</c:v>
+                  <c:v>7.6754733355837299</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22.624195858075399</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>22.5657731444328</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.1504080056141</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.26351463400000003</c:v>
+                  <c:v>7.76777594040046</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.26351463400000003</c:v>
+                  <c:v>11.6535292051355</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>32.6657378105105</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.24384</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.24384</c:v>
+                  <c:v>8.0612152297113795</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.24384</c:v>
+                  <c:v>7.8631523559558696</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.392848743</c:v>
+                  <c:v>30.1775506886923</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.392848743</c:v>
+                  <c:v>23.531152831216499</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.392848743</c:v>
+                  <c:v>18.703245444769301</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.392848743</c:v>
+                  <c:v>15.9745813671168</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>17.496680423021001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -490,7 +500,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-46A5-4B22-86F8-C2458802697F}"/>
+              <c16:uniqueId val="{00000000-C8C1-470E-B95C-FC31B64AD9C3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -502,11 +512,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1128867872"/>
-        <c:axId val="1128877952"/>
+        <c:axId val="549210224"/>
+        <c:axId val="405510960"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1128867872"/>
+        <c:axId val="549210224"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -563,12 +573,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1128877952"/>
+        <c:crossAx val="405510960"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1128877952"/>
+        <c:axId val="405510960"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -625,7 +635,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1128867872"/>
+        <c:crossAx val="549210224"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -736,11 +746,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GB!$C$1</c:f>
+              <c:f>GB!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>u</c:v>
+                  <c:v>k600_1.day</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -767,26 +777,12 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:trendline>
-            <c:spPr>
-              <a:ln w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:trendlineType val="linear"/>
-            <c:dispRSqr val="0"/>
-            <c:dispEq val="0"/>
-          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>GB!$B$2:$B$28</c:f>
+              <c:f>GB!$B$2:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>0.500234239386116</c:v>
                 </c:pt>
@@ -856,16 +852,16 @@
                 <c:pt idx="22">
                   <c:v>0.57001899623787999</c:v>
                 </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.55068895347565805</c:v>
-                </c:pt>
                 <c:pt idx="24">
                   <c:v>0.55068895347565805</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>0.55068895347565805</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>0.52913409322569804</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>0.51433262189204798</c:v>
                 </c:pt>
               </c:numCache>
@@ -873,10 +869,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$F$2:$F$28</c:f>
+              <c:f>GB!$G$2:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>8.0617713895940106</c:v>
                 </c:pt>
@@ -943,13 +939,10 @@
                 <c:pt idx="21">
                   <c:v>21.2301041068087</c:v>
                 </c:pt>
-                <c:pt idx="22">
-                  <c:v>-2.7729314633187902E-3</c:v>
-                </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>17.612268500013801</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>10.116682809798901</c:v>
                 </c:pt>
               </c:numCache>
@@ -958,7 +951,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7845-4E05-9612-5DF4AEBCDB3E}"/>
+              <c16:uniqueId val="{00000000-57DB-4077-93E9-A3A99C7244D8}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -970,11 +963,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1729563344"/>
-        <c:axId val="1886997552"/>
+        <c:axId val="697174239"/>
+        <c:axId val="697173759"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1729563344"/>
+        <c:axId val="697174239"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1031,12 +1024,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1886997552"/>
+        <c:crossAx val="697173759"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1886997552"/>
+        <c:axId val="697173759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1093,7 +1086,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1729563344"/>
+        <c:crossAx val="697174239"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1204,11 +1197,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ID!$C$1</c:f>
+              <c:f>ID!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>u</c:v>
+                  <c:v>k600_1.day</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1235,12 +1228,26 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ID!$B$2:$B$15</c:f>
+              <c:f>ID!$B$2:$B$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>0.84629581545158405</c:v>
                 </c:pt>
@@ -1274,13 +1281,13 @@
                 <c:pt idx="10">
                   <c:v>1.00713808149247</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>0.99935539120017003</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>0.94487655915406399</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>0.87483234652335495</c:v>
                 </c:pt>
               </c:numCache>
@@ -1288,48 +1295,54 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ID!$C$2:$C$15</c:f>
+              <c:f>ID!$G$2:$G$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
-                  <c:v>0.38927203100000002</c:v>
+                  <c:v>7.8958984290259</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.24384</c:v>
+                  <c:v>6.2631698085533101</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.27730699199999997</c:v>
+                  <c:v>4.17908012369488</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.152032679</c:v>
+                  <c:v>9.2886180882038705</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.9617103999999998E-2</c:v>
+                  <c:v>1.91650182628218</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.20904352600000001</c:v>
+                  <c:v>4.44794425583971</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.14364185700000001</c:v>
+                  <c:v>8.1938063501887299</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.217546613</c:v>
+                  <c:v>11.981817018407201</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.217546613</c:v>
+                  <c:v>11.9908106789727</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.29169342100000001</c:v>
+                  <c:v>8.5316662064735205</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.3052048733349402</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.245749827</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.31575888699999999</c:v>
+                  <c:v>16.0453723843845</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.27092143800000001</c:v>
+                  <c:v>7.0638592430665703</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>8.2264856374067996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1337,7 +1350,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-20BD-4835-9365-47E4A348CA11}"/>
+              <c16:uniqueId val="{00000000-5117-45FA-8FA4-CFA9B7EE1592}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1349,11 +1362,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1871026208"/>
-        <c:axId val="1871025728"/>
+        <c:axId val="697163679"/>
+        <c:axId val="697180479"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1871026208"/>
+        <c:axId val="697163679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1410,12 +1423,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1871025728"/>
+        <c:crossAx val="697180479"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1871025728"/>
+        <c:axId val="697180479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1472,7 +1485,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1871026208"/>
+        <c:crossAx val="697163679"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1574,7 +1587,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.3136482939632545E-2"/>
+          <c:y val="2.5428331875182269E-2"/>
+          <c:w val="0.87437751531058616"/>
+          <c:h val="0.72088764946048411"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1583,11 +1606,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>LF!$C$1</c:f>
+              <c:f>LF!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>u</c:v>
+                  <c:v>k600_1.day</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1693,51 +1716,48 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>LF!$C$2:$C$19</c:f>
+              <c:f>LF!$G$2:$G$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>9.9059999999999995E-2</c:v>
+                  <c:v>24.690084932127998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.9059999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.103632</c:v>
+                  <c:v>23.148382126467901</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50.954752325421801</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6.8341643999999993E-2</c:v>
+                  <c:v>9.73092604234097</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.8341643999999993E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7.7164556999999995E-2</c:v>
+                  <c:v>9.5554623120508193</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>5.9129280999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.12576395200000001</c:v>
+                  <c:v>7.9516472320781002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.0472021999999999E-2</c:v>
+                  <c:v>34.983383524448797</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.10404495</c:v>
+                  <c:v>53.152789367811998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>33.341043343649702</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.142205108</c:v>
+                  <c:v>31.9180285667398</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>15.8650769934215</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.11911748799999999</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.23330000000000001</c:v>
+                  <c:v>26.1959995510725</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.23330000000000001</c:v>
+                  <c:v>42.614245239660903</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1745,7 +1765,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-2349-4E14-91C4-B8E9F08548FA}"/>
+              <c16:uniqueId val="{00000000-BCF6-48DA-A0D6-4E04D3B3490E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1757,11 +1777,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1624481104"/>
-        <c:axId val="1132239360"/>
+        <c:axId val="697191519"/>
+        <c:axId val="697203999"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1624481104"/>
+        <c:axId val="697191519"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1818,12 +1838,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1132239360"/>
+        <c:crossAx val="697203999"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1132239360"/>
+        <c:axId val="697203999"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1880,401 +1900,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1624481104"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>OS!$C$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>u</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:noFill/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>OS!$B$2:$B$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.74411257103448103</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.74411257103448103</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.74411257103448103</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.87528110109794</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.87528110109794</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.87528110109794</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.62598028208757</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.62598028208757</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.32277923770115</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.32277923770115</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.0535668624027901</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.78894922945176305</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.73759563320647703</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.73062868871751996</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.73062868871751996</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>OS!$C$2:$C$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
-                <c:pt idx="0">
-                  <c:v>0.116835492</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.116835492</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.116835492</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.9573877999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>8.9573877999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8.9573877999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4.0360477999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>4.0360477999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2272940999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.2272940999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5.4257143000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.137964795</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.14825882000000001</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.14825882000000001</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.2192E-2</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.2192E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.2192E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BA74-41FB-86E9-C0420B0B15F4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="1860211616"/>
-        <c:axId val="1860209216"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="1860211616"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1860209216"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1860209216"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1860211616"/>
+        <c:crossAx val="697191519"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2490,46 +2116,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4594,543 +4180,27 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>4762</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE14FCCF-C532-FAD8-B774-C29805A0D67D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3638D75B-E76D-60AA-0E9B-08682A93FCF5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5155,23 +4225,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>100012</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE4B8E65-7449-6AA2-303D-7FEFFFCE5381}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B612589B-EF37-7A1C-3658-9DE4832C1E91}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5212,7 +4282,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDEC00EF-2730-19B8-DB6A-50F0EE1D5199}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F56FE988-7D8D-F7AD-1677-E0FAAEFB0B4F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5237,64 +4307,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>176212</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>481012</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>185737</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>61912</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>481012</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49BF9AF9-F0B6-3241-B273-5C2893680841}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBF99EFC-A32B-0EFF-C138-8FEB3F4F3926}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC4F6AC-1CCE-ED2D-1CFC-5D027CE7CB51}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5594,10 +4623,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5622,10 +4651,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0.66360277136277601</v>
@@ -5633,25 +4665,28 @@
       <c r="C2">
         <v>0.41148000000000001</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2">
+        <v>0.36972856114008101</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2">
+        <v>0.62006974316123398</v>
+      </c>
+      <c r="G2">
+        <v>8.7000179355782503</v>
+      </c>
+      <c r="H2">
+        <v>1.5</v>
+      </c>
+      <c r="I2">
+        <v>71.992540000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
-      </c>
-      <c r="E2">
-        <v>0.62006974316123398</v>
-      </c>
-      <c r="F2">
-        <v>8.7000179355782503</v>
-      </c>
-      <c r="G2">
-        <v>1.5</v>
-      </c>
-      <c r="H2">
-        <v>71.992540000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
       </c>
       <c r="B3">
         <v>0.66360277136277601</v>
@@ -5659,25 +4694,28 @@
       <c r="C3">
         <v>0.41148000000000001</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>0.36972856114008101</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3">
         <v>0.62006974316123398</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>14.0537866274825</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.5</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>71.992540000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>0.84496568832957797</v>
@@ -5685,25 +4723,28 @@
       <c r="C4">
         <v>0.41148000000000001</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>0.31614251553411798</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
         <v>0.48697835389441602</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>14.2509884099436</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>1.097</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>71.486959999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0.84496568832957797</v>
@@ -5711,25 +4752,28 @@
       <c r="C5">
         <v>0.41148000000000001</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5">
+      <c r="D5">
+        <v>0.31614251553411798</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
         <v>0.48697835389441602</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>14.019548098025901</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>1.097</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>71.486959999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>0.84496568832957797</v>
@@ -5737,25 +4781,28 @@
       <c r="C6">
         <v>0.41148000000000001</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>0.31614251553411798</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
         <v>0.48697835389441602</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>17.9748429691486</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1.097</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>71.486959999999996</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>1.79712100240526</v>
@@ -5763,22 +4810,25 @@
       <c r="C7">
         <v>9.6864407E-2</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>3.4815776102823201E-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
         <v>5.38997690585983E-2</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>1.3659747293628499</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>71.140784310000001</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>1.79712100240526</v>
@@ -5786,22 +4836,25 @@
       <c r="C8">
         <v>9.6864407E-2</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>3.4815776102823201E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8">
         <v>5.38997690585983E-2</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>1.43477614979118</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>71.140784310000001</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>1.91936208989603</v>
@@ -5809,25 +4862,28 @@
       <c r="C9">
         <v>2.5907667999999998E-2</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9">
+      <c r="D9">
+        <v>-1.30195181397141E-3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9">
         <v>1.34980617447766E-2</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.762817767337299</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1.288</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>71.42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>1.91936208989603</v>
@@ -5835,25 +4891,28 @@
       <c r="C10">
         <v>2.5907667999999998E-2</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
+        <v>-1.30195181397141E-3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
         <v>1.34980617447766E-2</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.954970513126703</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1.288</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>71.42</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11">
         <v>1.5364118092654899</v>
@@ -5861,22 +4920,25 @@
       <c r="C11">
         <v>0.111489093</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11">
+      <c r="D11">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11">
         <v>7.25645899931604E-2</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>3.2531836035536301</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1.26</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1.5364118092654899</v>
@@ -5884,22 +4946,25 @@
       <c r="C12">
         <v>0.111489093</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12">
+      <c r="D12">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12">
         <v>7.25645899931604E-2</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>2.4433323290317999</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>1.26</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13">
         <v>1.5364118092654899</v>
@@ -5907,22 +4972,25 @@
       <c r="C13">
         <v>0.111489093</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13">
+      <c r="D13">
+        <v>0.111845716661391</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13">
         <v>7.25645899931604E-2</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>2.43040464475121</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1.26</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14">
         <v>1.14254792657094</v>
@@ -5930,22 +4998,25 @@
       <c r="C14">
         <v>8.1843182E-2</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14">
+      <c r="D14">
+        <v>0.22821795159007199</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14">
         <v>7.1632165353124999E-2</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>7.0432970693483599</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>72.604545450000003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>1.14254792657094</v>
@@ -5953,22 +5024,25 @@
       <c r="C15">
         <v>8.1843182E-2</v>
       </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15">
+      <c r="D15">
+        <v>0.22821795159007199</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15">
         <v>7.1632165353124999E-2</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>2.7839849332143101</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>72.604545450000003</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16">
         <v>1.14254792657094</v>
@@ -5976,22 +5050,25 @@
       <c r="C16">
         <v>8.1843182E-2</v>
       </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
+        <v>0.22821795159007199</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
         <v>7.1632165353124999E-2</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>2.7892918049894102</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>72.604545450000003</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17">
         <v>0.76948902444658396</v>
@@ -5999,55 +5076,67 @@
       <c r="C17">
         <v>0.24384</v>
       </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17">
+      <c r="D17">
+        <v>0.33844308293048597</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17">
         <v>0.31688561142944099</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>7.6754733355837299</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>73.478181820000003</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>0.74683198736593104</v>
       </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18">
+      <c r="D18">
+        <v>0.34513740083518801</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
         <v>22.624195858075399</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>0.74683198736593104</v>
       </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19">
+      <c r="D19">
+        <v>0.34513740083518801</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19">
         <v>22.5657731444328</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>0.634197514012805</v>
       </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20">
+      <c r="D20">
+        <v>0.37841672897374601</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20">
         <v>16.1504080056141</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B21">
         <v>0.81193724612891904</v>
@@ -6055,19 +5144,22 @@
       <c r="C21">
         <v>0.26351463400000003</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21">
+      <c r="D21">
+        <v>0.32590120071440998</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21">
         <v>0.32455049359585503</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>7.76777594040046</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B22">
         <v>0.81193724612891904</v>
@@ -6075,61 +5167,64 @@
       <c r="C22">
         <v>0.26351463400000003</v>
       </c>
-      <c r="D22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22">
+      <c r="D22">
+        <v>0.32590120071440998</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22">
         <v>0.32455049359585503</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>11.6535292051355</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.64229622161300404</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23">
+      <c r="D23">
+        <v>0.37602385990176701</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23">
         <v>32.6657378105105</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>0.64229622161300404</v>
       </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24">
-        <v>51.880320990253502</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>0.37602385990176701</v>
+      </c>
+      <c r="E24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25">
-        <v>0.66551573852542301</v>
+        <v>18</v>
       </c>
       <c r="C25">
-        <v>0.24384</v>
-      </c>
-      <c r="D25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E25">
-        <v>0.36639253722274701</v>
-      </c>
-      <c r="F25">
-        <v>8.0612152297113795</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.32508800599999998</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" t="e">
+        <v>#NUM!</v>
+      </c>
+      <c r="H25">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B26">
         <v>0.66551573852542301</v>
@@ -6137,19 +5232,22 @@
       <c r="C26">
         <v>0.24384</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
-      </c>
-      <c r="E26">
+      <c r="D26">
+        <v>0.36916334997489503</v>
+      </c>
+      <c r="E26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26">
         <v>0.36639253722274701</v>
       </c>
-      <c r="F26">
-        <v>7.8631523559558696</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>8.0612152297113795</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B27">
         <v>0.66551573852542301</v>
@@ -6157,45 +5255,45 @@
       <c r="C27">
         <v>0.24384</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27">
+      <c r="D27">
+        <v>0.36916334997489503</v>
+      </c>
+      <c r="E27" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27">
         <v>0.36639253722274701</v>
       </c>
-      <c r="F27">
+      <c r="G27">
+        <v>7.8631523559558696</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>0.66551573852542301</v>
+      </c>
+      <c r="C28">
+        <v>0.24384</v>
+      </c>
+      <c r="D28">
+        <v>0.36916334997489503</v>
+      </c>
+      <c r="E28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>0.36639253722274701</v>
+      </c>
+      <c r="G28">
         <v>30.1775506886923</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>18</v>
-      </c>
-      <c r="B28">
-        <v>0.66831711482098599</v>
-      </c>
-      <c r="C28">
-        <v>0.392848743</v>
-      </c>
-      <c r="D28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28">
-        <v>0.587817870121772</v>
-      </c>
-      <c r="F28">
-        <v>23.531152831216499</v>
-      </c>
-      <c r="G28">
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="H28">
-        <v>71.94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>0.66831711482098599</v>
@@ -6203,51 +5301,57 @@
       <c r="C29">
         <v>0.392848743</v>
       </c>
-      <c r="D29" t="s">
-        <v>9</v>
-      </c>
-      <c r="E29">
+      <c r="D29">
+        <v>0.368335646713147</v>
+      </c>
+      <c r="E29" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29">
         <v>0.587817870121772</v>
       </c>
-      <c r="F29">
-        <v>18.703245444769301</v>
-      </c>
       <c r="G29">
+        <v>23.531152831216499</v>
+      </c>
+      <c r="H29">
         <v>0.97499999999999998</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <v>71.94</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B30">
-        <v>0.65580679181917101</v>
+        <v>0.66831711482098599</v>
       </c>
       <c r="C30">
         <v>0.392848743</v>
       </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30">
-        <v>0.59903122062865499</v>
+      <c r="D30">
+        <v>0.368335646713147</v>
+      </c>
+      <c r="E30" t="s">
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>15.9745813671168</v>
+        <v>0.587817870121772</v>
       </c>
       <c r="G30">
-        <v>1.42</v>
+        <v>18.703245444769301</v>
       </c>
       <c r="H30">
-        <v>71.942899999999995</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="I30">
+        <v>71.94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B31">
         <v>0.65580679181917101</v>
@@ -6255,19 +5359,51 @@
       <c r="C31">
         <v>0.392848743</v>
       </c>
-      <c r="D31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E31">
+      <c r="D31">
+        <v>0.372031985248788</v>
+      </c>
+      <c r="E31" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31">
         <v>0.59903122062865499</v>
       </c>
-      <c r="F31">
+      <c r="G31">
+        <v>15.9745813671168</v>
+      </c>
+      <c r="H31">
+        <v>1.42</v>
+      </c>
+      <c r="I31">
+        <v>71.942899999999995</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32">
+        <v>0.65580679181917101</v>
+      </c>
+      <c r="C32">
+        <v>0.392848743</v>
+      </c>
+      <c r="D32">
+        <v>0.372031985248788</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>0.59903122062865499</v>
+      </c>
+      <c r="G32">
         <v>17.496680423021001</v>
       </c>
-      <c r="G31">
+      <c r="H32">
         <v>1.42</v>
       </c>
-      <c r="H31">
+      <c r="I32">
         <v>71.942899999999995</v>
       </c>
     </row>
@@ -6280,10 +5416,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6308,10 +5444,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0.500234239386116</v>
@@ -6319,25 +5458,28 @@
       <c r="C2">
         <v>0.13716</v>
       </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
+        <v>0.15821662988639301</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2">
         <v>0.27419154708066701</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>8.0617713895940106</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>6.25</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>72.545299999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>0.500234239386116</v>
@@ -6345,25 +5487,28 @@
       <c r="C3">
         <v>0.13716</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>0.15821662988639301</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
         <v>0.27419154708066701</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>8.0092423263314494</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>6.25</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>72.545299999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>0.500234239386116</v>
@@ -6371,25 +5516,28 @@
       <c r="C4">
         <v>0.13716</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>0.15821662988639301</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4">
         <v>0.27419154708066701</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>20.759702379649699</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>6.25</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>72.545299999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>0.49838619196324002</v>
@@ -6397,25 +5545,28 @@
       <c r="C5">
         <v>0.195072</v>
       </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5">
+      <c r="D5">
+        <v>0.15917946283117099</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
         <v>0.39140731253322603</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>11.7604829329048</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>4.8</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>73.188749999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6">
         <v>0.49838619196324002</v>
@@ -6423,25 +5574,28 @@
       <c r="C6">
         <v>0.195072</v>
       </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>0.15917946283117099</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6">
         <v>0.39140731253322603</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>11.63069034185</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>4.8</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>73.188749999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7">
         <v>0.496481994488156</v>
@@ -6449,19 +5603,22 @@
       <c r="C7">
         <v>0.18592800000000001</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>0.16017154996036501</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
         <v>0.37449092225727298</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>16.082464877533099</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>0.496481994488156</v>
@@ -6469,19 +5626,22 @@
       <c r="C8">
         <v>0.18592800000000001</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>0.16017154996036501</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8">
         <v>0.37449092225727298</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>19.278549967453198</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>0.49364073113116103</v>
@@ -6489,19 +5649,22 @@
       <c r="C9">
         <v>0.176784</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9">
+      <c r="D9">
+        <v>0.16165184853443901</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9">
         <v>0.35812279832522198</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>18.3266040851639</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
         <v>0.49364073113116103</v>
@@ -6509,19 +5672,22 @@
       <c r="C10">
         <v>0.176784</v>
       </c>
-      <c r="D10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
+        <v>0.16165184853443901</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10">
         <v>0.35812279832522198</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>18.238219059268399</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>0.49364073113116103</v>
@@ -6529,19 +5695,22 @@
       <c r="C11">
         <v>0.176784</v>
       </c>
-      <c r="D11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11">
+      <c r="D11">
+        <v>0.16165184853443901</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11">
         <v>0.35812279832522198</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>15.8324828082942</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0.48014251849385198</v>
@@ -6549,25 +5718,28 @@
       <c r="C12">
         <v>0.20116800000000001</v>
       </c>
-      <c r="D12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12">
+      <c r="D12">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12">
         <v>0.418975600475957</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>12.5427239203201</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>5.58</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>73.188749999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>0.48014251849385198</v>
@@ -6575,25 +5747,28 @@
       <c r="C13">
         <v>0.20116800000000001</v>
       </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13">
+      <c r="D13">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13">
         <v>0.418975600475957</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>10.123963721124101</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>5.58</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>73.188749999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14">
         <v>0.48014251849385198</v>
@@ -6601,25 +5776,28 @@
       <c r="C14">
         <v>0.20116800000000001</v>
       </c>
-      <c r="D14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14">
+      <c r="D14">
+        <v>0.168684419052893</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14">
         <v>0.418975600475957</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>9.9882836327260591</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>5.58</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>73.188749999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15">
         <v>0.48738009477924898</v>
@@ -6627,25 +5805,28 @@
       <c r="C15">
         <v>0.20319999999999999</v>
       </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15">
+      <c r="D15">
+        <v>0.16491364087822899</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15">
         <v>0.41692305897727699</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>15.491084387970799</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>4.6849999999999996</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>72.484999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>0.48738009477924898</v>
@@ -6653,59 +5834,74 @@
       <c r="C16">
         <v>0.20319999999999999</v>
       </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
+        <v>0.16491364087822899</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16">
         <v>0.41692305897727699</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>15.422189134531401</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>4.6849999999999996</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>72.484999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17">
         <v>0.46633139234925403</v>
       </c>
-      <c r="D17" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17">
+      <c r="C17">
+        <v>0.1016</v>
+      </c>
+      <c r="D17">
+        <v>0.17588001754885099</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17">
         <v>0.21787081390374799</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>28.8790872259084</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18">
         <v>0.44959398748926399</v>
       </c>
-      <c r="D18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18">
+      <c r="C18">
+        <v>0.140208</v>
+      </c>
+      <c r="D18">
+        <v>0.18460020763153301</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18">
         <v>0.31185470424768102</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>31.877696149374302</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19">
         <v>0.42847041975631001</v>
@@ -6713,22 +5909,25 @@
       <c r="C19">
         <v>0.17526</v>
       </c>
-      <c r="D19" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19">
+      <c r="D19">
+        <v>0.19560558913461701</v>
+      </c>
+      <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19">
         <v>0.40903640465934199</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>32.379700829916601</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>4.6849999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B20">
         <v>0.42847041975631001</v>
@@ -6736,55 +5935,67 @@
       <c r="C20">
         <v>0.17526</v>
       </c>
-      <c r="D20" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20">
+      <c r="D20">
+        <v>0.19560558913461701</v>
+      </c>
+      <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20">
         <v>0.40903640465934199</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>32.274144438345303</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>4.6849999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>0.40867897602588799</v>
       </c>
-      <c r="D21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21">
+      <c r="D21">
+        <v>0.20591693386121401</v>
+      </c>
+      <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21">
         <v>19.545410722183501</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>0.40867897602588799</v>
       </c>
-      <c r="D22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22">
+      <c r="D22">
+        <v>0.20591693386121401</v>
+      </c>
+      <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22">
         <v>19.3542063534147</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>0.41829191635495</v>
       </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23">
+      <c r="D23">
+        <v>0.200908590714584</v>
+      </c>
+      <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23">
         <v>21.2301041068087</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24">
         <v>0.57001899623787999</v>
@@ -6792,42 +6003,36 @@
       <c r="C24">
         <v>9.0498811999999998E-2</v>
       </c>
-      <c r="D24" t="s">
-        <v>20</v>
-      </c>
-      <c r="E24">
+      <c r="D24">
+        <v>0.12185876259982401</v>
+      </c>
+      <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24">
         <v>0.15876455451009799</v>
       </c>
-      <c r="F24">
-        <v>-2.7729314633187902E-3</v>
-      </c>
-      <c r="G24">
+      <c r="H24">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <v>72.918940000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25">
-        <v>0.55068895347565805</v>
+        <v>18</v>
       </c>
       <c r="C25">
-        <v>0.132051846</v>
-      </c>
-      <c r="D25" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25">
-        <v>0.239793889393565</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>7.4432234E-2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B26">
         <v>0.55068895347565805</v>
@@ -6835,50 +6040,79 @@
       <c r="C26">
         <v>0.132051846</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26">
+        <v>0.13192971736270201</v>
+      </c>
+      <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26">
+        <v>0.239793889393565</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="C27">
+        <v>0.132051846</v>
+      </c>
+      <c r="D27">
+        <v>0.13192971736270201</v>
+      </c>
+      <c r="E27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27">
+        <v>0.239793889393565</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>20</v>
       </c>
-      <c r="E26">
-        <v>0.239793889393565</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B27">
+      <c r="B28">
         <v>0.52913409322569804</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>0.16555581</v>
       </c>
-      <c r="D27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27">
+      <c r="D28">
+        <v>0.14315980232256301</v>
+      </c>
+      <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28">
         <v>0.31288063294266599</v>
       </c>
-      <c r="F27">
+      <c r="G28">
         <v>17.612268500013801</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
         <v>0.51433262189204798</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>0.15135790499999999</v>
       </c>
-      <c r="D28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28">
+      <c r="D29">
+        <v>0.15087137078926999</v>
+      </c>
+      <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29">
         <v>0.29428019642854403</v>
       </c>
-      <c r="F28">
+      <c r="G29">
         <v>10.116682809798901</v>
       </c>
     </row>
@@ -6891,10 +6125,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6919,10 +6153,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>0.84629581545158405</v>
@@ -6930,19 +6167,22 @@
       <c r="C2">
         <v>0.38927203100000002</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
+        <v>0.32925108320353702</v>
+      </c>
+      <c r="E2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2">
         <v>0.45997158900317198</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>7.8958984290259</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>0.89039772710795695</v>
@@ -6950,19 +6190,22 @@
       <c r="C3">
         <v>0.24384</v>
       </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>0.32251637360024299</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3">
         <v>0.27385514649953202</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>6.2631698085533101</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4">
         <v>1.2795322417230099</v>
@@ -6970,19 +6213,22 @@
       <c r="C4">
         <v>0.27730699199999997</v>
       </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>0.26309246533588299</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <v>0.21672528675524499</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>4.17908012369488</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>1.93587245637372</v>
@@ -6990,19 +6236,22 @@
       <c r="C5">
         <v>0.152032679</v>
       </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5">
+      <c r="D5">
+        <v>0.16286414006333</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5">
         <v>7.8534450190374402E-2</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>9.2886180882038705</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B6">
         <v>2.4780665467373599</v>
@@ -7010,19 +6259,22 @@
       <c r="C6">
         <v>9.9617103999999998E-2</v>
       </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>8.0066827881655006E-2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
         <v>4.0199527382005301E-2</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>1.91650182628218</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B7">
         <v>1.77503019033284</v>
@@ -7030,19 +6282,22 @@
       <c r="C7">
         <v>0.20904352600000001</v>
       </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>0.18742602214593199</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7">
         <v>0.117768997473109</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>4.44794425583971</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8">
         <v>1.7075802077995601</v>
@@ -7050,19 +6305,22 @@
       <c r="C8">
         <v>0.14364185700000001</v>
       </c>
-      <c r="D8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>0.19772616624508799</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8">
         <v>8.4120122934137995E-2</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>8.1938063501887299</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9">
         <v>1.4922591097125699</v>
@@ -7070,19 +6328,22 @@
       <c r="C9">
         <v>0.217546613</v>
       </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9">
+      <c r="D9">
+        <v>0.2306073954847</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9">
         <v>0.14578340422522401</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>11.981817018407201</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10">
         <v>1.4922591097125699</v>
@@ -7090,19 +6351,22 @@
       <c r="C10">
         <v>0.217546613</v>
       </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
+        <v>0.2306073954847</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
         <v>0.14578340422522401</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>11.9908106789727</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11">
         <v>1.11609574558469</v>
@@ -7110,84 +6374,110 @@
       <c r="C11">
         <v>0.29169342100000001</v>
       </c>
-      <c r="D11" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11">
+      <c r="D11">
+        <v>0.28805050680691402</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11">
         <v>0.26135161087563402</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>8.5316662064735205</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1.00713808149247</v>
       </c>
-      <c r="D12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12">
+      <c r="D12">
+        <v>0.304689201120935</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12">
         <v>9.3052048733349402</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
         <v>0.99935539120017003</v>
       </c>
-      <c r="C13">
+      <c r="C14">
         <v>0.245749827</v>
       </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13">
+      <c r="D14">
+        <v>0.305877679286223</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14">
         <v>0.24590834168099901</v>
       </c>
-      <c r="F13">
+      <c r="G14">
         <v>16.0453723843845</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
         <v>0.94487655915406399</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>0.31575888699999999</v>
       </c>
-      <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14">
+      <c r="D15">
+        <v>0.314197026443233</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15">
         <v>0.33418004070573498</v>
       </c>
-      <c r="F14">
+      <c r="G15">
         <v>7.0638592430665703</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
         <v>0.87483234652335495</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>0.27092143800000001</v>
       </c>
-      <c r="D15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E15">
+      <c r="D16">
+        <v>0.32489332993081799</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16">
         <v>0.30968383722511</v>
       </c>
-      <c r="F15">
+      <c r="G16">
         <v>8.2264856374067996</v>
       </c>
     </row>
@@ -7200,10 +6490,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7228,10 +6518,13 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>0.27582680972963097</v>
@@ -7239,25 +6532,28 @@
       <c r="C2">
         <v>9.9059999999999995E-2</v>
       </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
+      <c r="D2">
+        <v>0.108072813469553</v>
+      </c>
+      <c r="E2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2">
         <v>0.359138403178066</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>24.690084932127998</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1.76</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>74.42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>0.27582680972963097</v>
@@ -7265,25 +6561,28 @@
       <c r="C3">
         <v>9.9059999999999995E-2</v>
       </c>
-      <c r="D3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>0.108072813469553</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3">
         <v>0.359138403178066</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>23.148382126467901</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>1.76</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>74.42</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0.14842325926962999</v>
@@ -7291,42 +6590,48 @@
       <c r="C4">
         <v>0.103632</v>
       </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>0.11932456079093</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
         <v>0.69821940651323</v>
       </c>
-      <c r="F4">
-        <v>118.259222088889</v>
-      </c>
-      <c r="G4">
+      <c r="H4">
         <v>1.83</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>73.290000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5">
         <v>0.13941805406320101</v>
       </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
+      <c r="C5">
+        <v>0.100003886</v>
+      </c>
+      <c r="D5">
+        <v>0.12011986275225001</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5">
         <v>0.71729509260447999</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>50.954752325421801</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0.35708644464821998</v>
@@ -7334,19 +6639,22 @@
       <c r="C6">
         <v>6.8341643999999993E-2</v>
       </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>0.100896303268462</v>
+      </c>
+      <c r="E6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6">
         <v>0.19138683370444401</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>9.73092604234097</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>0.35708644464821998</v>
@@ -7354,19 +6662,22 @@
       <c r="C7">
         <v>6.8341643999999993E-2</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>0.100896303268462</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7">
         <v>0.19138683370444401</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>9.5554623120508193</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8">
         <v>0.97908907233996301</v>
@@ -7374,19 +6685,19 @@
       <c r="C8">
         <v>7.7164556999999995E-2</v>
       </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8">
+      <c r="D8">
+        <v>4.5963639502409802E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
         <v>7.8812601610986702E-2</v>
       </c>
-      <c r="F8">
-        <v>12.1601192837523</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9">
         <v>0.73912910715284497</v>
@@ -7394,25 +6705,28 @@
       <c r="C9">
         <v>5.9129280999999999E-2</v>
       </c>
-      <c r="D9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9">
+      <c r="D9">
+        <v>6.7155897377356E-2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
         <v>7.9998582693852197E-2</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>7.9516472320781002</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1.93</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>74.42</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10">
         <v>0.50655758454314603</v>
@@ -7420,25 +6734,25 @@
       <c r="C10">
         <v>0.12576395200000001</v>
       </c>
-      <c r="D10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10">
+      <c r="D10">
+        <v>8.7695638986629201E-2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10">
         <v>0.24827177765667799</v>
       </c>
-      <c r="F10">
-        <v>30.7702058957052</v>
-      </c>
-      <c r="G10">
+      <c r="H10">
         <v>1.53</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11">
         <v>0.26422745354100802</v>
@@ -7446,25 +6760,28 @@
       <c r="C11">
         <v>9.0472021999999999E-2</v>
       </c>
-      <c r="D11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11">
+      <c r="D11">
+        <v>0.109097219967282</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
         <v>0.34240205091314901</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>34.983383524448797</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1.704</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>73.278000000000006</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12">
         <v>0.20547930573848</v>
@@ -7472,39 +6789,48 @@
       <c r="C12">
         <v>0.10404495</v>
       </c>
-      <c r="D12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12">
+      <c r="D12">
+        <v>0.114285610026165</v>
+      </c>
+      <c r="E12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12">
         <v>0.50635245055977096</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>53.152789367811998</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>72.669256200000007</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B13">
         <v>0.168078940883987</v>
       </c>
-      <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13">
+      <c r="C13">
+        <v>5.4061723999999999E-2</v>
+      </c>
+      <c r="D13">
+        <v>0.11758865341507101</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13">
         <v>0.32164483971442398</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>33.341043343649702</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14">
         <v>0.25776243935158599</v>
@@ -7512,36 +6838,42 @@
       <c r="C14">
         <v>0.142205108</v>
       </c>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14">
+      <c r="D14">
+        <v>0.109668182910041</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14">
         <v>0.55169057352857198</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>31.9180285667398</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>1.628292683</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>73.679374999999993</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>0.30718976746298698</v>
       </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15">
+      <c r="D15">
+        <v>0.105302968560265</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="G15">
         <v>15.8650769934215</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B16">
         <v>0.24912069961521999</v>
@@ -7549,42 +6881,48 @@
       <c r="C16">
         <v>0.11911748799999999</v>
       </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16">
+      <c r="D16">
+        <v>0.11043138512520299</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16">
         <v>0.47815170792303902</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>26.1959995510725</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>1.78</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>73.430000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B17">
         <v>0.23799883780685399</v>
       </c>
-      <c r="D17" t="s">
-        <v>26</v>
-      </c>
-      <c r="E17">
+      <c r="C17">
+        <v>0.23090909100000001</v>
+      </c>
+      <c r="D17">
+        <v>0.111413621321598</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17">
         <v>0.97021100240578795</v>
       </c>
-      <c r="F17">
-        <v>94.218748150536896</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B18">
         <v>0.26752308407063402</v>
@@ -7592,19 +6930,19 @@
       <c r="C18">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D18" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18">
+      <c r="D18">
+        <v>0.108806163698834</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18">
         <v>0.87207427654505298</v>
       </c>
-      <c r="F18">
-        <v>115.910838296351</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19">
         <v>0.16056832408994501</v>
@@ -7612,13 +6950,16 @@
       <c r="C19">
         <v>0.23330000000000001</v>
       </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19">
+      <c r="D19">
+        <v>0.11825195959522899</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19">
         <v>1.45296403460818</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>42.614245239660903</v>
       </c>
     </row>
@@ -7631,10 +6972,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7659,30 +7000,27 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2">
-        <v>0.74411257103448103</v>
+        <v>27</v>
       </c>
       <c r="C2">
-        <v>0.116835492</v>
-      </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E2">
-        <v>0.157013194707318</v>
-      </c>
-      <c r="F2">
-        <v>12.0270837749951</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6.096E-2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>0.74411257103448103</v>
@@ -7690,19 +7028,22 @@
       <c r="C3">
         <v>0.116835492</v>
       </c>
-      <c r="D3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E3">
+      <c r="D3">
+        <v>8.7694745966911306E-2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3">
         <v>0.157013194707318</v>
       </c>
-      <c r="F3">
-        <v>11.673900030623701</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>12.0270837749951</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0.74411257103448103</v>
@@ -7710,39 +7051,45 @@
       <c r="C4">
         <v>0.116835492</v>
       </c>
-      <c r="D4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E4">
+      <c r="D4">
+        <v>8.7694745966911306E-2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4">
         <v>0.157013194707318</v>
       </c>
-      <c r="F4">
+      <c r="G4">
+        <v>11.673900030623701</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
+        <v>0.74411257103448103</v>
+      </c>
+      <c r="C5">
+        <v>0.116835492</v>
+      </c>
+      <c r="D5">
+        <v>8.7694745966911306E-2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5">
+        <v>0.157013194707318</v>
+      </c>
+      <c r="G5">
         <v>4.8225004830932496</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5">
-        <v>0.87528110109794</v>
-      </c>
-      <c r="C5">
-        <v>8.9573877999999996E-2</v>
-      </c>
-      <c r="D5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E5">
-        <v>0.10233726957847</v>
-      </c>
-      <c r="F5">
-        <v>2.0901187683293201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6">
         <v>0.87528110109794</v>
@@ -7750,19 +7097,22 @@
       <c r="C6">
         <v>8.9573877999999996E-2</v>
       </c>
-      <c r="D6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6">
+      <c r="D6">
+        <v>7.6126862837703799E-2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6">
         <v>0.10233726957847</v>
       </c>
-      <c r="F6">
-        <v>2.0802072636448998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>2.0901187683293201</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7">
         <v>0.87528110109794</v>
@@ -7770,39 +7120,45 @@
       <c r="C7">
         <v>8.9573877999999996E-2</v>
       </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7">
+      <c r="D7">
+        <v>7.6126862837703799E-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7">
         <v>0.10233726957847</v>
       </c>
-      <c r="F7">
+      <c r="G7">
+        <v>2.0802072636448998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8">
+        <v>0.87528110109794</v>
+      </c>
+      <c r="C8">
+        <v>8.9573877999999996E-2</v>
+      </c>
+      <c r="D8">
+        <v>7.6126862837703799E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8">
+        <v>0.10233726957847</v>
+      </c>
+      <c r="G8">
         <v>3.4348545944842801</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8">
-        <v>1.62598028208757</v>
-      </c>
-      <c r="C8">
-        <v>4.0360477999999998E-2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8">
-        <v>2.48222431997649E-2</v>
-      </c>
-      <c r="F8">
-        <v>11.4435970636991</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B9">
         <v>1.62598028208757</v>
@@ -7810,39 +7166,45 @@
       <c r="C9">
         <v>4.0360477999999998E-2</v>
       </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9">
+      <c r="D9">
+        <v>9.9219554054219006E-3</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9">
         <v>2.48222431997649E-2</v>
       </c>
-      <c r="F9">
+      <c r="G9">
+        <v>11.4435970636991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10">
+        <v>1.62598028208757</v>
+      </c>
+      <c r="C10">
+        <v>4.0360477999999998E-2</v>
+      </c>
+      <c r="D10">
+        <v>9.9219554054219006E-3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10">
+        <v>2.48222431997649E-2</v>
+      </c>
+      <c r="G10">
         <v>5.2429283117314203</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
-        <v>1.32277923770115</v>
-      </c>
-      <c r="C10">
-        <v>3.2272940999999999E-2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10">
-        <v>2.4397828511496002E-2</v>
-      </c>
-      <c r="F10">
-        <v>8.1503583923791698</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11">
         <v>1.32277923770115</v>
@@ -7850,161 +7212,275 @@
       <c r="C11">
         <v>3.2272940999999999E-2</v>
       </c>
-      <c r="D11" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11">
+      <c r="D11">
+        <v>3.6661557079839702E-2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11">
         <v>2.4397828511496002E-2</v>
       </c>
-      <c r="F11">
+      <c r="G11">
+        <v>8.1503583923791698</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12">
+        <v>1.32277923770115</v>
+      </c>
+      <c r="C12">
+        <v>3.2272940999999999E-2</v>
+      </c>
+      <c r="D12">
+        <v>3.6661557079839702E-2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12">
+        <v>2.4397828511496002E-2</v>
+      </c>
+      <c r="G12">
         <v>22.095712310493202</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12">
-        <v>1.0535668624027901</v>
-      </c>
-      <c r="C12">
-        <v>5.4257143000000001E-2</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12">
-        <v>5.1498528414475699E-2</v>
-      </c>
-      <c r="F12">
-        <v>5.8251150947610704</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B13">
-        <v>0.78894922945176305</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13">
-        <v>6.4381260228580199</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>4.4325555000000003E-2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
       <c r="B14">
+        <v>1.0535668624027901</v>
+      </c>
+      <c r="C14">
+        <v>5.4257143000000001E-2</v>
+      </c>
+      <c r="D14">
+        <v>6.0403664221553403E-2</v>
+      </c>
+      <c r="E14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14">
+        <v>5.1498528414475699E-2</v>
+      </c>
+      <c r="G14">
+        <v>5.8251150947610704</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>0.78894922945176305</v>
+      </c>
+      <c r="D15">
+        <v>8.3740556465630903E-2</v>
+      </c>
+      <c r="E15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15">
+        <v>6.4381260228580199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16">
         <v>0.73759563320647703</v>
       </c>
-      <c r="C14">
+      <c r="C16">
         <v>0.137964795</v>
       </c>
-      <c r="D14" t="s">
-        <v>41</v>
-      </c>
-      <c r="E14">
+      <c r="D16">
+        <v>8.8269481195842894E-2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16">
         <v>0.18704665373388801</v>
       </c>
-      <c r="F14">
+      <c r="G16">
         <v>5.5662125718823496</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15">
-        <v>0.73062868871751996</v>
-      </c>
-      <c r="C15">
-        <v>0.14825882000000001</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15">
-        <v>0.202919516150181</v>
-      </c>
-      <c r="F15">
-        <v>5.1949848895037301</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
-        <v>0.73062868871751996</v>
-      </c>
-      <c r="C16">
-        <v>0.14825882000000001</v>
-      </c>
-      <c r="D16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16">
-        <v>0.202919516150181</v>
-      </c>
-      <c r="F16">
-        <v>5.1262681581610803</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>37</v>
       </c>
+      <c r="B17">
+        <v>0.73062868871751996</v>
+      </c>
       <c r="C17">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E17">
-        <v>1.6423830418461599E-2</v>
+        <v>0.14825882000000001</v>
+      </c>
+      <c r="D17">
+        <v>8.8883902959789998E-2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
       </c>
       <c r="F17">
-        <v>-163.072100172185</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.202919516150181</v>
+      </c>
+      <c r="G17">
+        <v>5.1949848895037301</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
+      <c r="B18">
+        <v>0.73062868871751996</v>
+      </c>
       <c r="C18">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>41</v>
-      </c>
-      <c r="E18">
-        <v>1.6423830418461599E-2</v>
+        <v>0.14825882000000001</v>
+      </c>
+      <c r="D18">
+        <v>8.8883902959789998E-2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
       </c>
       <c r="F18">
-        <v>-157.05714565763799</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0.202919516150181</v>
+      </c>
+      <c r="G18">
+        <v>5.1262681581610803</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="B19">
+        <v>0.74233596483651698</v>
       </c>
       <c r="C19">
         <v>1.2192E-2</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19">
+        <v>8.7851426634558596E-2</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19">
+        <v>1.6423830418461599E-2</v>
+      </c>
+      <c r="G19">
+        <v>-163.072100172185</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20">
+        <v>0.74233596483651698</v>
+      </c>
+      <c r="C20">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="D20">
+        <v>8.7851426634558596E-2</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20">
+        <v>1.6423830418461599E-2</v>
+      </c>
+      <c r="G20">
+        <v>-157.05714565763799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21">
+        <v>0.74233596483651698</v>
+      </c>
+      <c r="C21">
+        <v>1.2192E-2</v>
+      </c>
+      <c r="D21">
+        <v>8.7851426634558596E-2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21">
+        <v>1.6423830418461599E-2</v>
+      </c>
+      <c r="G21">
+        <v>53.487681099100698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22">
+        <v>0.104457388</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="G22" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>41</v>
       </c>
-      <c r="E19">
-        <v>1.6423830418461599E-2</v>
-      </c>
-      <c r="F19">
-        <v>53.487681099100698</v>
+      <c r="C23">
+        <v>0.119632672</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24">
+        <v>0.125639851</v>
+      </c>
+      <c r="E24" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" t="e">
+        <v>#NUM!</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samanthahowley\Desktop\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AC1A98-805B-4CA3-825B-5FD4C8DAED3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD267F9-7AAB-430D-B56F-7192AC8B22A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25080" yWindow="-3480" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="8">
   <si>
     <t>Date</t>
   </si>
@@ -32,146 +32,43 @@
     <t>depth</t>
   </si>
   <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>velocity</t>
-  </si>
-  <si>
     <t>ID</t>
-  </si>
-  <si>
-    <t>uh</t>
   </si>
   <si>
     <t>k600_1.day</t>
   </si>
   <si>
-    <t>VentDO</t>
-  </si>
-  <si>
-    <t>VentTemp</t>
-  </si>
-  <si>
-    <t>1/3/2023</t>
-  </si>
-  <si>
     <t>AM</t>
-  </si>
-  <si>
-    <t>1/18/2023</t>
-  </si>
-  <si>
-    <t>2/1/2023</t>
-  </si>
-  <si>
-    <t>2/15/2023</t>
-  </si>
-  <si>
-    <t>3/29/2023</t>
-  </si>
-  <si>
-    <t>4/12/2023</t>
-  </si>
-  <si>
-    <t>4/26/2023</t>
-  </si>
-  <si>
-    <t>5/29/2023</t>
-  </si>
-  <si>
-    <t>11/7/2022</t>
-  </si>
-  <si>
-    <t>11/21/2022</t>
-  </si>
-  <si>
-    <t>12/5/2022</t>
-  </si>
-  <si>
-    <t>12/19/2022</t>
   </si>
   <si>
     <t>GB</t>
   </si>
   <si>
-    <t>3/1/2023</t>
-  </si>
-  <si>
-    <t>3/15/2023</t>
-  </si>
-  <si>
-    <t>10/24/2022</t>
-  </si>
-  <si>
-    <t>12/20/2022</t>
-  </si>
-  <si>
-    <t>1/4/2023</t>
-  </si>
-  <si>
     <t>LF</t>
   </si>
   <si>
-    <t>1/11/2023</t>
-  </si>
-  <si>
-    <t>1/25/2023</t>
-  </si>
-  <si>
-    <t>2/6/2023</t>
-  </si>
-  <si>
-    <t>2/22/2023</t>
-  </si>
-  <si>
-    <t>3/8/2023</t>
-  </si>
-  <si>
-    <t>4/5/2023</t>
-  </si>
-  <si>
-    <t>4/19/2023</t>
-  </si>
-  <si>
-    <t>5/3/2023</t>
-  </si>
-  <si>
-    <t>5/17/2023</t>
-  </si>
-  <si>
-    <t>5/30/2023</t>
-  </si>
-  <si>
-    <t>10/31/2022</t>
-  </si>
-  <si>
-    <t>11/14/2022</t>
-  </si>
-  <si>
-    <t>11/28/2022</t>
-  </si>
-  <si>
-    <t>12/12/2022</t>
-  </si>
-  <si>
     <t>OS</t>
-  </si>
-  <si>
-    <t>3/20/2023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -194,8 +91,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -268,7 +166,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>AM!$G$1</c:f>
+              <c:f>AM!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -299,6 +197,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>AM!$B$2:$B$32</c:f>
@@ -400,7 +312,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>AM!$G$2:$G$32</c:f>
+              <c:f>AM!$D$2:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
@@ -469,9 +381,6 @@
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>32.6657378105105</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>8.0612152297113795</c:v>
@@ -500,7 +409,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C8C1-470E-B95C-FC31B64AD9C3}"/>
+              <c16:uniqueId val="{00000000-8E08-4FCE-B184-F8BB4AAE55CA}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -512,11 +421,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="549210224"/>
-        <c:axId val="405510960"/>
+        <c:axId val="790405791"/>
+        <c:axId val="790411071"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="549210224"/>
+        <c:axId val="790405791"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -573,12 +482,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="405510960"/>
+        <c:crossAx val="790411071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="405510960"/>
+        <c:axId val="790411071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -635,7 +544,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="549210224"/>
+        <c:crossAx val="790405791"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -746,7 +655,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>GB!$G$1</c:f>
+              <c:f>GB!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -777,6 +686,20 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
           <c:xVal>
             <c:numRef>
               <c:f>GB!$B$2:$B$29</c:f>
@@ -869,7 +792,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$G$2:$G$29</c:f>
+              <c:f>GB!$D$2:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="28"/>
@@ -951,7 +874,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-57DB-4077-93E9-A3A99C7244D8}"/>
+              <c16:uniqueId val="{00000000-DCD4-47E7-9F46-B167D36B0401}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -963,11 +886,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="697174239"/>
-        <c:axId val="697173759"/>
+        <c:axId val="790408191"/>
+        <c:axId val="790401951"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="697174239"/>
+        <c:axId val="790408191"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1024,12 +947,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697173759"/>
+        <c:crossAx val="790401951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="697173759"/>
+        <c:axId val="790401951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1086,7 +1009,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697174239"/>
+        <c:crossAx val="790408191"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1197,7 +1120,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>ID!$G$1</c:f>
+              <c:f>ID!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1295,7 +1218,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ID!$G$2:$G$16</c:f>
+              <c:f>ID!$D$2:$D$16</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -1350,7 +1273,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5117-45FA-8FA4-CFA9B7EE1592}"/>
+              <c16:uniqueId val="{00000000-AA68-4551-A4ED-4716C3F7ADEE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1362,11 +1285,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="697163679"/>
-        <c:axId val="697180479"/>
+        <c:axId val="790460511"/>
+        <c:axId val="790460991"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="697163679"/>
+        <c:axId val="790460511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1423,12 +1346,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697180479"/>
+        <c:crossAx val="790460991"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="697180479"/>
+        <c:axId val="790460991"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1485,7 +1408,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697163679"/>
+        <c:crossAx val="790460511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1587,17 +1510,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.3136482939632545E-2"/>
-          <c:y val="2.5428331875182269E-2"/>
-          <c:w val="0.87437751531058616"/>
-          <c:h val="0.72088764946048411"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1606,7 +1519,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>LF!$G$1</c:f>
+              <c:f>LF!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1716,7 +1629,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>LF!$G$2:$G$19</c:f>
+              <c:f>LF!$D$2:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
@@ -1726,6 +1639,9 @@
                 <c:pt idx="1">
                   <c:v>23.148382126467901</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>118.259222088889</c:v>
+                </c:pt>
                 <c:pt idx="3">
                   <c:v>50.954752325421801</c:v>
                 </c:pt>
@@ -1735,9 +1651,15 @@
                 <c:pt idx="5">
                   <c:v>9.5554623120508193</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>12.1601192837523</c:v>
+                </c:pt>
                 <c:pt idx="7">
                   <c:v>7.9516472320781002</c:v>
                 </c:pt>
+                <c:pt idx="8">
+                  <c:v>30.7702058957052</c:v>
+                </c:pt>
                 <c:pt idx="9">
                   <c:v>34.983383524448797</c:v>
                 </c:pt>
@@ -1755,6 +1677,12 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>26.1959995510725</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>94.218748150536896</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>115.910838296351</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>42.614245239660903</c:v>
@@ -1765,7 +1693,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BCF6-48DA-A0D6-4E04D3B3490E}"/>
+              <c16:uniqueId val="{00000000-078D-4AF8-95D0-AEC7CAD7A4B9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1777,11 +1705,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="697191519"/>
-        <c:axId val="697203999"/>
+        <c:axId val="736366095"/>
+        <c:axId val="736403055"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="697191519"/>
+        <c:axId val="736366095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1838,12 +1766,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697203999"/>
+        <c:crossAx val="736403055"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="697203999"/>
+        <c:axId val="736403055"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1900,7 +1828,404 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="697191519"/>
+        <c:crossAx val="736366095"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>OS!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>k600_1.day</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>OS!$B$2:$B$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="1">
+                  <c:v>0.74411257103448103</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.74411257103448103</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.74411257103448103</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.87528110109794</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.87528110109794</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.87528110109794</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.62598028208757</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.62598028208757</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.32277923770115</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.32277923770115</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0535668624027901</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.78894922945176305</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.73759563320647703</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.73062868871751996</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.73062868871751996</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.74233596483651698</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.74233596483651698</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.74233596483651698</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>OS!$D$2:$D$24</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="1">
+                  <c:v>12.0270837749951</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.673900030623701</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8225004830932496</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.0901187683293201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.0802072636448998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.4348545944842801</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11.4435970636991</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5.2429283117314203</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.1503583923791698</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>22.095712310493202</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5.8251150947610704</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>6.4381260228580199</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5.5662125718823496</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.1949848895037301</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5.1262681581610803</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F822-4C65-9F39-07E7A2261092}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="790448511"/>
+        <c:axId val="790434111"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="790448511"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="790434111"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="790434111"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="790448511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2116,6 +2441,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -4180,27 +4545,543 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>109537</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3638D75B-E76D-60AA-0E9B-08682A93FCF5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119E926F-0970-A21B-C4D1-1DAC5673F1D7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4227,21 +5108,21 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B612589B-EF37-7A1C-3658-9DE4832C1E91}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCD8786-89E2-7E2C-F308-8422A9649FD9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4268,21 +5149,21 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>128587</xdr:rowOff>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F56FE988-7D8D-F7AD-1677-E0FAAEFB0B4F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95567553-5376-4F57-872C-B00663ADF10E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4307,23 +5188,64 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>481012</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFC4F6AC-1CCE-ED2D-1CFC-5D027CE7CB51}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECAF12D-F437-BF75-16E0-B3FBC5DBE18E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFE4EA57-7C85-80AE-1989-24A5BD379E0A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4623,10 +5545,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4639,772 +5561,430 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>44929</v>
       </c>
       <c r="B2">
         <v>0.66360277136277601</v>
       </c>
-      <c r="C2">
-        <v>0.41148000000000001</v>
+      <c r="C2" t="s">
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>0.36972856114008101</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
-        <v>0.62006974316123398</v>
-      </c>
-      <c r="G2">
         <v>8.7000179355782503</v>
       </c>
-      <c r="H2">
-        <v>1.5</v>
-      </c>
-      <c r="I2">
-        <v>71.992540000000005</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>44929</v>
       </c>
       <c r="B3">
         <v>0.66360277136277601</v>
       </c>
-      <c r="C3">
-        <v>0.41148000000000001</v>
+      <c r="C3" t="s">
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>0.36972856114008101</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>0.62006974316123398</v>
-      </c>
-      <c r="G3">
         <v>14.0537866274825</v>
       </c>
-      <c r="H3">
-        <v>1.5</v>
-      </c>
-      <c r="I3">
-        <v>71.992540000000005</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44944</v>
       </c>
       <c r="B4">
         <v>0.84496568832957797</v>
       </c>
-      <c r="C4">
-        <v>0.41148000000000001</v>
+      <c r="C4" t="s">
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>0.31614251553411798</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4">
-        <v>0.48697835389441602</v>
-      </c>
-      <c r="G4">
         <v>14.2509884099436</v>
       </c>
-      <c r="H4">
-        <v>1.097</v>
-      </c>
-      <c r="I4">
-        <v>71.486959999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>44944</v>
       </c>
       <c r="B5">
         <v>0.84496568832957797</v>
       </c>
-      <c r="C5">
-        <v>0.41148000000000001</v>
+      <c r="C5" t="s">
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>0.31614251553411798</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5">
-        <v>0.48697835389441602</v>
-      </c>
-      <c r="G5">
         <v>14.019548098025901</v>
       </c>
-      <c r="H5">
-        <v>1.097</v>
-      </c>
-      <c r="I5">
-        <v>71.486959999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44944</v>
       </c>
       <c r="B6">
         <v>0.84496568832957797</v>
       </c>
-      <c r="C6">
-        <v>0.41148000000000001</v>
+      <c r="C6" t="s">
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>0.31614251553411798</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>0.48697835389441602</v>
-      </c>
-      <c r="G6">
         <v>17.9748429691486</v>
       </c>
-      <c r="H6">
-        <v>1.097</v>
-      </c>
-      <c r="I6">
-        <v>71.486959999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>44958</v>
       </c>
       <c r="B7">
         <v>1.79712100240526</v>
       </c>
-      <c r="C7">
-        <v>9.6864407E-2</v>
+      <c r="C7" t="s">
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>3.4815776102823201E-2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>5.38997690585983E-2</v>
-      </c>
-      <c r="G7">
         <v>1.3659747293628499</v>
       </c>
-      <c r="I7">
-        <v>71.140784310000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>44958</v>
       </c>
       <c r="B8">
         <v>1.79712100240526</v>
       </c>
-      <c r="C8">
-        <v>9.6864407E-2</v>
+      <c r="C8" t="s">
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>3.4815776102823201E-2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>5.38997690585983E-2</v>
-      </c>
-      <c r="G8">
         <v>1.43477614979118</v>
       </c>
-      <c r="I8">
-        <v>71.140784310000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>44972</v>
       </c>
       <c r="B9">
         <v>1.91936208989603</v>
       </c>
-      <c r="C9">
-        <v>2.5907667999999998E-2</v>
+      <c r="C9" t="s">
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>-1.30195181397141E-3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9">
-        <v>1.34980617447766E-2</v>
-      </c>
-      <c r="G9">
         <v>0.762817767337299</v>
       </c>
-      <c r="H9">
-        <v>1.288</v>
-      </c>
-      <c r="I9">
-        <v>71.42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>44972</v>
       </c>
       <c r="B10">
         <v>1.91936208989603</v>
       </c>
-      <c r="C10">
-        <v>2.5907667999999998E-2</v>
+      <c r="C10" t="s">
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>-1.30195181397141E-3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10">
-        <v>1.34980617447766E-2</v>
-      </c>
-      <c r="G10">
         <v>0.954970513126703</v>
       </c>
-      <c r="H10">
-        <v>1.288</v>
-      </c>
-      <c r="I10">
-        <v>71.42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45014</v>
       </c>
       <c r="B11">
         <v>1.5364118092654899</v>
       </c>
-      <c r="C11">
-        <v>0.111489093</v>
+      <c r="C11" t="s">
+        <v>4</v>
       </c>
       <c r="D11">
-        <v>0.111845716661391</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>7.25645899931604E-2</v>
-      </c>
-      <c r="G11">
         <v>3.2531836035536301</v>
       </c>
-      <c r="H11">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45014</v>
       </c>
       <c r="B12">
         <v>1.5364118092654899</v>
       </c>
-      <c r="C12">
-        <v>0.111489093</v>
+      <c r="C12" t="s">
+        <v>4</v>
       </c>
       <c r="D12">
-        <v>0.111845716661391</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12">
-        <v>7.25645899931604E-2</v>
-      </c>
-      <c r="G12">
         <v>2.4433323290317999</v>
       </c>
-      <c r="H12">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45014</v>
       </c>
       <c r="B13">
         <v>1.5364118092654899</v>
       </c>
-      <c r="C13">
-        <v>0.111489093</v>
+      <c r="C13" t="s">
+        <v>4</v>
       </c>
       <c r="D13">
-        <v>0.111845716661391</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13">
-        <v>7.25645899931604E-2</v>
-      </c>
-      <c r="G13">
         <v>2.43040464475121</v>
       </c>
-      <c r="H13">
-        <v>1.26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>15</v>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45028</v>
       </c>
       <c r="B14">
         <v>1.14254792657094</v>
       </c>
-      <c r="C14">
-        <v>8.1843182E-2</v>
+      <c r="C14" t="s">
+        <v>4</v>
       </c>
       <c r="D14">
-        <v>0.22821795159007199</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <v>7.1632165353124999E-2</v>
-      </c>
-      <c r="G14">
         <v>7.0432970693483599</v>
       </c>
-      <c r="I14">
-        <v>72.604545450000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>15</v>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45028</v>
       </c>
       <c r="B15">
         <v>1.14254792657094</v>
       </c>
-      <c r="C15">
-        <v>8.1843182E-2</v>
+      <c r="C15" t="s">
+        <v>4</v>
       </c>
       <c r="D15">
-        <v>0.22821795159007199</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>7.1632165353124999E-2</v>
-      </c>
-      <c r="G15">
         <v>2.7839849332143101</v>
       </c>
-      <c r="I15">
-        <v>72.604545450000003</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>15</v>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45028</v>
       </c>
       <c r="B16">
         <v>1.14254792657094</v>
       </c>
-      <c r="C16">
-        <v>8.1843182E-2</v>
+      <c r="C16" t="s">
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>0.22821795159007199</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>7.1632165353124999E-2</v>
-      </c>
-      <c r="G16">
         <v>2.7892918049894102</v>
       </c>
-      <c r="I16">
-        <v>72.604545450000003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45042</v>
       </c>
       <c r="B17">
         <v>0.76948902444658396</v>
       </c>
-      <c r="C17">
-        <v>0.24384</v>
+      <c r="C17" t="s">
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>0.33844308293048597</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17">
-        <v>0.31688561142944099</v>
-      </c>
-      <c r="G17">
         <v>7.6754733355837299</v>
       </c>
-      <c r="I17">
-        <v>73.478181820000003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45050</v>
+      </c>
       <c r="B18">
         <v>0.74683198736593104</v>
       </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
       <c r="D18">
-        <v>0.34513740083518801</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18">
         <v>22.624195858075399</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45050</v>
+      </c>
       <c r="B19">
         <v>0.74683198736593104</v>
       </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
       <c r="D19">
-        <v>0.34513740083518801</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19">
         <v>22.5657731444328</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45064</v>
+      </c>
       <c r="B20">
         <v>0.634197514012805</v>
       </c>
+      <c r="C20" t="s">
+        <v>4</v>
+      </c>
       <c r="D20">
-        <v>0.37841672897374601</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20">
         <v>16.1504080056141</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>17</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45075</v>
       </c>
       <c r="B21">
         <v>0.81193724612891904</v>
       </c>
-      <c r="C21">
-        <v>0.26351463400000003</v>
+      <c r="C21" t="s">
+        <v>4</v>
       </c>
       <c r="D21">
-        <v>0.32590120071440998</v>
-      </c>
-      <c r="E21" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21">
-        <v>0.32455049359585503</v>
-      </c>
-      <c r="G21">
         <v>7.76777594040046</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>17</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45075</v>
       </c>
       <c r="B22">
         <v>0.81193724612891904</v>
       </c>
-      <c r="C22">
-        <v>0.26351463400000003</v>
+      <c r="C22" t="s">
+        <v>4</v>
       </c>
       <c r="D22">
-        <v>0.32590120071440998</v>
-      </c>
-      <c r="E22" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22">
-        <v>0.32455049359585503</v>
-      </c>
-      <c r="G22">
         <v>11.6535292051355</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45086</v>
+      </c>
       <c r="B23">
         <v>0.64229622161300404</v>
       </c>
+      <c r="C23" t="s">
+        <v>4</v>
+      </c>
       <c r="D23">
-        <v>0.37602385990176701</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23">
         <v>32.6657378105105</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>45086</v>
+      </c>
       <c r="B24">
         <v>0.64229622161300404</v>
       </c>
-      <c r="D24">
-        <v>0.37602385990176701</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25">
-        <v>0.32508800599999998</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="H25">
-        <v>1.0900000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>19</v>
+      <c r="C24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>44872</v>
+      </c>
+      <c r="C25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>44886</v>
       </c>
       <c r="B26">
         <v>0.66551573852542301</v>
       </c>
-      <c r="C26">
-        <v>0.24384</v>
+      <c r="C26" t="s">
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>0.36916334997489503</v>
-      </c>
-      <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26">
-        <v>0.36639253722274701</v>
-      </c>
-      <c r="G26">
         <v>8.0612152297113795</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>19</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>44886</v>
       </c>
       <c r="B27">
         <v>0.66551573852542301</v>
       </c>
-      <c r="C27">
-        <v>0.24384</v>
+      <c r="C27" t="s">
+        <v>4</v>
       </c>
       <c r="D27">
-        <v>0.36916334997489503</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27">
-        <v>0.36639253722274701</v>
-      </c>
-      <c r="G27">
         <v>7.8631523559558696</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>19</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>44886</v>
       </c>
       <c r="B28">
         <v>0.66551573852542301</v>
       </c>
-      <c r="C28">
-        <v>0.24384</v>
+      <c r="C28" t="s">
+        <v>4</v>
       </c>
       <c r="D28">
-        <v>0.36916334997489503</v>
-      </c>
-      <c r="E28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28">
-        <v>0.36639253722274701</v>
-      </c>
-      <c r="G28">
         <v>30.1775506886923</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>20</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>44900</v>
       </c>
       <c r="B29">
         <v>0.66831711482098599</v>
       </c>
-      <c r="C29">
-        <v>0.392848743</v>
+      <c r="C29" t="s">
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>0.368335646713147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29">
-        <v>0.587817870121772</v>
-      </c>
-      <c r="G29">
         <v>23.531152831216499</v>
       </c>
-      <c r="H29">
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="I29">
-        <v>71.94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>20</v>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>44900</v>
       </c>
       <c r="B30">
         <v>0.66831711482098599</v>
       </c>
-      <c r="C30">
-        <v>0.392848743</v>
+      <c r="C30" t="s">
+        <v>4</v>
       </c>
       <c r="D30">
-        <v>0.368335646713147</v>
-      </c>
-      <c r="E30" t="s">
-        <v>10</v>
-      </c>
-      <c r="F30">
-        <v>0.587817870121772</v>
-      </c>
-      <c r="G30">
         <v>18.703245444769301</v>
       </c>
-      <c r="H30">
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="I30">
-        <v>71.94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>21</v>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>44914</v>
       </c>
       <c r="B31">
         <v>0.65580679181917101</v>
       </c>
-      <c r="C31">
-        <v>0.392848743</v>
+      <c r="C31" t="s">
+        <v>4</v>
       </c>
       <c r="D31">
-        <v>0.372031985248788</v>
-      </c>
-      <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31">
-        <v>0.59903122062865499</v>
-      </c>
-      <c r="G31">
         <v>15.9745813671168</v>
       </c>
-      <c r="H31">
-        <v>1.42</v>
-      </c>
-      <c r="I31">
-        <v>71.942899999999995</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>21</v>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>44914</v>
       </c>
       <c r="B32">
         <v>0.65580679181917101</v>
       </c>
-      <c r="C32">
-        <v>0.392848743</v>
+      <c r="C32" t="s">
+        <v>4</v>
       </c>
       <c r="D32">
-        <v>0.372031985248788</v>
-      </c>
-      <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32">
-        <v>0.59903122062865499</v>
-      </c>
-      <c r="G32">
         <v>17.496680423021001</v>
-      </c>
-      <c r="H32">
-        <v>1.42</v>
-      </c>
-      <c r="I32">
-        <v>71.942899999999995</v>
       </c>
     </row>
   </sheetData>
@@ -5416,10 +5996,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5432,687 +6012,381 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>44929</v>
       </c>
       <c r="B2">
         <v>0.500234239386116</v>
       </c>
-      <c r="C2">
-        <v>0.13716</v>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
       <c r="D2">
-        <v>0.15821662988639301</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>0.27419154708066701</v>
-      </c>
-      <c r="G2">
         <v>8.0617713895940106</v>
       </c>
-      <c r="H2">
-        <v>6.25</v>
-      </c>
-      <c r="I2">
-        <v>72.545299999999997</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>44929</v>
       </c>
       <c r="B3">
         <v>0.500234239386116</v>
       </c>
-      <c r="C3">
-        <v>0.13716</v>
+      <c r="C3" t="s">
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>0.15821662988639301</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>0.27419154708066701</v>
-      </c>
-      <c r="G3">
         <v>8.0092423263314494</v>
       </c>
-      <c r="H3">
-        <v>6.25</v>
-      </c>
-      <c r="I3">
-        <v>72.545299999999997</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44929</v>
       </c>
       <c r="B4">
         <v>0.500234239386116</v>
       </c>
-      <c r="C4">
-        <v>0.13716</v>
+      <c r="C4" t="s">
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>0.15821662988639301</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>0.27419154708066701</v>
-      </c>
-      <c r="G4">
         <v>20.759702379649699</v>
       </c>
-      <c r="H4">
-        <v>6.25</v>
-      </c>
-      <c r="I4">
-        <v>72.545299999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>11</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>44944</v>
       </c>
       <c r="B5">
         <v>0.49838619196324002</v>
       </c>
-      <c r="C5">
-        <v>0.195072</v>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0.15917946283117099</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5">
-        <v>0.39140731253322603</v>
-      </c>
-      <c r="G5">
         <v>11.7604829329048</v>
       </c>
-      <c r="H5">
-        <v>4.8</v>
-      </c>
-      <c r="I5">
-        <v>73.188749999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44944</v>
       </c>
       <c r="B6">
         <v>0.49838619196324002</v>
       </c>
-      <c r="C6">
-        <v>0.195072</v>
+      <c r="C6" t="s">
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>0.15917946283117099</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>0.39140731253322603</v>
-      </c>
-      <c r="G6">
         <v>11.63069034185</v>
       </c>
-      <c r="H6">
-        <v>4.8</v>
-      </c>
-      <c r="I6">
-        <v>73.188749999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>12</v>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>44958</v>
       </c>
       <c r="B7">
         <v>0.496481994488156</v>
       </c>
-      <c r="C7">
-        <v>0.18592800000000001</v>
+      <c r="C7" t="s">
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>0.16017154996036501</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7">
-        <v>0.37449092225727298</v>
-      </c>
-      <c r="G7">
         <v>16.082464877533099</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>44958</v>
       </c>
       <c r="B8">
         <v>0.496481994488156</v>
       </c>
-      <c r="C8">
-        <v>0.18592800000000001</v>
+      <c r="C8" t="s">
+        <v>5</v>
       </c>
       <c r="D8">
-        <v>0.16017154996036501</v>
-      </c>
-      <c r="E8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8">
-        <v>0.37449092225727298</v>
-      </c>
-      <c r="G8">
         <v>19.278549967453198</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>13</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>44972</v>
       </c>
       <c r="B9">
         <v>0.49364073113116103</v>
       </c>
-      <c r="C9">
-        <v>0.176784</v>
+      <c r="C9" t="s">
+        <v>5</v>
       </c>
       <c r="D9">
-        <v>0.16165184853443901</v>
-      </c>
-      <c r="E9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9">
-        <v>0.35812279832522198</v>
-      </c>
-      <c r="G9">
         <v>18.3266040851639</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>44972</v>
       </c>
       <c r="B10">
         <v>0.49364073113116103</v>
       </c>
-      <c r="C10">
-        <v>0.176784</v>
+      <c r="C10" t="s">
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>0.16165184853443901</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10">
-        <v>0.35812279832522198</v>
-      </c>
-      <c r="G10">
         <v>18.238219059268399</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>13</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>44972</v>
       </c>
       <c r="B11">
         <v>0.49364073113116103</v>
       </c>
-      <c r="C11">
-        <v>0.176784</v>
+      <c r="C11" t="s">
+        <v>5</v>
       </c>
       <c r="D11">
-        <v>0.16165184853443901</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11">
-        <v>0.35812279832522198</v>
-      </c>
-      <c r="G11">
         <v>15.8324828082942</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>44986</v>
       </c>
       <c r="B12">
         <v>0.48014251849385198</v>
       </c>
-      <c r="C12">
-        <v>0.20116800000000001</v>
+      <c r="C12" t="s">
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>0.168684419052893</v>
-      </c>
-      <c r="E12" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12">
-        <v>0.418975600475957</v>
-      </c>
-      <c r="G12">
         <v>12.5427239203201</v>
       </c>
-      <c r="H12">
-        <v>5.58</v>
-      </c>
-      <c r="I12">
-        <v>73.188749999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>23</v>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>44986</v>
       </c>
       <c r="B13">
         <v>0.48014251849385198</v>
       </c>
-      <c r="C13">
-        <v>0.20116800000000001</v>
+      <c r="C13" t="s">
+        <v>5</v>
       </c>
       <c r="D13">
-        <v>0.168684419052893</v>
-      </c>
-      <c r="E13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13">
-        <v>0.418975600475957</v>
-      </c>
-      <c r="G13">
         <v>10.123963721124101</v>
       </c>
-      <c r="H13">
-        <v>5.58</v>
-      </c>
-      <c r="I13">
-        <v>73.188749999999999</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>23</v>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>44986</v>
       </c>
       <c r="B14">
         <v>0.48014251849385198</v>
       </c>
-      <c r="C14">
-        <v>0.20116800000000001</v>
+      <c r="C14" t="s">
+        <v>5</v>
       </c>
       <c r="D14">
-        <v>0.168684419052893</v>
-      </c>
-      <c r="E14" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14">
-        <v>0.418975600475957</v>
-      </c>
-      <c r="G14">
         <v>9.9882836327260591</v>
       </c>
-      <c r="H14">
-        <v>5.58</v>
-      </c>
-      <c r="I14">
-        <v>73.188749999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>24</v>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45000</v>
       </c>
       <c r="B15">
         <v>0.48738009477924898</v>
       </c>
-      <c r="C15">
-        <v>0.20319999999999999</v>
+      <c r="C15" t="s">
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>0.16491364087822899</v>
-      </c>
-      <c r="E15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15">
-        <v>0.41692305897727699</v>
-      </c>
-      <c r="G15">
         <v>15.491084387970799</v>
       </c>
-      <c r="H15">
-        <v>4.6849999999999996</v>
-      </c>
-      <c r="I15">
-        <v>72.484999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>24</v>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45000</v>
       </c>
       <c r="B16">
         <v>0.48738009477924898</v>
       </c>
-      <c r="C16">
-        <v>0.20319999999999999</v>
+      <c r="C16" t="s">
+        <v>5</v>
       </c>
       <c r="D16">
-        <v>0.16491364087822899</v>
-      </c>
-      <c r="E16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16">
-        <v>0.41692305897727699</v>
-      </c>
-      <c r="G16">
         <v>15.422189134531401</v>
       </c>
-      <c r="H16">
-        <v>4.6849999999999996</v>
-      </c>
-      <c r="I16">
-        <v>72.484999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45014</v>
       </c>
       <c r="B17">
         <v>0.46633139234925403</v>
       </c>
-      <c r="C17">
-        <v>0.1016</v>
+      <c r="C17" t="s">
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>0.17588001754885099</v>
-      </c>
-      <c r="E17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17">
-        <v>0.21787081390374799</v>
-      </c>
-      <c r="G17">
         <v>28.8790872259084</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>15</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45028</v>
       </c>
       <c r="B18">
         <v>0.44959398748926399</v>
       </c>
-      <c r="C18">
-        <v>0.140208</v>
+      <c r="C18" t="s">
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>0.18460020763153301</v>
-      </c>
-      <c r="E18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18">
-        <v>0.31185470424768102</v>
-      </c>
-      <c r="G18">
         <v>31.877696149374302</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>45042</v>
       </c>
       <c r="B19">
         <v>0.42847041975631001</v>
       </c>
-      <c r="C19">
-        <v>0.17526</v>
+      <c r="C19" t="s">
+        <v>5</v>
       </c>
       <c r="D19">
-        <v>0.19560558913461701</v>
-      </c>
-      <c r="E19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19">
-        <v>0.40903640465934199</v>
-      </c>
-      <c r="G19">
         <v>32.379700829916601</v>
       </c>
-      <c r="H19">
-        <v>4.6849999999999996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>45042</v>
       </c>
       <c r="B20">
         <v>0.42847041975631001</v>
       </c>
-      <c r="C20">
-        <v>0.17526</v>
+      <c r="C20" t="s">
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>0.19560558913461701</v>
-      </c>
-      <c r="E20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20">
-        <v>0.40903640465934199</v>
-      </c>
-      <c r="G20">
         <v>32.274144438345303</v>
       </c>
-      <c r="H20">
-        <v>4.6849999999999996</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>45064</v>
+      </c>
       <c r="B21">
         <v>0.40867897602588799</v>
       </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
       <c r="D21">
-        <v>0.20591693386121401</v>
-      </c>
-      <c r="E21" t="s">
-        <v>22</v>
-      </c>
-      <c r="G21">
         <v>19.545410722183501</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>45064</v>
+      </c>
       <c r="B22">
         <v>0.40867897602588799</v>
       </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
       <c r="D22">
-        <v>0.20591693386121401</v>
-      </c>
-      <c r="E22" t="s">
-        <v>22</v>
-      </c>
-      <c r="G22">
         <v>19.3542063534147</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>45075</v>
+      </c>
       <c r="B23">
         <v>0.41829191635495</v>
       </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
       <c r="D23">
-        <v>0.200908590714584</v>
-      </c>
-      <c r="E23" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23">
         <v>21.2301041068087</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>25</v>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>44858</v>
       </c>
       <c r="B24">
         <v>0.57001899623787999</v>
       </c>
-      <c r="C24">
-        <v>9.0498811999999998E-2</v>
-      </c>
-      <c r="D24">
-        <v>0.12185876259982401</v>
-      </c>
-      <c r="E24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24">
-        <v>0.15876455451009799</v>
-      </c>
-      <c r="H24">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="I24">
-        <v>72.918940000000006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25">
-        <v>7.4432234E-2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>19</v>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>44872</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>44886</v>
       </c>
       <c r="B26">
         <v>0.55068895347565805</v>
       </c>
-      <c r="C26">
-        <v>0.132051846</v>
-      </c>
-      <c r="D26">
-        <v>0.13192971736270201</v>
-      </c>
-      <c r="E26" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26">
-        <v>0.239793889393565</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>19</v>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>44886</v>
       </c>
       <c r="B27">
         <v>0.55068895347565805</v>
       </c>
-      <c r="C27">
-        <v>0.132051846</v>
-      </c>
-      <c r="D27">
-        <v>0.13192971736270201</v>
-      </c>
-      <c r="E27" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27">
-        <v>0.239793889393565</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>20</v>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>44900</v>
       </c>
       <c r="B28">
         <v>0.52913409322569804</v>
       </c>
-      <c r="C28">
-        <v>0.16555581</v>
+      <c r="C28" t="s">
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>0.14315980232256301</v>
-      </c>
-      <c r="E28" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28">
-        <v>0.31288063294266599</v>
-      </c>
-      <c r="G28">
         <v>17.612268500013801</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>26</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>44915</v>
       </c>
       <c r="B29">
         <v>0.51433262189204798</v>
       </c>
-      <c r="C29">
-        <v>0.15135790499999999</v>
+      <c r="C29" t="s">
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>0.15087137078926999</v>
-      </c>
-      <c r="E29" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29">
-        <v>0.29428019642854403</v>
-      </c>
-      <c r="G29">
         <v>10.116682809798901</v>
       </c>
     </row>
@@ -6125,10 +6399,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6141,343 +6415,211 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>44929</v>
       </c>
       <c r="B2">
         <v>0.84629581545158405</v>
       </c>
-      <c r="C2">
-        <v>0.38927203100000002</v>
+      <c r="C2" t="s">
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>0.32925108320353702</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>0.45997158900317198</v>
-      </c>
-      <c r="G2">
         <v>7.8958984290259</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>44944</v>
       </c>
       <c r="B3">
         <v>0.89039772710795695</v>
       </c>
-      <c r="C3">
-        <v>0.24384</v>
+      <c r="C3" t="s">
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0.32251637360024299</v>
-      </c>
-      <c r="E3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>0.27385514649953202</v>
-      </c>
-      <c r="G3">
         <v>6.2631698085533101</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44958</v>
       </c>
       <c r="B4">
         <v>1.2795322417230099</v>
       </c>
-      <c r="C4">
-        <v>0.27730699199999997</v>
+      <c r="C4" t="s">
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>0.26309246533588299</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>0.21672528675524499</v>
-      </c>
-      <c r="G4">
         <v>4.17908012369488</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>44972</v>
       </c>
       <c r="B5">
         <v>1.93587245637372</v>
       </c>
-      <c r="C5">
-        <v>0.152032679</v>
+      <c r="C5" t="s">
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>0.16286414006333</v>
-      </c>
-      <c r="E5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5">
-        <v>7.8534450190374402E-2</v>
-      </c>
-      <c r="G5">
         <v>9.2886180882038705</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>23</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44986</v>
       </c>
       <c r="B6">
         <v>2.4780665467373599</v>
       </c>
-      <c r="C6">
-        <v>9.9617103999999998E-2</v>
+      <c r="C6" t="s">
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>8.0066827881655006E-2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6">
-        <v>4.0199527382005301E-2</v>
-      </c>
-      <c r="G6">
         <v>1.91650182628218</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>24</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>45000</v>
       </c>
       <c r="B7">
         <v>1.77503019033284</v>
       </c>
-      <c r="C7">
-        <v>0.20904352600000001</v>
+      <c r="C7" t="s">
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0.18742602214593199</v>
-      </c>
-      <c r="E7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>0.117768997473109</v>
-      </c>
-      <c r="G7">
         <v>4.44794425583971</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>14</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>45014</v>
       </c>
       <c r="B8">
         <v>1.7075802077995601</v>
       </c>
-      <c r="C8">
-        <v>0.14364185700000001</v>
+      <c r="C8" t="s">
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>0.19772616624508799</v>
-      </c>
-      <c r="E8" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8">
-        <v>8.4120122934137995E-2</v>
-      </c>
-      <c r="G8">
         <v>8.1938063501887299</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>15</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>45028</v>
       </c>
       <c r="B9">
         <v>1.4922591097125699</v>
       </c>
-      <c r="C9">
-        <v>0.217546613</v>
+      <c r="C9" t="s">
+        <v>2</v>
       </c>
       <c r="D9">
-        <v>0.2306073954847</v>
-      </c>
-      <c r="E9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>0.14578340422522401</v>
-      </c>
-      <c r="G9">
         <v>11.981817018407201</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>15</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45028</v>
       </c>
       <c r="B10">
         <v>1.4922591097125699</v>
       </c>
-      <c r="C10">
-        <v>0.217546613</v>
+      <c r="C10" t="s">
+        <v>2</v>
       </c>
       <c r="D10">
-        <v>0.2306073954847</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10">
-        <v>0.14578340422522401</v>
-      </c>
-      <c r="G10">
         <v>11.9908106789727</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45042</v>
       </c>
       <c r="B11">
         <v>1.11609574558469</v>
       </c>
-      <c r="C11">
-        <v>0.29169342100000001</v>
+      <c r="C11" t="s">
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0.28805050680691402</v>
-      </c>
-      <c r="E11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>0.26135161087563402</v>
-      </c>
-      <c r="G11">
         <v>8.5316662064735205</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45075</v>
+      </c>
       <c r="B12">
         <v>1.00713808149247</v>
       </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
       <c r="D12">
-        <v>0.304689201120935</v>
-      </c>
-      <c r="E12" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12">
         <v>9.3052048733349402</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" t="e">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>44872</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" t="e">
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>19</v>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>44886</v>
       </c>
       <c r="B14">
         <v>0.99935539120017003</v>
       </c>
-      <c r="C14">
-        <v>0.245749827</v>
+      <c r="C14" t="s">
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>0.305877679286223</v>
-      </c>
-      <c r="E14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14">
-        <v>0.24590834168099901</v>
-      </c>
-      <c r="G14">
         <v>16.0453723843845</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>20</v>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>44900</v>
       </c>
       <c r="B15">
         <v>0.94487655915406399</v>
       </c>
-      <c r="C15">
-        <v>0.31575888699999999</v>
+      <c r="C15" t="s">
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>0.314197026443233</v>
-      </c>
-      <c r="E15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15">
-        <v>0.33418004070573498</v>
-      </c>
-      <c r="G15">
         <v>7.0638592430665703</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>21</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>44914</v>
       </c>
       <c r="B16">
         <v>0.87483234652335495</v>
       </c>
-      <c r="C16">
-        <v>0.27092143800000001</v>
+      <c r="C16" t="s">
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>0.32489332993081799</v>
-      </c>
-      <c r="E16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16">
-        <v>0.30968383722511</v>
-      </c>
-      <c r="G16">
         <v>8.2264856374067996</v>
       </c>
     </row>
@@ -6490,10 +6632,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6506,460 +6648,256 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>27</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>44930</v>
       </c>
       <c r="B2">
         <v>0.27582680972963097</v>
       </c>
-      <c r="C2">
-        <v>9.9059999999999995E-2</v>
+      <c r="C2" t="s">
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0.108072813469553</v>
-      </c>
-      <c r="E2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>0.359138403178066</v>
-      </c>
-      <c r="G2">
         <v>24.690084932127998</v>
       </c>
-      <c r="H2">
-        <v>1.76</v>
-      </c>
-      <c r="I2">
-        <v>74.42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>44930</v>
       </c>
       <c r="B3">
         <v>0.27582680972963097</v>
       </c>
-      <c r="C3">
-        <v>9.9059999999999995E-2</v>
+      <c r="C3" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>0.108072813469553</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3">
-        <v>0.359138403178066</v>
-      </c>
-      <c r="G3">
         <v>23.148382126467901</v>
       </c>
-      <c r="H3">
-        <v>1.76</v>
-      </c>
-      <c r="I3">
-        <v>74.42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>29</v>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44937</v>
       </c>
       <c r="B4">
         <v>0.14842325926962999</v>
       </c>
-      <c r="C4">
-        <v>0.103632</v>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>0.11932456079093</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>0.69821940651323</v>
-      </c>
-      <c r="H4">
-        <v>1.83</v>
-      </c>
-      <c r="I4">
-        <v>73.290000000000006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
+        <v>118.259222088889</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>44951</v>
       </c>
       <c r="B5">
         <v>0.13941805406320101</v>
       </c>
-      <c r="C5">
-        <v>0.100003886</v>
+      <c r="C5" t="s">
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>0.12011986275225001</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5">
-        <v>0.71729509260447999</v>
-      </c>
-      <c r="G5">
         <v>50.954752325421801</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44963</v>
       </c>
       <c r="B6">
         <v>0.35708644464821998</v>
       </c>
-      <c r="C6">
-        <v>6.8341643999999993E-2</v>
+      <c r="C6" t="s">
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>0.100896303268462</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>0.19138683370444401</v>
-      </c>
-      <c r="G6">
         <v>9.73092604234097</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>44963</v>
       </c>
       <c r="B7">
         <v>0.35708644464821998</v>
       </c>
-      <c r="C7">
-        <v>6.8341643999999993E-2</v>
+      <c r="C7" t="s">
+        <v>6</v>
       </c>
       <c r="D7">
-        <v>0.100896303268462</v>
-      </c>
-      <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7">
-        <v>0.19138683370444401</v>
-      </c>
-      <c r="G7">
         <v>9.5554623120508193</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>32</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>44979</v>
       </c>
       <c r="B8">
         <v>0.97908907233996301</v>
       </c>
-      <c r="C8">
-        <v>7.7164556999999995E-2</v>
+      <c r="C8" t="s">
+        <v>6</v>
       </c>
       <c r="D8">
-        <v>4.5963639502409802E-2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8">
-        <v>7.8812601610986702E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>33</v>
+        <v>12.1601192837523</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>44993</v>
       </c>
       <c r="B9">
         <v>0.73912910715284497</v>
       </c>
-      <c r="C9">
-        <v>5.9129280999999999E-2</v>
+      <c r="C9" t="s">
+        <v>6</v>
       </c>
       <c r="D9">
-        <v>6.7155897377356E-2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9">
-        <v>7.9998582693852197E-2</v>
-      </c>
-      <c r="G9">
         <v>7.9516472320781002</v>
       </c>
-      <c r="H9">
-        <v>1.93</v>
-      </c>
-      <c r="I9">
-        <v>74.42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>34</v>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>45021</v>
       </c>
       <c r="B10">
         <v>0.50655758454314603</v>
       </c>
-      <c r="C10">
-        <v>0.12576395200000001</v>
+      <c r="C10" t="s">
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>8.7695638986629201E-2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F10">
-        <v>0.24827177765667799</v>
-      </c>
-      <c r="H10">
-        <v>1.53</v>
-      </c>
-      <c r="I10">
-        <v>71.739999999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>35</v>
+        <v>30.7702058957052</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>45035</v>
       </c>
       <c r="B11">
         <v>0.26422745354100802</v>
       </c>
-      <c r="C11">
-        <v>9.0472021999999999E-2</v>
+      <c r="C11" t="s">
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>0.109097219967282</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11">
-        <v>0.34240205091314901</v>
-      </c>
-      <c r="G11">
         <v>34.983383524448797</v>
       </c>
-      <c r="H11">
-        <v>1.704</v>
-      </c>
-      <c r="I11">
-        <v>73.278000000000006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>36</v>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>45049</v>
       </c>
       <c r="B12">
         <v>0.20547930573848</v>
       </c>
-      <c r="C12">
-        <v>0.10404495</v>
+      <c r="C12" t="s">
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>0.114285610026165</v>
-      </c>
-      <c r="E12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12">
-        <v>0.50635245055977096</v>
-      </c>
-      <c r="G12">
         <v>53.152789367811998</v>
       </c>
-      <c r="I12">
-        <v>72.669256200000007</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>37</v>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45063</v>
       </c>
       <c r="B13">
         <v>0.168078940883987</v>
       </c>
-      <c r="C13">
-        <v>5.4061723999999999E-2</v>
+      <c r="C13" t="s">
+        <v>6</v>
       </c>
       <c r="D13">
-        <v>0.11758865341507101</v>
-      </c>
-      <c r="E13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F13">
-        <v>0.32164483971442398</v>
-      </c>
-      <c r="G13">
         <v>33.341043343649702</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>38</v>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45076</v>
       </c>
       <c r="B14">
         <v>0.25776243935158599</v>
       </c>
-      <c r="C14">
-        <v>0.142205108</v>
+      <c r="C14" t="s">
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>0.109668182910041</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F14">
-        <v>0.55169057352857198</v>
-      </c>
-      <c r="G14">
         <v>31.9180285667398</v>
       </c>
-      <c r="H14">
-        <v>1.628292683</v>
-      </c>
-      <c r="I14">
-        <v>73.679374999999993</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45089</v>
+      </c>
       <c r="B15">
         <v>0.30718976746298698</v>
       </c>
+      <c r="C15" t="s">
+        <v>6</v>
+      </c>
       <c r="D15">
-        <v>0.105302968560265</v>
-      </c>
-      <c r="E15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15">
         <v>15.8650769934215</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>39</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>44865</v>
       </c>
       <c r="B16">
         <v>0.24912069961521999</v>
       </c>
-      <c r="C16">
-        <v>0.11911748799999999</v>
+      <c r="C16" t="s">
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>0.11043138512520299</v>
-      </c>
-      <c r="E16" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16">
-        <v>0.47815170792303902</v>
-      </c>
-      <c r="G16">
         <v>26.1959995510725</v>
       </c>
-      <c r="H16">
-        <v>1.78</v>
-      </c>
-      <c r="I16">
-        <v>73.430000000000007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>40</v>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>44879</v>
       </c>
       <c r="B17">
         <v>0.23799883780685399</v>
       </c>
-      <c r="C17">
-        <v>0.23090909100000001</v>
+      <c r="C17" t="s">
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>0.111413621321598</v>
-      </c>
-      <c r="E17" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17">
-        <v>0.97021100240578795</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>41</v>
+        <v>94.218748150536896</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>44893</v>
       </c>
       <c r="B18">
         <v>0.26752308407063402</v>
       </c>
-      <c r="C18">
-        <v>0.23330000000000001</v>
+      <c r="C18" t="s">
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>0.108806163698834</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18">
-        <v>0.87207427654505298</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>42</v>
+        <v>115.910838296351</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>44907</v>
       </c>
       <c r="B19">
         <v>0.16056832408994501</v>
       </c>
-      <c r="C19">
-        <v>0.23330000000000001</v>
+      <c r="C19" t="s">
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>0.11825195959522899</v>
-      </c>
-      <c r="E19" t="s">
-        <v>28</v>
-      </c>
-      <c r="F19">
-        <v>1.45296403460818</v>
-      </c>
-      <c r="G19">
         <v>42.614245239660903</v>
       </c>
     </row>
@@ -6972,10 +6910,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6988,499 +6926,293 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>44930</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2">
-        <v>6.096E-2</v>
-      </c>
-      <c r="E2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>30</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>44951</v>
       </c>
       <c r="B3">
         <v>0.74411257103448103</v>
       </c>
-      <c r="C3">
-        <v>0.116835492</v>
+      <c r="C3" t="s">
+        <v>7</v>
       </c>
       <c r="D3">
-        <v>8.7694745966911306E-2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3">
-        <v>0.157013194707318</v>
-      </c>
-      <c r="G3">
         <v>12.0270837749951</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>30</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>44951</v>
       </c>
       <c r="B4">
         <v>0.74411257103448103</v>
       </c>
-      <c r="C4">
-        <v>0.116835492</v>
+      <c r="C4" t="s">
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>8.7694745966911306E-2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4">
-        <v>0.157013194707318</v>
-      </c>
-      <c r="G4">
         <v>11.673900030623701</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>30</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>44951</v>
       </c>
       <c r="B5">
         <v>0.74411257103448103</v>
       </c>
-      <c r="C5">
-        <v>0.116835492</v>
+      <c r="C5" t="s">
+        <v>7</v>
       </c>
       <c r="D5">
-        <v>8.7694745966911306E-2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5">
-        <v>0.157013194707318</v>
-      </c>
-      <c r="G5">
         <v>4.8225004830932496</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>31</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>44963</v>
       </c>
       <c r="B6">
         <v>0.87528110109794</v>
       </c>
-      <c r="C6">
-        <v>8.9573877999999996E-2</v>
+      <c r="C6" t="s">
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>7.6126862837703799E-2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6">
-        <v>0.10233726957847</v>
-      </c>
-      <c r="G6">
         <v>2.0901187683293201</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>31</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>44963</v>
       </c>
       <c r="B7">
         <v>0.87528110109794</v>
       </c>
-      <c r="C7">
-        <v>8.9573877999999996E-2</v>
+      <c r="C7" t="s">
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>7.6126862837703799E-2</v>
-      </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7">
-        <v>0.10233726957847</v>
-      </c>
-      <c r="G7">
         <v>2.0802072636448998</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>31</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>44963</v>
       </c>
       <c r="B8">
         <v>0.87528110109794</v>
       </c>
-      <c r="C8">
-        <v>8.9573877999999996E-2</v>
+      <c r="C8" t="s">
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>7.6126862837703799E-2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8">
-        <v>0.10233726957847</v>
-      </c>
-      <c r="G8">
         <v>3.4348545944842801</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>32</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>44979</v>
       </c>
       <c r="B9">
         <v>1.62598028208757</v>
       </c>
-      <c r="C9">
-        <v>4.0360477999999998E-2</v>
+      <c r="C9" t="s">
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>9.9219554054219006E-3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9">
-        <v>2.48222431997649E-2</v>
-      </c>
-      <c r="G9">
         <v>11.4435970636991</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>32</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>44979</v>
       </c>
       <c r="B10">
         <v>1.62598028208757</v>
       </c>
-      <c r="C10">
-        <v>4.0360477999999998E-2</v>
+      <c r="C10" t="s">
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>9.9219554054219006E-3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10">
-        <v>2.48222431997649E-2</v>
-      </c>
-      <c r="G10">
         <v>5.2429283117314203</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>33</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>44993</v>
       </c>
       <c r="B11">
         <v>1.32277923770115</v>
       </c>
-      <c r="C11">
-        <v>3.2272940999999999E-2</v>
+      <c r="C11" t="s">
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>3.6661557079839702E-2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11">
-        <v>2.4397828511496002E-2</v>
-      </c>
-      <c r="G11">
         <v>8.1503583923791698</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>33</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>44993</v>
       </c>
       <c r="B12">
         <v>1.32277923770115</v>
       </c>
-      <c r="C12">
-        <v>3.2272940999999999E-2</v>
+      <c r="C12" t="s">
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>3.6661557079839702E-2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12">
-        <v>2.4397828511496002E-2</v>
-      </c>
-      <c r="G12">
         <v>22.095712310493202</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13">
-        <v>4.4325555000000003E-2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>34</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>45005</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>45021</v>
       </c>
       <c r="B14">
         <v>1.0535668624027901</v>
       </c>
-      <c r="C14">
-        <v>5.4257143000000001E-2</v>
+      <c r="C14" t="s">
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>6.0403664221553403E-2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14">
-        <v>5.1498528414475699E-2</v>
-      </c>
-      <c r="G14">
         <v>5.8251150947610704</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>45035</v>
+      </c>
       <c r="B15">
         <v>0.78894922945176305</v>
       </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
       <c r="D15">
-        <v>8.3740556465630903E-2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>43</v>
-      </c>
-      <c r="G15">
         <v>6.4381260228580199</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>36</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>45049</v>
       </c>
       <c r="B16">
         <v>0.73759563320647703</v>
       </c>
-      <c r="C16">
-        <v>0.137964795</v>
+      <c r="C16" t="s">
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>8.8269481195842894E-2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16">
-        <v>0.18704665373388801</v>
-      </c>
-      <c r="G16">
         <v>5.5662125718823496</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>37</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>45063</v>
       </c>
       <c r="B17">
         <v>0.73062868871751996</v>
       </c>
-      <c r="C17">
-        <v>0.14825882000000001</v>
+      <c r="C17" t="s">
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>8.8883902959789998E-2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17">
-        <v>0.202919516150181</v>
-      </c>
-      <c r="G17">
         <v>5.1949848895037301</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>37</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>45063</v>
       </c>
       <c r="B18">
         <v>0.73062868871751996</v>
       </c>
-      <c r="C18">
-        <v>0.14825882000000001</v>
+      <c r="C18" t="s">
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>8.8883902959789998E-2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18">
-        <v>0.202919516150181</v>
-      </c>
-      <c r="G18">
         <v>5.1262681581610803</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>39</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>44865</v>
       </c>
       <c r="B19">
         <v>0.74233596483651698</v>
       </c>
-      <c r="C19">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="D19">
-        <v>8.7851426634558596E-2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F19">
-        <v>1.6423830418461599E-2</v>
-      </c>
-      <c r="G19">
-        <v>-163.072100172185</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>39</v>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>44865</v>
       </c>
       <c r="B20">
         <v>0.74233596483651698</v>
       </c>
-      <c r="C20">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="D20">
-        <v>8.7851426634558596E-2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20">
-        <v>1.6423830418461599E-2</v>
-      </c>
-      <c r="G20">
-        <v>-157.05714565763799</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>39</v>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>44865</v>
       </c>
       <c r="B21">
         <v>0.74233596483651698</v>
       </c>
-      <c r="C21">
-        <v>1.2192E-2</v>
-      </c>
-      <c r="D21">
-        <v>8.7851426634558596E-2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F21">
-        <v>1.6423830418461599E-2</v>
-      </c>
-      <c r="G21">
-        <v>53.487681099100698</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22">
-        <v>0.104457388</v>
-      </c>
-      <c r="E22" t="s">
-        <v>43</v>
-      </c>
-      <c r="G22" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23">
-        <v>0.119632672</v>
-      </c>
-      <c r="E23" t="s">
-        <v>43</v>
-      </c>
-      <c r="G23" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24">
-        <v>0.125639851</v>
-      </c>
-      <c r="E24" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" t="e">
-        <v>#NUM!</v>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>44879</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>44893</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>44907</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samanthahowley\Desktop\SpringMetabolism_FlowReversals\04_Outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD267F9-7AAB-430D-B56F-7192AC8B22A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B7E1C1-C871-4A8E-B165-A4DA5D1ACD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
     <sheet name="LF" sheetId="4" r:id="rId4"/>
     <sheet name="OS" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -38,37 +51,125 @@
     <t>k600_1.day</t>
   </si>
   <si>
+    <t>1/3/2023</t>
+  </si>
+  <si>
     <t>AM</t>
+  </si>
+  <si>
+    <t>1/18/2023</t>
+  </si>
+  <si>
+    <t>2/1/2023</t>
+  </si>
+  <si>
+    <t>2/15/2023</t>
+  </si>
+  <si>
+    <t>3/29/2023</t>
+  </si>
+  <si>
+    <t>4/12/2023</t>
+  </si>
+  <si>
+    <t>4/26/2023</t>
+  </si>
+  <si>
+    <t>5/29/2023</t>
+  </si>
+  <si>
+    <t>11/7/2022</t>
+  </si>
+  <si>
+    <t>11/21/2022</t>
+  </si>
+  <si>
+    <t>12/5/2022</t>
+  </si>
+  <si>
+    <t>12/19/2022</t>
   </si>
   <si>
     <t>GB</t>
   </si>
   <si>
+    <t>3/1/2023</t>
+  </si>
+  <si>
+    <t>3/15/2023</t>
+  </si>
+  <si>
+    <t>10/24/2022</t>
+  </si>
+  <si>
+    <t>12/20/2022</t>
+  </si>
+  <si>
+    <t>1/4/2023</t>
+  </si>
+  <si>
     <t>LF</t>
   </si>
   <si>
+    <t>1/11/2023</t>
+  </si>
+  <si>
+    <t>1/25/2023</t>
+  </si>
+  <si>
+    <t>2/6/2023</t>
+  </si>
+  <si>
+    <t>2/22/2023</t>
+  </si>
+  <si>
+    <t>3/8/2023</t>
+  </si>
+  <si>
+    <t>4/5/2023</t>
+  </si>
+  <si>
+    <t>4/19/2023</t>
+  </si>
+  <si>
+    <t>5/3/2023</t>
+  </si>
+  <si>
+    <t>5/17/2023</t>
+  </si>
+  <si>
+    <t>5/30/2023</t>
+  </si>
+  <si>
+    <t>10/31/2022</t>
+  </si>
+  <si>
+    <t>11/14/2022</t>
+  </si>
+  <si>
+    <t>11/28/2022</t>
+  </si>
+  <si>
+    <t>12/12/2022</t>
+  </si>
+  <si>
     <t>OS</t>
+  </si>
+  <si>
+    <t>3/20/2023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -91,9 +192,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -218,94 +318,97 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
                 <c:pt idx="0">
-                  <c:v>0.66360277136277601</c:v>
+                  <c:v>0.66929954724058005</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.66360277136277601</c:v>
+                  <c:v>0.64562359749952802</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.84496568832957797</c:v>
+                  <c:v>0.64562359749952802</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.84496568832957797</c:v>
+                  <c:v>0.66938268888003205</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84496568832957797</c:v>
+                  <c:v>0.74624235777991699</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.79712100240526</c:v>
+                  <c:v>0.74979625322111798</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.79712100240526</c:v>
+                  <c:v>0.82262807678377803</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.91936208989603</c:v>
+                  <c:v>0.64779631643734703</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.91936208989603</c:v>
+                  <c:v>0.64779631643734703</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5364118092654899</c:v>
+                  <c:v>0.63630915048649805</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.5364118092654899</c:v>
+                  <c:v>0.65936577783929395</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5364118092654899</c:v>
+                  <c:v>0.65936577783929395</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.14254792657094</c:v>
+                  <c:v>0.82262807678377803</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.14254792657094</c:v>
+                  <c:v>0.82262807678377803</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.14254792657094</c:v>
+                  <c:v>0.81485994116437999</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.76948902444658396</c:v>
+                  <c:v>0.67526977684662204</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.74683198736593104</c:v>
+                  <c:v>0.66591872251684503</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.74683198736593104</c:v>
+                  <c:v>0.66938268888003205</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.634197514012805</c:v>
+                  <c:v>1.13846124410022</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.81193724612891904</c:v>
+                  <c:v>0.81818901391054499</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.81193724612891904</c:v>
+                  <c:v>0.75244576730325496</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.64229622161300404</c:v>
+                  <c:v>0.67526977684662204</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.64229622161300404</c:v>
+                  <c:v>1.55941957646957</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.1363928753058901</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.66551573852542301</c:v>
+                  <c:v>1.13846124410022</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.66551573852542301</c:v>
+                  <c:v>1.5480843226282499</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.66551573852542301</c:v>
+                  <c:v>1.55941957646957</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.66831711482098599</c:v>
+                  <c:v>1.83146566866125</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.66831711482098599</c:v>
+                  <c:v>1.83146566866125</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.65580679181917101</c:v>
+                  <c:v>2.0052859302193</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.65580679181917101</c:v>
+                  <c:v>2.0052859302193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -316,92 +419,71 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="31"/>
-                <c:pt idx="0">
-                  <c:v>8.7000179355782503</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>14.0537866274825</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.2509884099436</c:v>
+                  <c:v>32.497387104732198</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>14.019548098025901</c:v>
+                  <c:v>30.003218289191299</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17.9748429691486</c:v>
+                  <c:v>22.583603072389199</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.3659747293628499</c:v>
+                  <c:v>22.534752718028901</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.43477614979118</c:v>
+                  <c:v>18.462931172278498</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.762817767337299</c:v>
+                  <c:v>17.7130396770579</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.954970513126703</c:v>
+                  <c:v>16.172118752756798</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.2531836035536301</c:v>
+                  <c:v>16.096811745708699</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.4433323290317999</c:v>
+                  <c:v>15.446661759491001</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.43040464475121</c:v>
+                  <c:v>15.0741857995821</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.0432970693483599</c:v>
+                  <c:v>14.63795920784</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.7839849332143101</c:v>
+                  <c:v>14.4002343744848</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.7892918049894102</c:v>
+                  <c:v>10.452469010274299</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>7.6754733355837299</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>22.624195858075399</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>22.5657731444328</c:v>
+                  <c:v>10.246063982032499</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16.1504080056141</c:v>
+                  <c:v>7.0685800720140799</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.76777594040046</c:v>
+                  <c:v>6.6081279033771398</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>11.6535292051355</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>32.6657378105105</c:v>
+                  <c:v>6.4931180194822504</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.2051859433009899</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.80439946223186</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8.0612152297113795</c:v>
+                  <c:v>2.7939784771177898</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>7.8631523559558696</c:v>
+                  <c:v>2.4120794603422602</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>30.1775506886923</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>23.531152831216499</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>18.703245444769301</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15.9745813671168</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>17.496680423021001</c:v>
+                  <c:v>2.4072832616244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -409,7 +491,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8E08-4FCE-B184-F8BB4AAE55CA}"/>
+              <c16:uniqueId val="{00000000-F58C-4A8A-9E96-0B1332BCE4F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -421,11 +503,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="790405791"/>
-        <c:axId val="790411071"/>
+        <c:axId val="1605681951"/>
+        <c:axId val="1605682431"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="790405791"/>
+        <c:axId val="1605681951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -482,12 +564,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790411071"/>
+        <c:crossAx val="1605682431"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="790411071"/>
+        <c:axId val="1605682431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -544,7 +626,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790405791"/>
+        <c:crossAx val="1605681951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -702,171 +784,171 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>GB!$B$2:$B$29</c:f>
+              <c:f>GB!$B$2:$B$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
-                <c:pt idx="0">
+                <c:ptCount val="29"/>
+                <c:pt idx="1">
+                  <c:v>0.55068895347565805</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.55068895347565805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.42847041975631001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.42847041975631001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.44959398748926399</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.46633139234925403</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.41829191635495</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>0.500234239386116</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="9">
+                  <c:v>0.40867897602588799</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.40867897602588799</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.496481994488156</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.49364073113116103</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.49364073113116103</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.52913409322569804</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.496481994488156</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.49364073113116103</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.48738009477924898</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.48738009477924898</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.48014251849385198</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.49838619196324002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.49838619196324002</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.48014251849385198</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.51433262189204798</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.48014251849385198</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>0.500234239386116</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="26">
                   <c:v>0.500234239386116</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.49838619196324002</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.49838619196324002</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.496481994488156</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.496481994488156</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.49364073113116103</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.49364073113116103</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.49364073113116103</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.48014251849385198</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.48014251849385198</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.48014251849385198</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.48738009477924898</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.48738009477924898</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.46633139234925403</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0.44959398748926399</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0.42847041975631001</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>0.42847041975631001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>0.40867897602588799</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>0.40867897602588799</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>0.41829191635495</c:v>
-                </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="27">
                   <c:v>0.57001899623787999</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>0.55068895347565805</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>0.55068895347565805</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>0.52913409322569804</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>0.51433262189204798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>GB!$D$2:$D$29</c:f>
+              <c:f>GB!$D$2:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
-                <c:pt idx="0">
+                <c:ptCount val="29"/>
+                <c:pt idx="3">
+                  <c:v>32.379700829916601</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32.274144438345303</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31.877696149374302</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.8790872259084</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>21.2301041068087</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>20.759702379649699</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>19.545410722183501</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>19.3542063534147</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19.278549967453198</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>18.3266040851639</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>18.238219059268399</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17.612268500013801</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16.082464877533099</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>15.8324828082942</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>15.491084387970799</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>15.422189134531401</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.5427239203201</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11.7604829329048</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11.63069034185</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10.123963721124101</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>10.116682809798901</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>9.9882836327260591</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>8.0617713895940106</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="26">
                   <c:v>8.0092423263314494</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20.759702379649699</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>11.7604829329048</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>11.63069034185</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>16.082464877533099</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>19.278549967453198</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18.3266040851639</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>18.238219059268399</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>15.8324828082942</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>12.5427239203201</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>10.123963721124101</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>9.9882836327260591</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>15.491084387970799</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>15.422189134531401</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>28.8790872259084</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>31.877696149374302</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>32.379700829916601</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>32.274144438345303</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>19.545410722183501</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>19.3542063534147</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>21.2301041068087</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>17.612268500013801</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>10.116682809798901</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -874,7 +956,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DCD4-47E7-9F46-B167D36B0401}"/>
+              <c16:uniqueId val="{00000000-C4BE-40F7-AF9D-281D711669A5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -886,11 +968,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="790408191"/>
-        <c:axId val="790401951"/>
+        <c:axId val="1451252303"/>
+        <c:axId val="1451250863"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="790408191"/>
+        <c:axId val="1451252303"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -947,12 +1029,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790401951"/>
+        <c:crossAx val="1451250863"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="790401951"/>
+        <c:axId val="1451250863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1009,7 +1091,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790408191"/>
+        <c:crossAx val="1451252303"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1167,105 +1249,87 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>ID!$B$2:$B$16</c:f>
+              <c:f>ID!$B$2:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
+                <c:ptCount val="16"/>
+                <c:pt idx="1">
+                  <c:v>0.99935539120017003</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4922591097125699</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.4922591097125699</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.00713808149247</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.93587245637372</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.11609574558469</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.87483234652335495</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.7075802077995601</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0.84629581545158405</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
+                  <c:v>0.94487655915406399</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0.89039772710795695</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="12">
+                  <c:v>1.77503019033284</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>1.2795322417230099</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>1.93587245637372</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="14">
                   <c:v>2.4780665467373599</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1.77503019033284</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1.7075802077995601</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1.4922591097125699</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1.4922591097125699</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1.11609574558469</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1.00713808149247</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.99935539120017003</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>0.94487655915406399</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>0.87483234652335495</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>ID!$D$2:$D$16</c:f>
+              <c:f>ID!$D$2:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
-                <c:pt idx="0">
+                <c:ptCount val="16"/>
+                <c:pt idx="4">
+                  <c:v>9.3052048733349402</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5316662064735205</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.2264856374067996</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>7.8958984290259</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="10">
+                  <c:v>7.0638592430665703</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>6.2631698085533101</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="12">
+                  <c:v>4.44794425583971</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>4.17908012369488</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.2886180882038705</c:v>
-                </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="14">
                   <c:v>1.91650182628218</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.44794425583971</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>8.1938063501887299</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>11.981817018407201</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>11.9908106789727</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>8.5316662064735205</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>9.3052048733349402</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>16.0453723843845</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>7.0638592430665703</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>8.2264856374067996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1273,7 +1337,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-AA68-4551-A4ED-4716C3F7ADEE}"/>
+              <c16:uniqueId val="{00000000-A6C7-469A-9749-27D9705D6671}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1285,11 +1349,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="790460511"/>
-        <c:axId val="790460991"/>
+        <c:axId val="125049631"/>
+        <c:axId val="123090095"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="790460511"/>
+        <c:axId val="125049631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1346,12 +1410,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790460991"/>
+        <c:crossAx val="123090095"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="790460991"/>
+        <c:axId val="123090095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1408,7 +1472,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790460511"/>
+        <c:crossAx val="125049631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1571,58 +1635,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
+                  <c:v>0.14842325926962999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26752308407063402</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.23799883780685399</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.20547930573848</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.13941805406320101</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16056832408994501</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26422745354100802</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.168078940883987</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25776243935158599</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.50655758454314603</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.24912069961521999</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>0.27582680972963097</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="12">
                   <c:v>0.27582680972963097</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.14842325926962999</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.13941805406320101</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.35708644464821998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.35708644464821998</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.97908907233996301</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.73912910715284497</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.50655758454314603</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.26422745354100802</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.20547930573848</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.168078940883987</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.25776243935158599</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.30718976746298698</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.24912069961521999</c:v>
+                  <c:v>0.97908907233996301</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.23799883780685399</c:v>
+                  <c:v>0.35708644464821998</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.26752308407063402</c:v>
+                  <c:v>0.35708644464821998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.16056832408994501</c:v>
+                  <c:v>0.73912910715284497</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1633,59 +1697,41 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
-                <c:pt idx="0">
+                <c:pt idx="3">
+                  <c:v>53.152789367811998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.954752325421801</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>42.614245239660903</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34.983383524448797</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33.341043343649702</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31.9180285667398</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.1959995510725</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>24.690084932127998</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="12">
                   <c:v>23.148382126467901</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>118.259222088889</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>50.954752325421801</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>9.73092604234097</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>9.5554623120508193</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>12.1601192837523</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>7.9516472320781002</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>30.7702058957052</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>34.983383524448797</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>53.152789367811998</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>33.341043343649702</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>31.9180285667398</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>15.8650769934215</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>26.1959995510725</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>94.218748150536896</c:v>
+                  <c:v>9.73092604234097</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>115.910838296351</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>42.614245239660903</c:v>
+                  <c:v>9.5554623120508193</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1693,7 +1739,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-078D-4AF8-95D0-AEC7CAD7A4B9}"/>
+              <c16:uniqueId val="{00000000-D7D2-46E6-BDF9-8F0D073F503E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1705,11 +1751,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="736366095"/>
-        <c:axId val="736403055"/>
+        <c:axId val="1442258431"/>
+        <c:axId val="1442255071"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="736366095"/>
+        <c:axId val="1442258431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1766,12 +1812,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="736403055"/>
+        <c:crossAx val="1442255071"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="736403055"/>
+        <c:axId val="1442255071"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1828,7 +1874,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="736366095"/>
+        <c:crossAx val="1442258431"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2039,6 +2085,9 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
                 <c:pt idx="1">
                   <c:v>12.0270837749951</c:v>
                 </c:pt>
@@ -2066,8 +2115,8 @@
                 <c:pt idx="9">
                   <c:v>8.1503583923791698</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>22.095712310493202</c:v>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>5.8251150947610704</c:v>
@@ -2090,7 +2139,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F822-4C65-9F39-07E7A2261092}"/>
+              <c16:uniqueId val="{00000000-24EC-45AC-B1F7-6275CAA698C7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2102,11 +2151,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="790448511"/>
-        <c:axId val="790434111"/>
+        <c:axId val="1308801951"/>
+        <c:axId val="1308802431"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="790448511"/>
+        <c:axId val="1308801951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2163,12 +2212,12 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790434111"/>
+        <c:crossAx val="1308802431"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="790434111"/>
+        <c:axId val="1308802431"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2225,7 +2274,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="790448511"/>
+        <c:crossAx val="1308801951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5065,23 +5114,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119E926F-0970-A21B-C4D1-1DAC5673F1D7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F2D97EB-BB48-8DDB-8044-188325B6032F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5108,21 +5157,21 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
       <xdr:colOff>533400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDCD8786-89E2-7E2C-F308-8422A9649FD9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8891A90C-0E30-5E01-02A3-777C076D4CF3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5147,23 +5196,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>700087</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>700087</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{95567553-5376-4F57-872C-B00663ADF10E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{13588F77-B3C5-0FED-AC71-6A5F0EB50D70}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5188,23 +5237,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>700087</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>52386</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DECAF12D-F437-BF75-16E0-B3FBC5DBE18E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25448DF6-6494-E5FB-A792-E9AE8219DC92}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5229,23 +5278,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>147637</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>385762</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>61912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>33337</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>176212</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>182562</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFE4EA57-7C85-80AE-1989-24A5BD379E0A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1369FC31-BBC1-4B26-C7D2-E5C83E571F7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5546,9 +5595,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5562,432 +5611,402 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44929</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>0.66360277136277601</v>
+        <v>0.66929954724058005</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B3">
+        <v>0.64562359749952802</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B4">
+        <v>0.64562359749952802</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>32.497387104732198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>0.66938268888003205</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>30.003218289191299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>0.74624235777991699</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>22.583603072389199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B7">
+        <v>0.74979625322111798</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>22.534752718028901</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B8">
+        <v>0.82262807678377803</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>18.462931172278498</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>0.64779631643734703</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>17.7130396770579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>0.64779631643734703</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>16.172118752756798</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>0.63630915048649805</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>16.096811745708699</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B12">
+        <v>0.65936577783929395</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>15.446661759491001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>0.65936577783929395</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>15.0741857995821</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>0.82262807678377803</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>14.63795920784</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
         <v>4</v>
       </c>
-      <c r="D2">
-        <v>8.7000179355782503</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>44929</v>
-      </c>
-      <c r="B3">
-        <v>0.66360277136277601</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="B15">
+        <v>0.82262807678377803</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>14.4002343744848</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>0.81485994116437999</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>10.452469010274299</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17">
+        <v>0.67526977684662204</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>10.246063982032499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
         <v>4</v>
       </c>
-      <c r="D3">
-        <v>14.0537866274825</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>44944</v>
-      </c>
-      <c r="B4">
-        <v>0.84496568832957797</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>14.2509884099436</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>44944</v>
-      </c>
-      <c r="B5">
-        <v>0.84496568832957797</v>
-      </c>
-      <c r="C5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>14.019548098025901</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44944</v>
-      </c>
-      <c r="B6">
-        <v>0.84496568832957797</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6">
-        <v>17.9748429691486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>44958</v>
-      </c>
-      <c r="B7">
-        <v>1.79712100240526</v>
-      </c>
-      <c r="C7" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>1.3659747293628499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>44958</v>
-      </c>
-      <c r="B8">
-        <v>1.79712100240526</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>1.43477614979118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>44972</v>
-      </c>
-      <c r="B9">
-        <v>1.91936208989603</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>0.762817767337299</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>44972</v>
-      </c>
-      <c r="B10">
-        <v>1.91936208989603</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>0.954970513126703</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>45014</v>
-      </c>
-      <c r="B11">
-        <v>1.5364118092654899</v>
-      </c>
-      <c r="C11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>3.2531836035536301</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>45014</v>
-      </c>
-      <c r="B12">
-        <v>1.5364118092654899</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>2.4433323290317999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>45014</v>
-      </c>
-      <c r="B13">
-        <v>1.5364118092654899</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>2.43040464475121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>45028</v>
-      </c>
-      <c r="B14">
-        <v>1.14254792657094</v>
-      </c>
-      <c r="C14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14">
-        <v>7.0432970693483599</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>45028</v>
-      </c>
-      <c r="B15">
-        <v>1.14254792657094</v>
-      </c>
-      <c r="C15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15">
-        <v>2.7839849332143101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>45028</v>
-      </c>
-      <c r="B16">
-        <v>1.14254792657094</v>
-      </c>
-      <c r="C16" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16">
-        <v>2.7892918049894102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>45042</v>
-      </c>
-      <c r="B17">
-        <v>0.76948902444658396</v>
-      </c>
-      <c r="C17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17">
-        <v>7.6754733355837299</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>45050</v>
-      </c>
       <c r="B18">
-        <v>0.74683198736593104</v>
+        <v>0.66591872251684503</v>
       </c>
       <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18">
-        <v>22.624195858075399</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>45050</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>14</v>
       </c>
       <c r="B19">
-        <v>0.74683198736593104</v>
+        <v>0.66938268888003205</v>
       </c>
       <c r="C19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>22.5657731444328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>45064</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>14</v>
       </c>
       <c r="B20">
-        <v>0.634197514012805</v>
+        <v>1.13846124410022</v>
       </c>
       <c r="C20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>16.1504080056141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>45075</v>
+        <v>7.0685800720140799</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>12</v>
       </c>
       <c r="B21">
-        <v>0.81193724612891904</v>
+        <v>0.81818901391054499</v>
       </c>
       <c r="C21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21">
-        <v>7.76777594040046</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>45075</v>
+        <v>6.6081279033771398</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>11</v>
       </c>
       <c r="B22">
-        <v>0.81193724612891904</v>
+        <v>0.75244576730325496</v>
       </c>
       <c r="C22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22">
-        <v>11.6535292051355</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>45086</v>
+        <v>6.4931180194822504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>10</v>
       </c>
       <c r="B23">
-        <v>0.64229622161300404</v>
+        <v>0.67526977684662204</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D23">
-        <v>32.6657378105105</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>45086</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>9</v>
       </c>
       <c r="B24">
-        <v>0.64229622161300404</v>
+        <v>1.55941957646957</v>
       </c>
       <c r="C24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>44872</v>
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>3.2051859433009899</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>1.1363928753058901</v>
       </c>
       <c r="C25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>44886</v>
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>2.80439946223186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>10</v>
       </c>
       <c r="B26">
-        <v>0.66551573852542301</v>
+        <v>1.13846124410022</v>
       </c>
       <c r="C26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>8.0612152297113795</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>44886</v>
+        <v>2.7939784771177898</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>9</v>
       </c>
       <c r="B27">
-        <v>0.66551573852542301</v>
+        <v>1.5480843226282499</v>
       </c>
       <c r="C27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>7.8631523559558696</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>44886</v>
+        <v>2.4120794603422602</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>9</v>
       </c>
       <c r="B28">
-        <v>0.66551573852542301</v>
+        <v>1.55941957646957</v>
       </c>
       <c r="C28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>30.1775506886923</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>44900</v>
+        <v>2.4072832616244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>7</v>
       </c>
       <c r="B29">
-        <v>0.66831711482098599</v>
+        <v>1.83146566866125</v>
       </c>
       <c r="C29" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29">
-        <v>23.531152831216499</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
-        <v>44900</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A30" t="s">
+        <v>7</v>
       </c>
       <c r="B30">
-        <v>0.66831711482098599</v>
+        <v>1.83146566866125</v>
       </c>
       <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30">
-        <v>18.703245444769301</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
-        <v>44914</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A31" t="s">
+        <v>8</v>
       </c>
       <c r="B31">
-        <v>0.65580679181917101</v>
+        <v>2.0052859302193</v>
       </c>
       <c r="C31" t="s">
-        <v>4</v>
-      </c>
-      <c r="D31">
-        <v>15.9745813671168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
-        <v>44914</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A32" t="s">
+        <v>8</v>
       </c>
       <c r="B32">
-        <v>0.65580679181917101</v>
+        <v>2.0052859302193</v>
       </c>
       <c r="C32" t="s">
-        <v>4</v>
-      </c>
-      <c r="D32">
-        <v>17.496680423021001</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D32">
+    <sortCondition descending="1" ref="D2:D32"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -5997,9 +6016,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6013,384 +6032,378 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44929</v>
-      </c>
-      <c r="B2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>0.55068895347565805</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>0.42847041975631001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>32.379700829916601</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0.42847041975631001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6">
+        <v>32.274144438345303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7">
+        <v>0.44959398748926399</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
+        <v>31.877696149374302</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8">
+        <v>0.46633139234925403</v>
+      </c>
+      <c r="C8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8">
+        <v>28.8790872259084</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B9">
+        <v>0.41829191635495</v>
+      </c>
+      <c r="C9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9">
+        <v>21.2301041068087</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
         <v>0.500234239386116</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2">
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10">
+        <v>20.759702379649699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B11">
+        <v>0.40867897602588799</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>19.545410722183501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="B12">
+        <v>0.40867897602588799</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12">
+        <v>19.3542063534147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>0.496481994488156</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>19.278549967453198</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>0.49364073113116103</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14">
+        <v>18.3266040851639</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15">
+        <v>0.49364073113116103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15">
+        <v>18.238219059268399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.52913409322569804</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16">
+        <v>17.612268500013801</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17">
+        <v>0.496481994488156</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17">
+        <v>16.082464877533099</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18">
+        <v>0.49364073113116103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18">
+        <v>15.8324828082942</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19">
+        <v>0.48738009477924898</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19">
+        <v>15.491084387970799</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0.48738009477924898</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20">
+        <v>15.422189134531401</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21">
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21">
+        <v>12.5427239203201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22">
+        <v>0.49838619196324002</v>
+      </c>
+      <c r="C22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22">
+        <v>11.7604829329048</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23">
+        <v>0.49838619196324002</v>
+      </c>
+      <c r="C23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23">
+        <v>11.63069034185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="C24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24">
+        <v>10.123963721124101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25">
+        <v>0.51433262189204798</v>
+      </c>
+      <c r="C25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25">
+        <v>10.116682809798901</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A26" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>0.48014251849385198</v>
+      </c>
+      <c r="C26" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26">
+        <v>9.9882836327260591</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>0.500234239386116</v>
+      </c>
+      <c r="C27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27">
         <v>8.0617713895940106</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>44929</v>
-      </c>
-      <c r="B3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
         <v>0.500234239386116</v>
       </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3">
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28">
         <v>8.0092423263314494</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>44929</v>
-      </c>
-      <c r="B4">
-        <v>0.500234239386116</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4">
-        <v>20.759702379649699</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>44944</v>
-      </c>
-      <c r="B5">
-        <v>0.49838619196324002</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>11.7604829329048</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44944</v>
-      </c>
-      <c r="B6">
-        <v>0.49838619196324002</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6">
-        <v>11.63069034185</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>44958</v>
-      </c>
-      <c r="B7">
-        <v>0.496481994488156</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>16.082464877533099</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>44958</v>
-      </c>
-      <c r="B8">
-        <v>0.496481994488156</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>19.278549967453198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>44972</v>
-      </c>
-      <c r="B9">
-        <v>0.49364073113116103</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>18.3266040851639</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>44972</v>
-      </c>
-      <c r="B10">
-        <v>0.49364073113116103</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>18.238219059268399</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>44972</v>
-      </c>
-      <c r="B11">
-        <v>0.49364073113116103</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11">
-        <v>15.8324828082942</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>44986</v>
-      </c>
-      <c r="B12">
-        <v>0.48014251849385198</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12">
-        <v>12.5427239203201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>44986</v>
-      </c>
-      <c r="B13">
-        <v>0.48014251849385198</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <v>10.123963721124101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>44986</v>
-      </c>
-      <c r="B14">
-        <v>0.48014251849385198</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>9.9882836327260591</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>45000</v>
-      </c>
-      <c r="B15">
-        <v>0.48738009477924898</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15">
-        <v>15.491084387970799</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>45000</v>
-      </c>
-      <c r="B16">
-        <v>0.48738009477924898</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16">
-        <v>15.422189134531401</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>45014</v>
-      </c>
-      <c r="B17">
-        <v>0.46633139234925403</v>
-      </c>
-      <c r="C17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17">
-        <v>28.8790872259084</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>45028</v>
-      </c>
-      <c r="B18">
-        <v>0.44959398748926399</v>
-      </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18">
-        <v>31.877696149374302</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>45042</v>
-      </c>
-      <c r="B19">
-        <v>0.42847041975631001</v>
-      </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19">
-        <v>32.379700829916601</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>45042</v>
-      </c>
-      <c r="B20">
-        <v>0.42847041975631001</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20">
-        <v>32.274144438345303</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>45064</v>
-      </c>
-      <c r="B21">
-        <v>0.40867897602588799</v>
-      </c>
-      <c r="C21" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21">
-        <v>19.545410722183501</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>45064</v>
-      </c>
-      <c r="B22">
-        <v>0.40867897602588799</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22">
-        <v>19.3542063534147</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>45075</v>
-      </c>
-      <c r="B23">
-        <v>0.41829191635495</v>
-      </c>
-      <c r="C23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23">
-        <v>21.2301041068087</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>44858</v>
-      </c>
-      <c r="B24">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29">
         <v>0.57001899623787999</v>
       </c>
-      <c r="C24" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
-        <v>44872</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
-        <v>44886</v>
-      </c>
-      <c r="B26">
-        <v>0.55068895347565805</v>
-      </c>
-      <c r="C26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
-        <v>44886</v>
-      </c>
-      <c r="B27">
-        <v>0.55068895347565805</v>
-      </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
-        <v>44900</v>
-      </c>
-      <c r="B28">
-        <v>0.52913409322569804</v>
-      </c>
-      <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28">
-        <v>17.612268500013801</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
-        <v>44915</v>
-      </c>
-      <c r="B29">
-        <v>0.51433262189204798</v>
-      </c>
       <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29">
-        <v>10.116682809798901</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D29">
+    <sortCondition descending="1" ref="D2:D29"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -6400,9 +6413,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6416,214 +6429,196 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44929</v>
-      </c>
-      <c r="B2">
-        <v>0.84629581545158405</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
-      <c r="D2">
-        <v>7.8958984290259</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>44944</v>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.89039772710795695</v>
+        <v>0.99935539120017003</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="D3">
-        <v>6.2631698085533101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>44958</v>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>10</v>
       </c>
       <c r="B4">
-        <v>1.2795322417230099</v>
+        <v>1.4922591097125699</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
-      <c r="D4">
-        <v>4.17908012369488</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>44972</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>1.93587245637372</v>
+        <v>1.4922591097125699</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
-      <c r="D5">
-        <v>9.2886180882038705</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44986</v>
-      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
       <c r="B6">
-        <v>2.4780665467373599</v>
+        <v>1.00713808149247</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6">
-        <v>1.91650182628218</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>45000</v>
+        <v>9.3052048733349402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>1.77503019033284</v>
+        <v>1.93587245637372</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>4.44794425583971</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>45014</v>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>1.7075802077995601</v>
+        <v>1.11609574558469</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
       <c r="D8">
-        <v>8.1938063501887299</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>45028</v>
+        <v>8.5316662064735205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>16</v>
       </c>
       <c r="B9">
-        <v>1.4922591097125699</v>
+        <v>0.87483234652335495</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>11.981817018407201</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>45028</v>
+        <v>8.2264856374067996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>1.4922591097125699</v>
+        <v>1.7075802077995601</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D10">
-        <v>11.9908106789727</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>45042</v>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>4</v>
       </c>
       <c r="B11">
-        <v>1.11609574558469</v>
+        <v>0.84629581545158405</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>8.5316662064735205</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>45075</v>
+        <v>7.8958984290259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>1.00713808149247</v>
+        <v>0.94487655915406399</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12">
-        <v>9.3052048733349402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>44872</v>
+        <v>7.0638592430665703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>0.89039772710795695</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
-      <c r="D13" t="e">
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>44886</v>
+      <c r="D13">
+        <v>6.2631698085533101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>19</v>
       </c>
       <c r="B14">
-        <v>0.99935539120017003</v>
+        <v>1.77503019033284</v>
       </c>
       <c r="C14" t="s">
         <v>2</v>
       </c>
       <c r="D14">
-        <v>16.0453723843845</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>44900</v>
+        <v>4.44794425583971</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A15" t="s">
+        <v>7</v>
       </c>
       <c r="B15">
-        <v>0.94487655915406399</v>
+        <v>1.2795322417230099</v>
       </c>
       <c r="C15" t="s">
         <v>2</v>
       </c>
       <c r="D15">
-        <v>7.0638592430665703</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>44914</v>
+        <v>4.17908012369488</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>18</v>
       </c>
       <c r="B16">
-        <v>0.87483234652335495</v>
+        <v>2.4780665467373599</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
       </c>
       <c r="D16">
-        <v>8.2264856374067996</v>
+        <v>1.91650182628218</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D16">
+    <sortCondition descending="1" ref="D2:D16"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -6633,9 +6628,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6649,259 +6644,241 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44930</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>24</v>
       </c>
       <c r="B2">
+        <v>0.14842325926962999</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3">
+        <v>0.26752308407063402</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4">
+        <v>0.23799883780685399</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5">
+        <v>0.20547930573848</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5">
+        <v>53.152789367811998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>0.13941805406320101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6">
+        <v>50.954752325421801</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7">
+        <v>0.16056832408994501</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>42.614245239660903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8">
+        <v>0.26422745354100802</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>34.983383524448797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9">
+        <v>0.168078940883987</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9">
+        <v>33.341043343649702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10">
+        <v>0.25776243935158599</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>31.9180285667398</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <v>0.50655758454314603</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>0.24912069961521999</v>
+      </c>
+      <c r="C12" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12">
+        <v>26.1959995510725</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
         <v>0.27582680972963097</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13">
         <v>24.690084932127998</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>44930</v>
-      </c>
-      <c r="B3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14">
         <v>0.27582680972963097</v>
       </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14">
         <v>23.148382126467901</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>44937</v>
-      </c>
-      <c r="B4">
-        <v>0.14842325926962999</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
-        <v>118.259222088889</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>44951</v>
-      </c>
-      <c r="B5">
-        <v>0.13941805406320101</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5">
-        <v>50.954752325421801</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44963</v>
-      </c>
-      <c r="B6">
-        <v>0.35708644464821998</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>9.73092604234097</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>44963</v>
-      </c>
-      <c r="B7">
-        <v>0.35708644464821998</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>9.5554623120508193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>44979</v>
-      </c>
-      <c r="B8">
-        <v>0.97908907233996301</v>
-      </c>
-      <c r="C8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>12.1601192837523</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>44993</v>
-      </c>
-      <c r="B9">
-        <v>0.73912910715284497</v>
-      </c>
-      <c r="C9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>7.9516472320781002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>45021</v>
-      </c>
-      <c r="B10">
-        <v>0.50655758454314603</v>
-      </c>
-      <c r="C10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>30.7702058957052</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>45035</v>
-      </c>
-      <c r="B11">
-        <v>0.26422745354100802</v>
-      </c>
-      <c r="C11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>34.983383524448797</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>45049</v>
-      </c>
-      <c r="B12">
-        <v>0.20547930573848</v>
-      </c>
-      <c r="C12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12">
-        <v>53.152789367811998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>45063</v>
-      </c>
-      <c r="B13">
-        <v>0.168078940883987</v>
-      </c>
-      <c r="C13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13">
-        <v>33.341043343649702</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>45076</v>
-      </c>
-      <c r="B14">
-        <v>0.25776243935158599</v>
-      </c>
-      <c r="C14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14">
-        <v>31.9180285667398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>45089</v>
-      </c>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="B15">
         <v>0.30718976746298698</v>
       </c>
       <c r="C15" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>15.8650769934215</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>44865</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>27</v>
       </c>
       <c r="B16">
-        <v>0.24912069961521999</v>
+        <v>0.97908907233996301</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16">
-        <v>26.1959995510725</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>44879</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>0.23799883780685399</v>
+        <v>0.35708644464821998</v>
       </c>
       <c r="C17" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D17">
-        <v>94.218748150536896</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>44893</v>
+        <v>9.73092604234097</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>0.26752308407063402</v>
+        <v>0.35708644464821998</v>
       </c>
       <c r="C18" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D18">
-        <v>115.910838296351</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>44907</v>
+        <v>9.5554623120508193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>28</v>
       </c>
       <c r="B19">
-        <v>0.16056832408994501</v>
+        <v>0.73912910715284497</v>
       </c>
       <c r="C19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19">
-        <v>42.614245239660903</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D19">
+    <sortCondition descending="1" ref="D2:D19"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <drawing r:id="rId1"/>
@@ -6911,9 +6888,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6927,287 +6904,287 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>44930</v>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A2" t="s">
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>44951</v>
+        <v>38</v>
+      </c>
+      <c r="D2" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A3" t="s">
+        <v>25</v>
       </c>
       <c r="B3">
         <v>0.74411257103448103</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D3">
         <v>12.0270837749951</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>44951</v>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A4" t="s">
+        <v>25</v>
       </c>
       <c r="B4">
         <v>0.74411257103448103</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D4">
         <v>11.673900030623701</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>44951</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A5" t="s">
+        <v>25</v>
       </c>
       <c r="B5">
         <v>0.74411257103448103</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>4.8225004830932496</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>44963</v>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A6" t="s">
+        <v>26</v>
       </c>
       <c r="B6">
         <v>0.87528110109794</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>2.0901187683293201</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>44963</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A7" t="s">
+        <v>26</v>
       </c>
       <c r="B7">
         <v>0.87528110109794</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D7">
         <v>2.0802072636448998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>44963</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A8" t="s">
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0.87528110109794</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>3.4348545944842801</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>44979</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A9" t="s">
+        <v>27</v>
       </c>
       <c r="B9">
         <v>1.62598028208757</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>11.4435970636991</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>44979</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A10" t="s">
+        <v>27</v>
       </c>
       <c r="B10">
         <v>1.62598028208757</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>5.2429283117314203</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>44993</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A11" t="s">
+        <v>28</v>
       </c>
       <c r="B11">
         <v>1.32277923770115</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D11">
         <v>8.1503583923791698</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>44993</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A12" t="s">
+        <v>28</v>
       </c>
       <c r="B12">
         <v>1.32277923770115</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>22.095712310493202</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>45005</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A13" t="s">
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>45021</v>
+        <v>38</v>
+      </c>
+      <c r="D13" t="e">
+        <v>#NUM!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A14" t="s">
+        <v>29</v>
       </c>
       <c r="B14">
         <v>1.0535668624027901</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D14">
         <v>5.8251150947610704</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>45035</v>
-      </c>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
       <c r="B15">
         <v>0.78894922945176305</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D15">
         <v>6.4381260228580199</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>45049</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16">
         <v>0.73759563320647703</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>5.5662125718823496</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
-        <v>45063</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A17" t="s">
+        <v>32</v>
       </c>
       <c r="B17">
         <v>0.73062868871751996</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>5.1949848895037301</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <v>45063</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A18" t="s">
+        <v>32</v>
       </c>
       <c r="B18">
         <v>0.73062868871751996</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D18">
         <v>5.1262681581610803</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <v>44865</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A19" t="s">
+        <v>34</v>
       </c>
       <c r="B19">
         <v>0.74233596483651698</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1">
-        <v>44865</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A20" t="s">
+        <v>34</v>
       </c>
       <c r="B20">
         <v>0.74233596483651698</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>44865</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A21" t="s">
+        <v>34</v>
       </c>
       <c r="B21">
         <v>0.74233596483651698</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>44879</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A22" t="s">
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>44893</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A23" t="s">
+        <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
-        <v>44907</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+      <c r="A24" t="s">
+        <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/04_Outputs/rC_k600_edited.xlsx
+++ b/04_Outputs/rC_k600_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SpringMetabolism_FlowReversals\04_Outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63B7E1C1-C871-4A8E-B165-A4DA5D1ACD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6BD00B-A5C4-4D98-BFAB-32978976AC1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25080" yWindow="-3480" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AM" sheetId="1" r:id="rId1"/>
@@ -434,41 +434,14 @@
                 <c:pt idx="6">
                   <c:v>18.462931172278498</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>17.7130396770579</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>16.172118752756798</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>16.096811745708699</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>15.446661759491001</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>15.0741857995821</c:v>
-                </c:pt>
                 <c:pt idx="12">
                   <c:v>14.63795920784</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>14.4002343744848</c:v>
                 </c:pt>
-                <c:pt idx="14">
-                  <c:v>10.452469010274299</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10.246063982032499</c:v>
-                </c:pt>
                 <c:pt idx="18">
                   <c:v>7.0685800720140799</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>6.6081279033771398</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>6.4931180194822504</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>3.2051859433009899</c:v>
@@ -5595,9 +5568,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5611,7 +5584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -5622,7 +5595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>0.64562359749952802</v>
       </c>
@@ -5630,7 +5603,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>0.64562359749952802</v>
       </c>
@@ -5641,7 +5614,7 @@
         <v>32.497387104732198</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -5655,7 +5628,7 @@
         <v>30.003218289191299</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5669,7 +5642,7 @@
         <v>22.583603072389199</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>0.74979625322111798</v>
       </c>
@@ -5680,7 +5653,7 @@
         <v>22.534752718028901</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>0.82262807678377803</v>
       </c>
@@ -5691,7 +5664,7 @@
         <v>18.462931172278498</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -5701,11 +5674,8 @@
       <c r="C9" t="s">
         <v>5</v>
       </c>
-      <c r="D9">
-        <v>17.7130396770579</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -5715,11 +5685,8 @@
       <c r="C10" t="s">
         <v>5</v>
       </c>
-      <c r="D10">
-        <v>16.172118752756798</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -5729,22 +5696,16 @@
       <c r="C11" t="s">
         <v>5</v>
       </c>
-      <c r="D11">
-        <v>16.096811745708699</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>0.65936577783929395</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="D12">
-        <v>15.446661759491001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -5754,11 +5715,8 @@
       <c r="C13" t="s">
         <v>5</v>
       </c>
-      <c r="D13">
-        <v>15.0741857995821</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -5772,7 +5730,7 @@
         <v>14.63795920784</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -5786,7 +5744,7 @@
         <v>14.4002343744848</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -5796,11 +5754,8 @@
       <c r="C16" t="s">
         <v>5</v>
       </c>
-      <c r="D16">
-        <v>10.452469010274299</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -5810,11 +5765,8 @@
       <c r="C17" t="s">
         <v>5</v>
       </c>
-      <c r="D17">
-        <v>10.246063982032499</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -5825,7 +5777,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
@@ -5836,7 +5788,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -5850,7 +5802,7 @@
         <v>7.0685800720140799</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -5860,11 +5812,8 @@
       <c r="C21" t="s">
         <v>5</v>
       </c>
-      <c r="D21">
-        <v>6.6081279033771398</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -5874,11 +5823,8 @@
       <c r="C22" t="s">
         <v>5</v>
       </c>
-      <c r="D22">
-        <v>6.4931180194822504</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -5889,7 +5835,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -5903,7 +5849,7 @@
         <v>3.2051859433009899</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -5917,7 +5863,7 @@
         <v>2.80439946223186</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -5931,7 +5877,7 @@
         <v>2.7939784771177898</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -5945,7 +5891,7 @@
         <v>2.4120794603422602</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -5959,7 +5905,7 @@
         <v>2.4072832616244</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -5970,7 +5916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -5981,7 +5927,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -5992,7 +5938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -6016,9 +5962,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D29"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6032,7 +5978,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6040,7 +5986,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -6051,7 +5997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -6062,7 +6008,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -6076,7 +6022,7 @@
         <v>32.379700829916601</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -6090,7 +6036,7 @@
         <v>32.274144438345303</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -6104,7 +6050,7 @@
         <v>31.877696149374302</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -6118,7 +6064,7 @@
         <v>28.8790872259084</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>0.41829191635495</v>
       </c>
@@ -6129,7 +6075,7 @@
         <v>21.2301041068087</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -6143,7 +6089,7 @@
         <v>20.759702379649699</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>0.40867897602588799</v>
       </c>
@@ -6154,7 +6100,7 @@
         <v>19.545410722183501</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>0.40867897602588799</v>
       </c>
@@ -6165,7 +6111,7 @@
         <v>19.3542063534147</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -6179,7 +6125,7 @@
         <v>19.278549967453198</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -6193,7 +6139,7 @@
         <v>18.3266040851639</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -6207,7 +6153,7 @@
         <v>18.238219059268399</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -6221,7 +6167,7 @@
         <v>17.612268500013801</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -6235,7 +6181,7 @@
         <v>16.082464877533099</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -6249,7 +6195,7 @@
         <v>15.8324828082942</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -6263,7 +6209,7 @@
         <v>15.491084387970799</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -6277,7 +6223,7 @@
         <v>15.422189134531401</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -6291,7 +6237,7 @@
         <v>12.5427239203201</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -6305,7 +6251,7 @@
         <v>11.7604829329048</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -6319,7 +6265,7 @@
         <v>11.63069034185</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -6333,7 +6279,7 @@
         <v>10.123963721124101</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -6347,7 +6293,7 @@
         <v>10.116682809798901</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -6361,7 +6307,7 @@
         <v>9.9882836327260591</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -6375,7 +6321,7 @@
         <v>8.0617713895940106</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -6389,7 +6335,7 @@
         <v>8.0092423263314494</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>20</v>
       </c>
@@ -6413,9 +6359,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6429,7 +6375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -6437,7 +6383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -6448,7 +6394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -6459,7 +6405,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -6470,7 +6416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1.00713808149247</v>
       </c>
@@ -6481,7 +6427,7 @@
         <v>9.3052048733349402</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -6492,7 +6438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -6506,7 +6452,7 @@
         <v>8.5316662064735205</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -6520,7 +6466,7 @@
         <v>8.2264856374067996</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -6531,7 +6477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -6545,7 +6491,7 @@
         <v>7.8958984290259</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -6559,7 +6505,7 @@
         <v>7.0638592430665703</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -6573,7 +6519,7 @@
         <v>6.2631698085533101</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -6587,7 +6533,7 @@
         <v>4.44794425583971</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -6601,7 +6547,7 @@
         <v>4.17908012369488</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -6628,9 +6574,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6644,7 +6590,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -6655,7 +6601,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -6666,7 +6612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -6677,7 +6623,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
@@ -6691,7 +6637,7 @@
         <v>53.152789367811998</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -6705,7 +6651,7 @@
         <v>50.954752325421801</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -6719,7 +6665,7 @@
         <v>42.614245239660903</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -6733,7 +6679,7 @@
         <v>34.983383524448797</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -6747,7 +6693,7 @@
         <v>33.341043343649702</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -6761,7 +6707,7 @@
         <v>31.9180285667398</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -6772,7 +6718,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -6786,7 +6732,7 @@
         <v>26.1959995510725</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -6800,7 +6746,7 @@
         <v>24.690084932127998</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -6814,7 +6760,7 @@
         <v>23.148382126467901</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>0.30718976746298698</v>
       </c>
@@ -6825,7 +6771,7 @@
         <v>15.8650769934215</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -6836,7 +6782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -6850,7 +6796,7 @@
         <v>9.73092604234097</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -6864,7 +6810,7 @@
         <v>9.5554623120508193</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>28</v>
       </c>
@@ -6888,9 +6834,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultColWidth="11.40625" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6904,7 +6850,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -6915,7 +6861,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -6929,7 +6875,7 @@
         <v>12.0270837749951</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -6943,7 +6889,7 @@
         <v>11.673900030623701</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -6957,7 +6903,7 @@
         <v>4.8225004830932496</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -6971,7 +6917,7 @@
         <v>2.0901187683293201</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -6985,7 +6931,7 @@
         <v>2.0802072636448998</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -6999,7 +6945,7 @@
         <v>3.4348545944842801</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -7013,7 +6959,7 @@
         <v>11.4435970636991</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -7027,7 +6973,7 @@
         <v>5.2429283117314203</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -7041,7 +6987,7 @@
         <v>8.1503583923791698</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -7052,7 +6998,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -7063,7 +7009,7 @@
         <v>#NUM!</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>29</v>
       </c>
@@ -7077,7 +7023,7 @@
         <v>5.8251150947610704</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>0.78894922945176305</v>
       </c>
@@ -7088,7 +7034,7 @@
         <v>6.4381260228580199</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>31</v>
       </c>
@@ -7102,7 +7048,7 @@
         <v>5.5662125718823496</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -7116,7 +7062,7 @@
         <v>5.1949848895037301</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>32</v>
       </c>
@@ -7130,7 +7076,7 @@
         <v>5.1262681581610803</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -7141,7 +7087,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
@@ -7152,7 +7098,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -7163,7 +7109,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -7171,7 +7117,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -7179,7 +7125,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
